--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="6" min="1" max="1"/>
@@ -476,17 +476,29 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Пустых «примерно» без источника. Если открытой цифры нет — «н/д». Региональные сети и большинство молочных заводов так и стоят: они отчитаются в 2027-м.</t>
+          <t>Пустых «примерно» без источника. Если открытой цифры нет — «н/д». Региональные сети и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Отраслевой фон (топ-10 сетей +9–11%, пищепром около нуля, e-grocery 1,83 трлн) в персональную ячейку не ставили.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" s="6">
       <c r="A11" s="9" t="inlineStr">
         <is>
+          <t>Были ли прогнозы в конце 2025 / начале 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Свои рублёвые — почти ни у кого из «н/д». X5 ещё в марте держала +12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «проекты начнут окупаться», без суммы. У регионалов вместо прогноза кассы были новости про продажу сети. Глобальные PepsiCo/Nestlé — мировой organic, не Россия.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1" s="6">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
           <t>Формат файла</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Списки те же: сети и производители в том же порядке. Добавлен только этот лист и обновлён «Медиа».</t>
         </is>
@@ -950,7 +962,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Отдельной продуктовой выручки Ozon Fresh за 2026 нет. Data Insight: пятёрка e-grocery (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) во 2 кв. вместе 260 млрд ₽ и 214 млн заказов; у Ozon Fresh заказы +65%. Это оборот рынка доставки, не строка МСФО Ozon. https://abn.agency/2026/08/14/oborot-rossijskogo-egrocery-dostig-8942-mlrd-rublej-za-polugodie/</t>
+          <t>Своей продуктовой выручки Ozon Fresh на 2026 нет — ни факта, ни прогноза компании. Что было в начале года: Data Insight в январе 2026 ждал рынок e-grocery 1,8 трлн ₽ за год (+24% к 2025), к марту уточнил до 1,83 трлн (+22%), к маю 1,84 трлн. Это весь рынок доставки, не строка МСФО Ozon. Во 2 кв. пятёрка (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) вместе 260 млрд; у Ozon Fresh заказы +65%. https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
     </row>
@@ -992,7 +1004,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Выручку Лавки отдельно не публикуют. Блок e-com Яндекса (Лавка+Маркет+Еда+Деливери) 1П 247 млрд (+19%) — это не только продукты. Заказы Лавки во 2 кв. +5% (Data Insight). https://www.comnews.ru/content/246667/2026-07-31/2026-w31/1008/ozon-ustremilsya-lidery-sredi-marketpleysov</t>
+          <t>Выручку Лавки отдельно не публикуют и прогноза по ней не было. Блок e-com Яндекса (Лавка+Маркет+Еда+Деливери) 1П 247 млрд (+19%) — это не только продукты. Заказы Лавки во 2 кв. +5% (Data Insight). Рыночный ориентир того же агентства на 2026: весь e-grocery 1,83–1,84 трлн — не цифра Лавки. https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1042,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" s="6">
+    <row r="15" ht="48" customHeight="1" s="6">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ТС Победа / Гулливер / Народный амбар (ТК Лето)</t>
@@ -1068,11 +1080,11 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1" s="6">
+          <t>Своего рублёвого прогноза на 2026 не было. В начале 2026 «Гулливер» из того же контура писали как выставленный на продажу. Аналитик Совкомбанка: независимые сети с кассой &gt;100 млрд (Победа, Командор, Ярче, Аникс) в 2–3 года могут сменить собственника — это не цифра выручки. Последнее открытое: 176 млрд за 2025. https://www.kommersant.ru/doc/8364093</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="6">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Ярче! (Камелот-А, Томск)</t>
@@ -1110,11 +1122,11 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1" s="6">
+          <t>Прогноза выручки на 2026 нет. В обзорах конца 2025 / 2026 фигурирует как кандидат на M&amp;A, не как эмитент с guidance. Последнее открытое: 168 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="6">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Гиперглобус (Globus)</t>
@@ -1125,38 +1137,30 @@
           <t>гипер</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+          <t>1 пол.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1" s="6">
+          <t>INFOLine / «Коммерсантъ»: 1П 80,6 млрд без НДС (+2,7%). Сопоставимые продажи 1П +5,7%, корзина +7,5% (оценка, знакомая с аналитикой сети). Своего прогноза выручки на 2026 нет. План экспансии — гипер в 2027 (&gt;4 млрд капзатрат), не цифра кассы на этот год. Оценка года: 165,6 × 1,027. https://www.kommersant.ru/doc/9005166</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="6">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Верный (Союз Святого Иоанна Воина)</t>
@@ -1194,7 +1198,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Прогноза кассы на 2026 нет. Октябрь 2025: основатель ищет покупателя, оценка бизнеса 25–35 млрд ₽ (это цена сети, не выручка года). РСБУ 2025 вышел 1 апреля 2026: 154,4 млрд — прошлый год. https://www.kommersant.ru/doc/8158706</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1" s="6">
+    <row r="20" ht="48" customHeight="1" s="6">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Мария-Ра (Розница К-1)</t>
@@ -1265,18 +1269,16 @@
           <t>н/д</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>1303</v>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1" s="6">
+          <t>Прогноза выручки на 2026 нет. Последнее: РСБУ 2025 = 127,5 млрд (+5%). На 1 июля 2026 — 1 303 магазина (штуки, не касса). Летом 2026 писали, что Лента смотрит покупку — сделка не подтверждена и цифры года не даёт. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="6">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Ермолино (оценка INFOLine, производство + своя розница)</t>
@@ -1314,11 +1316,11 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1" s="6">
+          <t>Своего прогноза на 2026 нет. INFOLine ставит оценку только по закрытому году. Последнее: ~111 млрд за 2025 (оценка, не МСФО).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="6">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>ГК Командор (Командор, Аллея, Хороший)</t>
@@ -1356,7 +1358,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Прогноза выручки на 2026 нет. В списках возможных M&amp;A 2026–2028 (Совкомбанк) — без суммы кассы. Последнее открытое: ~100 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1434,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1476,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1518,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1560,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1600,11 +1602,11 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1" s="6">
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="6">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Аникс (ТС Аникс + Прайд-А)</t>
@@ -1642,7 +1644,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Прогноза на 2026 нет. Упоминается рядом с Победой / Ярче / Командором как возможный объект консолидации. Последнее: 31,3 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1686,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1728,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1770,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1812,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1854,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1896,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1938,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1980,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2022,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2064,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2106,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Региональные сети обычно публикуют РСБУ только весной следующего года.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" s="6">
+    <row r="2" ht="48" customHeight="1" s="6">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PepsiCo Россия (вкл. Вимм-Билль-Данн)</t>
@@ -2213,7 +2215,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Российского прогноза в рублях нет (с 2022 глобальная PepsiCo не даёт локальный outlook). Глобально декабрь 2025 / весна 2026: органика +2–4% на 2026 — это мир, не «PepsiCo Россия». https://www.interfax.ru/business/1070847</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2255,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1" s="6">
+    <row r="4" ht="48" customHeight="1" s="6">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ЭФКО</t>
@@ -2291,7 +2293,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Цифры на 2026 нет. План на 2025 был 440 млрд — не взяли (факт 344, 0%). Весной 2026 менеджмент: новые проекты начнут окупаться в 2026–2027, ждут рост выручки и прибыли — без суммы. https://abireg.ru/newsitem/113897/</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2337,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1" s="6">
+    <row r="6" ht="48" customHeight="1" s="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>KDV Group</t>
@@ -2373,7 +2375,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Прогноза на 2026 нет. INFOLine прямо ставит KDV в пример замедления: уже 2025 только +1%, в 2026 «динамика лидеров около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
     </row>
@@ -2409,11 +2411,11 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П: 141,6 млрд (+3,5%); скорр. EBITDA 27,2 (+38%). Оценка года: 288,7 × 1,035. https://www.interfax.ru/business/1111410</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" s="6">
+          <t>МСФО 1П: 141,6 млрд (+3,5%). Свой рублёвый прогноз на год компания не давала — только «продолжим увеличивать выручку», капзатраты 2026 снова режут. Независимая оценка smart-lab: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="6">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ГАП Ресурс</t>
@@ -2451,11 +2453,11 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" s="6">
+          <t>Рублёвого прогноза на 2026 нет. Июнь 2025 (ПМЭФ): трёхлетка капзатрат &gt;40 млрд, доп. объёмы птицы — в 2027. На 2025 обещали удержать выпуск ~1 070 тыс. т — факт 1 054. Это тонны, не касса 2026. https://www.agroinvestor.ru/investments/news/44400-gap-resurs-vlozhit-40-mlrd-rubley-v-rasshirenie-proizvodstva/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="6">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nestlé Россия</t>
@@ -2493,11 +2495,11 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" s="6">
+          <t>Выручки и прогноза по России на 2026 нет. Глобальный consensus аналитиков к Nestlé SA: органика ~3,5–3,7% на год — не российская цифра. https://www.nestle.com/sites/default/files/2026-10/nestle-sa-consensus-pre-Q32026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="6">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Mars Россия</t>
@@ -2535,11 +2537,11 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" s="6">
+          <t>Локального прогноза выручки на 2026 не публиковали.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="6">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Продимекс (сумма предприятий группы)</t>
@@ -2577,11 +2579,11 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" s="6">
+          <t>Прогноза выручки на 2026 не было. Открытое — сумма заводов за 2025 (~220–224 млрд по разным периметрам). РСБУ за 2026 выйдет весной 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="6">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Агропромкомплектация</t>
@@ -2619,11 +2621,11 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1" s="6">
+          <t>Сводного прогноза группы на 2026 нет. INFOLine за 2025: 204,4 млрд (+15%). Отдельные юрлица (АПК-Курск и др.) отчитываются по РСБУ раз в год.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="6">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Логика молока (ex-Danone / Health&amp;Nutrition)</t>
@@ -2634,38 +2636,30 @@
           <t>молочка / детское питание</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>84.5</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+          <t>1 пол.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1" s="6">
+          <t>Сама компания 16.07.2026: 84,5 млрд (+3,5%), молочка 510 тыс. т (+2,7%). Ориентир на год — не рубли, а «преодолеть 1 млн тонн готовой продукции». Инвестплан до 2030: 120 млрд. Оценка рублей на год: 167,1 × 1,035. https://logikamoloka.ru/press-centr/news/logika-moloka-podvodit-rezultaty-i-polugodiya-2026-goda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="6">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Напитки вместе (ex-AB InBev Efes)</t>
@@ -2703,11 +2697,11 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1" s="6">
+          <t>Выручки 2026 нет. Стратегия без суммы: пиво &gt;30% рынка, безалкоголка &gt;8% портфеля в 1П, 700 млн в завод Саранск в 2026. https://napitkivmeste.ru/odin-god-pod-brendom-napitki-vmeste-bolee-30-novyh-produktov-i-rekordnye-vlozheniya-v-zavody/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="6">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Балтика (ООО ПК Балтика)</t>
@@ -2745,11 +2739,11 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1" s="6">
+          <t>Прогноза выручки на 2026 нет. По 2025 выпуск пива −16% — компания сама назвала это запланированной модернизацией. https://www.kommersant.ru/doc/8401281</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="6">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Сибагро (совокупность компаний группы)</t>
@@ -2787,11 +2781,11 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1" s="6">
+          <t>Прогноза кассы на 2026 нет. После убытка 2025 (~4,2 млрд) холдинг сам сказал: масштабирование временно снимаем, фокус на рентабельности; точечно ~500 млн в Томскую птицефабрику. https://www.akm.ru/news/gruppa_kompaniy_sibagro_narastila_vyruchku_na_14_odnako_zakonchila_2025_god_s_chistym_ubytkom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="6">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Объединённые кондитеры (ООО, дистрибуция группы)</t>
@@ -2829,11 +2823,11 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1" s="6">
+          <t>Прогноза на 2026 нет. В конце 2025 ходили слухи о продаже холдинга — «Гута» опровергла. Последнее открытое: ~113 млрд за 2025. https://www.kommersant.ru/doc/8339681</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="6">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>АБИ (ABI Product)</t>
@@ -2871,7 +2865,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. Последнее: ~88 млрд за 2025 (INFOLine).</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2905,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1" s="6">
+    <row r="20" ht="48" customHeight="1" s="6">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Комос Групп (молочный контур рейтинга)</t>
@@ -2949,11 +2943,11 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1" s="6">
+          <t>Прогноза выручки на 2026 нет. INFOLine отмечает холдинг среди быстрорастущих молочников 2025, без цифры на этот год. Последнее: молочный контур 63,1 млрд за 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="6">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Орими Трейд (Tess, Greenfield, Jardin)</t>
@@ -2991,7 +2985,7 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Локального прогноза на 2026 не публиковали. Последнее: 62,3 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3027,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3069,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3109,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1" s="6">
+    <row r="25" ht="48" customHeight="1" s="6">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Прогресс (ФрутоНяня / Малышам)</t>
@@ -3153,11 +3147,11 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1" s="6">
+          <t>Прогноза на 2026 нет. Март 2026 — это отчёт за 2025: выручка 52,1 (+8%), прибыль 10,2. https://www.kommersant.ru/doc/8552221</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="6">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>ГК Молвест</t>
@@ -3195,11 +3189,11 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1" s="6">
+          <t>Рублёвого прогноза выручки на 2026 нет. Июль 2026: инвестпрограмма ~13 млрд до 2028 (глубокая переработка, ингредиенты) — это капзатраты, не касса года. https://milknews.ru/index/molochnye-produkty/molvest-13-mlrd-investicii.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="6">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Эссен Продакшн (Махеевъ)</t>
@@ -3237,7 +3231,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Прогноза выручки на 2026 нет. Отраслевой фон кондитеров: дорогое какао и упаковка, без персональной цифры. Последнее: 50,2 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3273,7 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3315,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Выручку 2026 не публиковали. 1 кв.: продажи в натуральном выражении +7,5%, бренды «Сады Придонья» +11%, Nemoloko +19% (РБК Компании). https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
+          <t>Выручку 2026 не публиковали. 1 кв.: продажи в натуральном выражении +7,5%, бренды «Сады Придонья» +11%, Nemoloko +19% (РБК Компании). Рублёвого прогноза года нет. https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3357,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3399,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3441,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3483,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3563,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3605,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3647,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3689,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3731,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3773,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3815,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3857,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3899,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3941,7 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3983,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4025,7 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4067,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4109,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4151,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4193,7 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4235,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4277,7 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4319,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4361,7 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4403,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4445,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4487,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4529,7 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4571,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4613,7 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4655,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4697,7 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4739,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4781,7 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Открытой выручки / прогноза за 2026 не нашли. Большинство заводов рейтинга INFOLine отчитываются раз в год.</t>
+          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4796,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -5083,212 +5077,110 @@
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+    <row r="14" ht="72" customHeight="1" s="6">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Что было вместо цифры, если её нет</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>По большинству региональных сетей и заводов своего рублёвого прогноза на 2026 не было ни в конце 2025, ни в начале 2026. Что находилось: отраслевой фон (INFOLine: топ-10 сетей за год +9–11%; пищепром «около нуля»), рынок e-grocery 1,83–1,84 трлн (Data Insight, это не Ozon и не Лавка), и качественные фразы вроде «проекты начнут окупаться» у ЭФКО. В ячейку это не ставили — это не выручка компании.</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
+    <row r="15" ht="72" customHeight="1" s="6">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>INFOLine — сети на весь 2026</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (в 1П десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не Мария-Ра и не Командор.</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>https://www.kommersant.ru/doc/8923592</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+    <row r="16" ht="72" customHeight="1" s="6">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>INFOLine — заводы</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Светлана Силенина, сентябрь 2026: после эмбарго-2014 крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 динамика лидеров «приблизилась к нулю». KDV как пример: уже 2025 только +1%.</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+    <row r="17" ht="72" customHeight="1" s="6">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Data Insight — e-grocery, начало 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>В январе агентство заложило рынок доставки продуктов на 1,8 трлн ₽ за 2026 (+24%). К марту 1,83 трлн (+22%), к маю 1,84 трлн. Это весь рынок с НДС и доставкой, не выручка одной Лавки или Ozon Fresh.</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>https://datainsight.ru/DI_eGrocery_april_2026</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
+    <row r="18" ht="72" customHeight="1" s="6">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Региональные сети — не прогноз кассы, а продажа</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Верный с октября 2025 ищут покупателя (оценка 25–35 млрд — цена бизнеса). Гулливер в начале 2026 писали как выставленный на продажу. Про Мария-Ра летом 2026 писали, что смотрит Лента. Цифры выручки на 2026 никто из них не давал.</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>https://www.kommersant.ru/doc/8158706</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5304,6 +5196,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Сегодня 19 октября 2026. Финансовый год закроется 31 декабря. Годовые МСФО/РСБУ компании обычно публикуют весной 2027. Поэтому в таблице два разных числа: уже вышедший кусок года и, где можно, оценка полного года.</t>
+          <t>Сегодня 19 октября 2026. Год закроется 31 декабря. Полные годовые отчёты компании обычно публикуют весной 2027. Поэтому в таблице два разных числа: уже вышедший кусок года и, где можно, оценка полного года.</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Только опубликованная выручка за 9 месяцев, полугодие или (редко) квартал. X5 — единственная из крупных, у кого на октябрь уже есть 9 месяцев. Магнит, Лента, Fix Price, Русагро, Черкизово — полугодие. Светофор, Mercury, Самокат, Ашан, Metro — оценки INFOLine за полугодие, не их собственный МСФО.</t>
+          <t>Только опубликованная выручка за девять месяцев, полгода или (редко) квартал. X5 — единственная из крупных, у кого на октябрь уже есть девять месяцев. Магнит, Лента, Fix Price, Русагро, Черкизово — полгода. Светофор, Mercury, Самокат, Ашан, Metro — оценки агентства INFOLine за полгода, не их собственный отчёт.</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Либо слова самой компании (X5: рост 12–16%; Мираторг: «несколько процентов»), либо простая арифметика: выручка-2025 × темп уже вышедшего куска 2026. Это не отчёт и не гарантия. У агро (Русагро) второе полугодие обычно сильнее первого — поэтому не умножали полугодие на два.</t>
+          <t>Либо слова самой компании (X5: рост 12–16%; Мираторг: «несколько процентов»), либо простая арифметика: выручка 2025, умноженная на рост уже вышедшего куска 2026. Это не отчёт и не гарантия. У «Русагро» осень обычно сильнее весны — поэтому полугодие на два не умножали.</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Пустых «примерно» без источника. Если открытой цифры нет — «н/д». Региональные сети и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Отраслевой фон (топ-10 сетей +9–11%, пищепром около нуля, e-grocery 1,83 трлн) в персональную ячейку не ставили.</t>
+          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных» (в таблице «н/д»). Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей +9–11%, производители еды около нуля, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Свои рублёвые — почти ни у кого из «н/д». X5 ещё в марте держала +12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «проекты начнут окупаться», без суммы. У регионалов вместо прогноза кассы были новости про продажу сети. Глобальные PepsiCo/Nestlé — мировой organic, не Россия.</t>
+          <t>Свои в рублях — почти ни у кого из тех, у кого в таблице «нет данных». X5 ещё в марте держала +12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «новые заводы начнут себя окупать», без суммы. У сетей из регионов вместо прогноза продаж были новости про продажу самой сети. Мировые PepsiCo и Nestlé дают прогноз на весь мир, не на Россию.</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Период факта</t>
+          <t>За какой кусок года</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>YoY факта, %</t>
+          <t>Рост к тому же куску 2025, %</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Оценка / прогноз года 2026, млрд ₽</t>
+          <t>Оценка / прогноз на весь 2026, млрд ₽</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Откуда цифра / как считали оценку</t>
+          <t>Откуда цифра, простыми словами</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>9 мес.</t>
+          <t>январь–сентябрь</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
@@ -602,7 +602,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>ПАО, trading update 16.10.2026 (предварительные, без аудита). 9М выручка 3 791,5 млрд (+11,4%); 3 кв. 1 311 млрд (+13,0%). Пятёрочка 9М 2 918 (+9,4%), Перекрёсток 413 (+7,1%), Чижик 391 (+31,4%), X5 Digital 257 (+28,4%). Магазинов 30 981 на 30.09. Прогноз самой компании на год: рост 12–16% от 4 642 → 5 200–5 385. https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
+          <t>Сама компания 16 октября 2026, цифры ещё без проверки аудитора. За январь–сентябрь продали на 3 791,5 млрд рублей — на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь: 1 311 млрд (+13%). Пятёрочка за девять месяцев 2 918 (+9,4%), Перекрёсток 413 (+7,1%), Чижик 391 (+31,4%), доставка X5 — 257 (+28,4%). Магазинов 30 981 на конец сентября. Свой прогноз на весь год компания не снимала: рост 12–16%. От выручки 2025 (4 642) это 5 200–5 385. https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П, 28.08.2026: 1 887,2 млрд (+12,8%). Чистая розница 1 871. Магазинов 33 652. Чистый долг ~514,5; убыток по IFRS 16 ≈ −9,5. Оценка года: 3 509 × 1,128, если темп 1П удержится (это не отчёт за год). https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
+          <t>Официальный отчёт 28 августа 2026: за полгода продали на 1 887,2 млрд рублей (+12,8%). Из них магазины 1 871. Точек 33 652. Долги минус деньги на счетах ≈ 514,5 млрд. По прибыли группа всё ещё в минусе (около −9,5) — мешают проценты по кредитам. Оценка всего года, если второе полугодие будет как первое: 3 509 × 1,128. Это не отчёт за год. https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ» 02.09.2026, топ-10 FMCG 1П: 878 млрд (+11,2%). Сводного МСФО холдинга нет. Оценка года: 1 660 × 1,112, если темп 1П удержится. https://www.kommersant.ru/doc/8923592</t>
+          <t>Агентство INFOLine в «Коммерсанте» 2 сентября 2026: за полгода 878 млрд (+11,2%). Своего сводного отчёта всей группы нет. Оценка года, если темп удержится: 1 660 × 1,112. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П: 648,5 млрд (+26,2%); 2 кв. 341,6 (+28,8%). Магазинов 7 456 на 30.06. Супер Лента +30,2%, Монетка +26,1%, гипер +12,9% (INFOLine). В августе закрыла покупку гипермаркетов «О’КЕЙ» — во 2П периметр шире. Оценка года без сделки: 1 104 × 1,262. Стратегия к 2028 — 2,2 трлн. https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
+          <t>Официальный отчёт: за полгода 648,5 млрд (+26,2%); апрель–июнь 341,6 (+28,8%). Магазинов 7 456 на 30 июня. Быстрее всех внутри группы — «Супер Лента» (+30,2%) и «Монетка» (+26,1%), большие магазины +12,9%. В августе купила большие магазины «О’КЕЙ» — с осени в цифрах будут ещё и чужие точки. Оценка года без этой покупки: 1 104 × 1,262. К 2028 сама Лента хочет 2,2 триллиона — это цель на потом, не на 2026. https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -737,12 +737,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ»: 189 млрд (−4,5%). Оценка года: 394 × 0,955. https://www.kommersant.ru/doc/8923592</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 189 млрд — на 4,5% меньше, чем годом раньше. Оценка года: 394 × 0,955. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -773,12 +773,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ»: 191,06 млрд (+7,8%), обогнал Светофор в топ-5. Оценка года: 359 × 1,078. https://www.infoline.spb.ru/news/?news=308855</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 191,06 млрд (+7,8%). Обогнал «Светофор» среди пяти крупнейших. Оценка года: 359 × 1,078. https://www.infoline.spb.ru/news/?news=308855</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П, 27.08.2026: 155,3 млрд (+4,8%); 2 кв. 82,2 (+6,9%). Розница 1П 138,2, опт 17,1. Магазинов 8 077. Оценка года: 313 × 1,048. https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
+          <t>Официальный отчёт 27 августа 2026: за полгода 155,3 млрд (+4,8%); апрель–июнь 82,2 (+6,9%). Магазины 138,2, опт 17,1. Точек 8 077. Оценка года: 313 × 1,048. https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -843,12 +843,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Оценка INFOLine / «Коммерсантъ»: 135 млрд (+15,5%). Оценка года: 279 × 1,155. https://www.kommersant.ru/doc/8923592</t>
+          <t>Оценка агентства INFOLine / «Коммерсантъ»: за полгода 135 млрд (+15,5%). Оценка года: 279 × 1,155. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -879,12 +879,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ»: 118,9 млрд (+0,5%). Оценка года: 260 × 1,005. https://www.kommersant.ru/doc/8923610</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 118,9 млрд (+0,5%). Оценка года: 260 × 1,005. https://www.kommersant.ru/doc/8923610</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -915,12 +915,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ»: 127 млрд (−2,5%). Оценка года: 250 × 0,975. https://www.kommersant.ru/doc/8923592</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 127 млрд — на 2,5% меньше, чем годом раньше. Оценка года: 250 × 0,975. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
@@ -937,32 +937,32 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Своей продуктовой выручки Ozon Fresh на 2026 нет — ни факта, ни прогноза компании. Что было в начале года: Data Insight в январе 2026 ждал рынок e-grocery 1,8 трлн ₽ за год (+24% к 2025), к марту уточнил до 1,83 трлн (+22%), к маю 1,84 трлн. Это весь рынок доставки, не строка МСФО Ozon. Во 2 кв. пятёрка (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) вместе 260 млрд; у Ozon Fresh заказы +65%. https://datainsight.ru/DI_eGrocery_april_2026</t>
+          <t>Сколько именно продуктов продал Ozon Fresh в 2026, компания не говорит — ни факта, ни своего прогноза. Что было в начале года: агентство Data Insight в январе ждало, что вся доставка продуктов в России за 2026 год будет около 1,8 триллиона рублей (+24% к 2025). К марту уточнили 1,83 триллиона (+22%), к маю 1,84. Это весь рынок доставки, не цифра Ozon. За апрель–июнь пять сервисов (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) вместе сделали 260 млрд; заказы Ozon Fresh +65%. https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
     </row>
@@ -979,32 +979,32 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Выручку Лавки отдельно не публикуют и прогноза по ней не было. Блок e-com Яндекса (Лавка+Маркет+Еда+Деливери) 1П 247 млрд (+19%) — это не только продукты. Заказы Лавки во 2 кв. +5% (Data Insight). Рыночный ориентир того же агентства на 2026: весь e-grocery 1,83–1,84 трлн — не цифра Лавки. https://datainsight.ru/DI_eGrocery_april_2026</t>
+          <t>Выручку Лавки отдельно не публикуют, своего прогноза по ней тоже не было. Весь интернет-блок Яндекса (Лавка + Маркет + Еда + Деливери) за полгода 247 млрд (+19%) — туда входят не только продукты. Заказов у Лавки за апрель–июнь +5%. Прогноз агентства Data Insight на 2026 — вся доставка продуктов в стране 1,83–1,84 триллиона. Это не цифра Лавки. https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1 пол. «ДА!»</t>
+          <t>январь–июнь, только «ДА!»</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>После продажи гипер в конце 2025 у листинга O’KEY Group остался только «ДА!»: МСФО 1П 43,3 млрд (+10,4%), 236 магазинов. Оценка года контура «ДА!»: 80 × 1,104. Гипер ООО «О’КЕЙ» по РСБУ 1П 68,2 (−5,6%) — уже периметр Ленты, не складывать с «ДА!». https://okeygroup.lu/upload/IFRS%201H2026_RUS_final_.pdf</t>
+          <t>Большие магазины «О’КЕЙ» в конце 2025 продали. У оставшейся компании на бирже теперь только «ДА!»: за полгода 43,3 млрд (+10,4%), 236 магазинов. Оценка года именно «ДА!»: 80 × 1,104. Большие магазины ООО «О’КЕЙ» за полгода 68,2 (−5,6%) — это уже Лента, с «ДА!» не складывать. https://okeygroup.lu/upload/IFRS%201H2026_RUS_final_.pdf</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не было. В начале 2026 «Гулливер» из того же контура писали как выставленный на продажу. Аналитик Совкомбанка: независимые сети с кассой &gt;100 млрд (Победа, Командор, Ярче, Аникс) в 2–3 года могут сменить собственника — это не цифра выручки. Последнее открытое: 176 млрд за 2025. https://www.kommersant.ru/doc/8364093</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не было. В начале 2026 про «Гулливер» из той же группы писали: сеть выставлена на продажу. Аналитик Совкомбанка: независимые сети, которые в 2025 продали больше чем на 100 млрд (Победа, Командор, Ярче, Аникс), в ближайшие 2–3 года могут сменить хозяина. Это не цифра выручки. Последнее открытое: 176 млрд за 2025. https://www.kommersant.ru/doc/8364093</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. В обзорах конца 2025 / 2026 фигурирует как кандидат на M&amp;A, не как эмитент с guidance. Последнее открытое: 168 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+          <t>Прогноза выручки на 2026 нет. В обзорах конца 2025 и 2026 сеть называют как возможную покупку для крупного игрока — не как компанию со своим прогнозом. Последнее открытое: 168 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ»: 1П 80,6 млрд без НДС (+2,7%). Сопоставимые продажи 1П +5,7%, корзина +7,5% (оценка, знакомая с аналитикой сети). Своего прогноза выручки на 2026 нет. План экспансии — гипер в 2027 (&gt;4 млрд капзатрат), не цифра кассы на этот год. Оценка года: 165,6 × 1,027. https://www.kommersant.ru/doc/9005166</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 80,6 млрд без налога (+2,7%). В тех же магазинах, что были год назад, продажи +5,7%, средний чек +7,5%. Своего прогноза выручки на 2026 нет. Новый большой магазин планируют на 2027 (больше 4 млрд на стройку) — это не цифра продаж на этот год. Оценка года: 165,6 × 1,027. https://www.kommersant.ru/doc/9005166</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Прогноза кассы на 2026 нет. Октябрь 2025: основатель ищет покупателя, оценка бизнеса 25–35 млрд ₽ (это цена сети, не выручка года). РСБУ 2025 вышел 1 апреля 2026: 154,4 млрд — прошлый год. https://www.kommersant.ru/doc/8158706</t>
+          <t>Прогноза выручки на 2026 нет. В октябре 2025 основатель искал покупателя: сеть оценивали в 25–35 млрд рублей. Это цена всего бизнеса, если его продадут, а не «сколько продадут за год». Российский отчёт за 2025 вышел 1 апреля 2026: 154,4 млрд — это прошлый год. https://www.kommersant.ru/doc/8158706</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>INFOLine / «Коммерсантъ»: «Спар Миддл Волга, Smart» 103,57 млрд (+7,8%) — периметр шире, чем строка 2025 (только SPAR МВ 136 за год). Оценка года грубая: 136 × 1,078. https://www.kommersant.ru/doc/8923592</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: «Спар Миддл Волга, Smart» за полгода 103,57 млрд (+7,8%). Тут шире, чем строка 2025 (тогда только SPAR Миддл Волга — 136 за год). Грубая оценка года: 136 × 1,078. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
@@ -1251,22 +1251,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. Последнее: РСБУ 2025 = 127,5 млрд (+5%). На 1 июля 2026 — 1 303 магазина (штуки, не касса). Летом 2026 писали, что Лента смотрит покупку — сделка не подтверждена и цифры года не даёт. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+          <t>Прогноза выручки на 2026 нет. Последнее: российский отчёт за 2025 — 127,5 млрд (+5%). На 1 июля 2026 — 1 303 магазина (это штуки, не деньги). Летом 2026 писали, что «Лента» смотрит покупку — сделка не подтверждена и цифры года не даёт. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1291,32 +1291,32 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Своего прогноза на 2026 нет. INFOLine ставит оценку только по закрытому году. Последнее: ~111 млрд за 2025 (оценка, не МСФО).</t>
+          <t>Своего прогноза на 2026 нет. Агентство INFOLine считает оценку только когда год уже закрыт. Последнее: около 111 млрд за 2025 (оценка агентства, не официальный отчёт компании).</t>
         </is>
       </c>
     </row>
@@ -1333,32 +1333,32 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. В списках возможных M&amp;A 2026–2028 (Совкомбанк) — без суммы кассы. Последнее открытое: ~100 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+          <t>Прогноза выручки на 2026 нет. В списках возможных покупок 2026–2028 (Совкомбанк) — без суммы продаж. Последнее открытое: около 100 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П, 24.08.2026: 51,2 млрд (+7,2%), EBITDA 4,5, прибыль 0,8, точек 2 225 на 30.06 (2 222 на 30.09). Оценка года с темпа 1П: 95,1 × 1,072. 9М «продажи с НДС +24%» — это не IFRS-выручка, в ячейку не ставили. https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
+          <t>Официальный отчёт 24 августа 2026: за полгода 51,2 млрд (+7,2%), прибыль 0,8, точек 2 225 на 30 июня (2 222 на 30 сентября). Оценка года, если темп полугодия удержится: 95,1 × 1,072. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это не та выручка, что в таблице. https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1451,32 +1451,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1535,32 +1535,32 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1577,32 +1577,32 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1619,32 +1619,32 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. Упоминается рядом с Победой / Ярче / Командором как возможный объект консолидации. Последнее: 31,3 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+          <t>Прогноза на 2026 нет. Упоминается рядом с «Победой», «Ярче» и «Командором» как сеть, которую крупный игрок может купить. Последнее: 31,3 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1703,32 +1703,32 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1745,32 +1745,32 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1787,32 +1787,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1829,32 +1829,32 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1871,32 +1871,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1913,32 +1913,32 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1997,32 +1997,32 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2039,32 +2039,32 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. РСБУ за 2026 выйдет весной 2027. Отраслевой фон INFOLine (топ-10 сетей +9–11% за год) — не персональный прогноз этой сети.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2153,17 +2153,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Период факта</t>
+          <t>За какой кусок года</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>YoY факта, %</t>
+          <t>Рост к тому же куску 2025, %</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Оценка / прогноз года 2026, млрд ₽</t>
+          <t>Оценка / прогноз на весь 2026, млрд ₽</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Откуда цифра / как считали оценку</t>
+          <t>Откуда цифра, простыми словами</t>
         </is>
       </c>
     </row>
@@ -2190,32 +2190,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>Российского прогноза в рублях нет (с 2022 глобальная PepsiCo не даёт локальный outlook). Глобально декабрь 2025 / весна 2026: органика +2–4% на 2026 — это мир, не «PepsiCo Россия». https://www.interfax.ru/business/1070847</t>
+          <t>Прогноза именно по России в рублях нет: с 2022 мировая PepsiCo российские планы не публикует. В декабре 2025 и весной 2026 мировой прогноз: рост продаж на 2–4% — это весь мир, не «PepsiCo Россия». https://www.interfax.ru/business/1070847</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П: 183,0 млрд (+9,1%). У агро 2П обычно больше 1П, поэтому не умножали на 2. Оценка года: 396,5 × 1,091, если темп удержится. https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
+          <t>Официальный отчёт: за полгода 183,0 млрд (+9,1%). У растениеводства и сахара осень обычно сильнее весны, поэтому полугодие на два не умножали. Оценка года, если темп удержится: 396,5 × 1,091. https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
         </is>
       </c>
     </row>
@@ -2268,32 +2268,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Цифры на 2026 нет. План на 2025 был 440 млрд — не взяли (факт 344, 0%). Весной 2026 менеджмент: новые проекты начнут окупаться в 2026–2027, ждут рост выручки и прибыли — без суммы. https://abireg.ru/newsitem/113897/</t>
+          <t>Цифры на 2026 нет. На 2025 сами планировали 440 млрд — не получилось (факт 344, рост ноль). Весной 2026 руководство: новые заводы начнут себя окупать в 2026–2027, ждут рост продаж и прибыли — без конкретной суммы. https://abireg.ru/newsitem/113897/</t>
         </is>
       </c>
     </row>
@@ -2310,17 +2310,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Полной выручки 1П 2026 в открытом виде нет. Президент Линник (ПМЭФ, июнь): ожидает рост выручки «на несколько процентов»; экспорт удержать ~58 млрд как в 2025 (план +20% по экспорту снят из‑за крепкого рубля). Оценка года ≈ 342 × 1,03. Прибыль МСФО 6 мес. 19,61 млрд (+26%) — это не выручка. https://echomsk.spb.ru/nws/5317198-miratorg-ogidaet-neznachitelnyj-rost-vyruchki-po-itogam-2026-goda.html</t>
+          <t>Полной выручки за январь–июнь 2026 в открытом виде нет. Глава компании Виктор Линник в июне на Петербургском экономическом форуме: ждать рост продаж «на несколько процентов»; продажи за границу удержать около 58 млрд, как в 2025 (план +20% сняли — рубль слишком крепкий). Оценка года ≈ 342 × 1,03. Прибыль за полгода 19,61 млрд (+26%) — это не выручка. https://echomsk.spb.ru/nws/5317198-miratorg-ogidaet-neznachitelnyj-rost-vyruchki-po-itogam-2026-goda.html</t>
         </is>
       </c>
     </row>
@@ -2350,32 +2350,32 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. INFOLine прямо ставит KDV в пример замедления: уже 2025 только +1%, в 2026 «динамика лидеров около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+          <t>Прогноза на 2026 нет. Агентство INFOLine берёт KDV как пример торможения: уже 2025 только +1%, а в 2026 у крупных производителей еды рост «около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>МСФО 1П: 141,6 млрд (+3,5%). Свой рублёвый прогноз на год компания не давала — только «продолжим увеличивать выручку», капзатраты 2026 снова режут. Независимая оценка smart-lab: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
+          <t>Официальный отчёт: за полгода 141,6 млрд (+3,5%). Свой прогноз в рублях на год компания не давала — только «продолжим увеличивать выручку», деньги на стройки в 2026 снова режут. Независимая оценка на сайте для инвесторов: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Рублёвого прогноза на 2026 нет. Июнь 2025 (ПМЭФ): трёхлетка капзатрат &gt;40 млрд, доп. объёмы птицы — в 2027. На 2025 обещали удержать выпуск ~1 070 тыс. т — факт 1 054. Это тонны, не касса 2026. https://www.agroinvestor.ru/investments/news/44400-gap-resurs-vlozhit-40-mlrd-rubley-v-rasshirenie-proizvodstva/</t>
+          <t>Прогноза в рублях на 2026 нет. В июне 2025 на Петербургском экономическом форуме: за три года вложат больше 40 млрд в новые птичники, добавка по мясу — в 2027. На 2025 обещали удержать выпуск около 1 070 тысяч тонн — вышло 1 054. Это тонны, не деньги 2026. https://www.agroinvestor.ru/investments/news/44400-gap-resurs-vlozhit-40-mlrd-rubley-v-rasshirenie-proizvodstva/</t>
         </is>
       </c>
     </row>
@@ -2470,32 +2470,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Выручки и прогноза по России на 2026 нет. Глобальный consensus аналитиков к Nestlé SA: органика ~3,5–3,7% на год — не российская цифра. https://www.nestle.com/sites/default/files/2026-10/nestle-sa-consensus-pre-Q32026.pdf</t>
+          <t>Выручки и прогноза по России на 2026 нет. Оценка аналитиков по всей мировой Nestlé: рост продаж около 3,5–3,7% за год — не российская цифра. https://www.nestle.com/sites/default/files/2026-10/nestle-sa-consensus-pre-Q32026.pdf</t>
         </is>
       </c>
     </row>
@@ -2512,32 +2512,32 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Локального прогноза выручки на 2026 не публиковали.</t>
+          <t>Своего прогноза выручки по России на 2026 не публиковали.</t>
         </is>
       </c>
     </row>
@@ -2554,32 +2554,32 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 не было. Открытое — сумма заводов за 2025 (~220–224 млрд по разным периметрам). РСБУ за 2026 выйдет весной 2027.</t>
+          <t>Прогноза выручки на 2026 не было. Открытое — сумма заводов за 2025 (около 220–224 млрд, считают по-разному). Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -2596,32 +2596,32 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Сводного прогноза группы на 2026 нет. INFOLine за 2025: 204,4 млрд (+15%). Отдельные юрлица (АПК-Курск и др.) отчитываются по РСБУ раз в год.</t>
+          <t>Прогноза всей группы на 2026 нет. Агентство INFOLine за 2025: 204,4 млрд (+15%). Отдельные компании группы (АПК-Курск и другие) отчитываются раз в год.</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Сама компания 16.07.2026: 84,5 млрд (+3,5%), молочка 510 тыс. т (+2,7%). Ориентир на год — не рубли, а «преодолеть 1 млн тонн готовой продукции». Инвестплан до 2030: 120 млрд. Оценка рублей на год: 167,1 × 1,035. https://logikamoloka.ru/press-centr/news/logika-moloka-podvodit-rezultaty-i-polugodiya-2026-goda/</t>
+          <t>Сама компания 16 июля 2026: за полгода продали на 84,5 млрд (+3,5%), молочки 510 тысяч тонн (+2,7%). Ориентир на год — не деньги, а «сделать больше 1 миллиона тонн готовой продукции». На стройки и оборудование до 2030 заложили 120 млрд. Оценка рублей на год: 167,1 × 1,035. https://logikamoloka.ru/press-centr/news/logika-moloka-podvodit-rezultaty-i-polugodiya-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -2672,32 +2672,32 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Выручки 2026 нет. Стратегия без суммы: пиво &gt;30% рынка, безалкоголка &gt;8% портфеля в 1П, 700 млн в завод Саранск в 2026. https://napitkivmeste.ru/odin-god-pod-brendom-napitki-vmeste-bolee-30-novyh-produktov-i-rekordnye-vlozheniya-v-zavody/</t>
+          <t>Выручки 2026 нет. План без суммы: пиво — больше 30% рынка, напитки без алкоголя — больше 8% продаж за первое полугодие, 700 миллионов в завод в Саранске в 2026. https://napitkivmeste.ru/odin-god-pod-brendom-napitki-vmeste-bolee-30-novyh-produktov-i-rekordnye-vlozheniya-v-zavody/</t>
         </is>
       </c>
     </row>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. По 2025 выпуск пива −16% — компания сама назвала это запланированной модернизацией. https://www.kommersant.ru/doc/8401281</t>
+          <t>Прогноза выручки на 2026 нет. В 2025 выпуск пива упал на 16% — компания сама сказала, что так и задумала: обновляли заводы. Это про прошлый год, не про 2026. https://www.kommersant.ru/doc/8401281</t>
         </is>
       </c>
     </row>
@@ -2756,32 +2756,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Прогноза кассы на 2026 нет. После убытка 2025 (~4,2 млрд) холдинг сам сказал: масштабирование временно снимаем, фокус на рентабельности; точечно ~500 млн в Томскую птицефабрику. https://www.akm.ru/news/gruppa_kompaniy_sibagro_narastila_vyruchku_na_14_odnako_zakonchila_2025_god_s_chistym_ubytkom/</t>
+          <t>Прогноза выручки на 2026 нет. После убытка 2025 (около 4,2 млрд) группа сама сказала: новые большие стройки пока не начинаем, сначала надо выйти в плюс; точечно около 500 миллионов в Томскую птицефабрику. https://www.akm.ru/news/gruppa_kompaniy_sibagro_narastila_vyruchku_na_14_odnako_zakonchila_2025_god_s_chistym_ubytkom/</t>
         </is>
       </c>
     </row>
@@ -2798,32 +2798,32 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. В конце 2025 ходили слухи о продаже холдинга — «Гута» опровергла. Последнее открытое: ~113 млрд за 2025. https://www.kommersant.ru/doc/8339681</t>
+          <t>Прогноза на 2026 нет. В конце 2025 ходили слухи, что группу продадут — владельцы («Гута») опровергли. Последнее открытое: около 113 млрд за 2025. https://www.kommersant.ru/doc/8339681</t>
         </is>
       </c>
     </row>
@@ -2840,32 +2840,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. Последнее: ~88 млрд за 2025 (INFOLine).</t>
+          <t>Своего прогноза выручки на 2026 не публиковали. Последнее: около 88 млрд за 2025 (агентство INFOLine).</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Пресс-служба 07.09.2026: 46,3 млрд (+19%), EBITDA 10. Оценка года: 82,8 × 1,19. https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
+          <t>Пресс-служба 7 сентября 2026: за полгода 46,3 млрд (+19%). Оценка года: 82,8 × 1,19. https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
         </is>
       </c>
     </row>
@@ -2918,32 +2918,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. INFOLine отмечает холдинг среди быстрорастущих молочников 2025, без цифры на этот год. Последнее: молочный контур 63,1 млрд за 2025.</t>
+          <t>Прогноза выручки на 2026 нет. Агентство INFOLine отмечает группу среди быстрорастущих молочников 2025, без цифры на этот год. Последнее: только молочная часть 63,1 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -2960,32 +2960,32 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Локального прогноза на 2026 не публиковали. Последнее: 62,3 млрд за 2025.</t>
+          <t>Своего прогноза по России на 2026 не публиковали. Последнее: 62,3 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -3002,32 +3002,32 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3044,32 +3044,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>1 пол.</t>
+          <t>январь–июнь</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>МСФО 6 мес.: 24,63 млрд (−6,4% к 26,31). Прибыль 1,99 (−40%). Оценка года: 56,4 × 0,936. Объём свинины +10% при падении цены. https://www.tbank.ru/invest/social/profile/Marten_Resting/cbc77ff8-2a7f-49ae-8534-59a60c86da65/</t>
+          <t>Официальный отчёт за полгода: 24,63 млрд — на 6,4% меньше, чем 26,31 годом раньше. Прибыль 1,99 (−40%). Оценка года: 56,4 × 0,936. Свинины в тоннах сделали на 10% больше, но она подешевела. https://www.tbank.ru/invest/social/profile/Marten_Resting/cbc77ff8-2a7f-49ae-8534-59a60c86da65/</t>
         </is>
       </c>
     </row>
@@ -3122,32 +3122,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. Март 2026 — это отчёт за 2025: выручка 52,1 (+8%), прибыль 10,2. https://www.kommersant.ru/doc/8552221</t>
+          <t>Прогноза на 2026 нет. В марте 2026 вышел отчёт за 2025: выручка 52,1 (+8%), прибыль 10,2. https://www.kommersant.ru/doc/8552221</t>
         </is>
       </c>
     </row>
@@ -3164,32 +3164,32 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Рублёвого прогноза выручки на 2026 нет. Июль 2026: инвестпрограмма ~13 млрд до 2028 (глубокая переработка, ингредиенты) — это капзатраты, не касса года. https://milknews.ru/index/molochnye-produkty/molvest-13-mlrd-investicii.html</t>
+          <t>Прогноза выручки на 2026 нет. Июль 2026: до 2028 вложат около 13 млрд в новые линии (белки из молока и другие ингредиенты) — это деньги на стройку, не «сколько продадут за год». https://milknews.ru/index/molochnye-produkty/molvest-13-mlrd-investicii.html</t>
         </is>
       </c>
     </row>
@@ -3206,32 +3206,32 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. Отраслевой фон кондитеров: дорогое какао и упаковка, без персональной цифры. Последнее: 50,2 млрд за 2025.</t>
+          <t>Прогноза выручки на 2026 нет. У кондитеров в целом дорогое какао и упаковка — без цифры именно этой компании. Последнее: 50,2 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -3248,32 +3248,32 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3290,32 +3290,32 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1 кв., только тонны</t>
+          <t>январь–март, только тонны</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Выручку 2026 не публиковали. 1 кв.: продажи в натуральном выражении +7,5%, бренды «Сады Придонья» +11%, Nemoloko +19% (РБК Компании). Рублёвого прогноза года нет. https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
+          <t>Выручку 2026 в деньгах не публиковали. За январь–март продали на 7,5% больше в тоннах, бренды «Сады Придонья» +11%, Nemoloko +19%. Прогноза в рублях на год нет. https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3374,32 +3374,32 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3416,32 +3416,32 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3458,32 +3458,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>1 пол. весь холдинг</t>
+          <t>январь–июнь, вся группа</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>МСФО холдинга 1П 45,2 млрд (−2,8%), прибыль 1,1. Это ВЕСЬ холдинг, не молочный контур рейтинга INFOLine 2025 (29,8) — сравнивать с 29,8 нельзя. Оценку года для контура не ставили. https://abireg.ru/newsitem/116916/</t>
+          <t>Официальный отчёт всей группы за полгода: 45,2 млрд (−2,8%), прибыль 1,1. Это ВСЯ компания, а не только молочная часть, которую агентство INFOLine считало за 2025 (29,8). С 29,8 сравнивать нельзя. Оценку года только для молочки не ставили. https://abireg.ru/newsitem/116916/</t>
         </is>
       </c>
     </row>
@@ -3538,32 +3538,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3580,32 +3580,32 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3622,32 +3622,32 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3664,32 +3664,32 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3706,32 +3706,32 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3748,32 +3748,32 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3790,32 +3790,32 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3832,32 +3832,32 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3874,32 +3874,32 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3916,32 +3916,32 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3958,32 +3958,32 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4000,32 +4000,32 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4042,32 +4042,32 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4084,32 +4084,32 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4126,32 +4126,32 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4168,32 +4168,32 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4210,32 +4210,32 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4294,32 +4294,32 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4336,32 +4336,32 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4378,32 +4378,32 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4420,32 +4420,32 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4546,32 +4546,32 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4630,32 +4630,32 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4672,32 +4672,32 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4714,32 +4714,32 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4756,32 +4756,32 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>н/д</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Своего рублёвого прогноза на 2026 не публиковали. INFOLine (сентябрь 2026): у лидеров пищепрома динамика «около нуля» — это отрасль, не эта компания. РСБУ за 2026 — весной 2027.</t>
+          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Года ещё нет (сейчас октябрь 2026), полного МСФО за 2026 ни у кого нет. В столбце «факт» — уже опубликованный кусок: 9 месяцев, полугодие или квартал. «Оценка года» — не отчёт, а арифметика: либо прогноз самой компании, либо выручка-2025 × темп уже вышедшего куска 2026. Где куска нет — «н/д», ничего не додумано.</t>
+          <t>Года ещё нет (сейчас октябрь 2026), полного отчёта за весь 2026 ни у кого нет. В столбце «факт» — уже опубликованный кусок: девять месяцев, полгода или квартал. «Оценка года» — не отчёт, а арифметика: либо прогноз самой компании, либо выручка 2025, умноженная на рост уже вышедшего куска 2026. Где куска нет — «нет данных», ничего не додумано.</t>
         </is>
       </c>
       <c r="C2" s="14" t="inlineStr">
@@ -4849,12 +4849,12 @@
     <row r="3" ht="72" customHeight="1" s="6">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>X5 — 9 месяцев</t>
+          <t>X5 — январь–сентябрь</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Касса за январь–сентябрь 3,79 трлн ₽, на 11,4% больше, чем за те же 9 месяцев 2025-го. Третий квартал быстрее полугодия: +13% до 1,31 трлн. Чижик по-прежнему самый быстрый внутри группы (+31% за 9 мес., +35% за квартал). Компания свой прогноз на весь год не снимала: +12–16%.</t>
+          <t>Продали за январь–сентябрь на 3,79 триллиона рублей, на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь быстрее полугодия: +13% до 1,31 триллиона. Чижик по-прежнему самый быстрый внутри группы (+31% за девять месяцев, +35% за квартал). Компания свой прогноз на весь год не снимала: +12–16%.</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
@@ -4870,12 +4870,12 @@
     <row r="4" ht="72" customHeight="1" s="6">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>X5 — ориентир на год</t>
+          <t>X5 — свой прогноз на год</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>В марте и снова в июне президент Екатерина Лобачева: прогноз роста выручки 12–16% на 2026 держим. От базы 4,642 трлн это примерно 5,20–5,39 трлн за полный год. 9 месяцев идут ближе к нижней границе.</t>
+          <t>В марте и снова в июне президент Екатерина Лобачева: прогноз роста выручки 12–16% на 2026 держим. От выручки 2025 (4,642 триллиона) это примерно 5,20–5,39 триллиона за полный год. Девять месяцев идут ближе к нижней границе.</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -4891,12 +4891,12 @@
     <row r="5" ht="72" customHeight="1" s="6">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Магнит — полугодие</t>
+          <t>Магнит — полгода</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1 887 млрд ₽ за полгода, +12,8%. Магазины работают, касса растёт, по прибыли группа всё ещё в минусе по IFRS 16. Это тот же сюжет, что в 2025: полка живая, проценты тяжёлые.</t>
+          <t>1 887 млрд рублей за полгода, +12,8%. Магазины работают, продажи растут, по прибыли группа всё ещё в минусе: мешают проценты по кредитам. Это тот же сюжет, что в 2025: полка живая, кредиты тяжёлые.</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -4912,12 +4912,12 @@
     <row r="6" ht="72" customHeight="1" s="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Топ-10 сетей, 1 пол. 2026</t>
+          <t>Десять крупнейших сетей, январь–июнь 2026</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>INFOLine сложил десятку: 6,76 трлн ₽, +11,6% (годом раньше десятка росла на 17%). Лента +26% — самый быстрый из крупных. Светофор и Ашан в минусе. На весь 2026 INFOLine ждёт рост крупнейших сетей примерно 9–11%.</t>
+          <t>Агентство INFOLine сложила десятку: 6,76 триллиона рублей, +11,6% (годом раньше десятка росла на 17%). Лента +26% — самый быстрый из крупных. Светофор и Ашан продали меньше, чем год назад. На весь 2026 агентство ждёт рост крупнейших сетей примерно 9–11%.</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -4933,12 +4933,12 @@
     <row r="7" ht="72" customHeight="1" s="6">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Лента — полугодие</t>
+          <t>Лента — полгода</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>648 млрд ₽ за полгода, +26%. Драйверы — Супер Лента и Монетка. В августе забрала гипер «О’КЕЙ» — второе полугодие будет уже с чужими магазинами в периметре.</t>
+          <t>648 млрд рублей за полгода, +26%. Тянут «Супер Лента» и «Монетка». В августе купила большие магазины «О’КЕЙ» — со второго полугодия в цифрах будут ещё и эти магазины.</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -4954,12 +4954,12 @@
     <row r="8" ht="72" customHeight="1" s="6">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Fix Price — полугодие</t>
+          <t>Fix Price — полгода</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>155 млрд ₽, +4,8%. Медленнее продуктовых федералов: фиксированная цена и смешанный ассортимент.</t>
+          <t>155 млрд рублей, +4,8%. Медленнее больших продуктовых сетей: цены фиксированные, в ассортименте не только еда.</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -4975,12 +4975,12 @@
     <row r="9" ht="72" customHeight="1" s="6">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Винлаб — полугодие</t>
+          <t>Винлаб — полгода</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>51 млрд ₽ по МСФО, +7%. Отдельно компания хвалится продажами с НДС за 9 месяцев (+24%) — это восстановление после кибератаки 2025-го, не путать с выручкой в таблице.</t>
+          <t>51 млрд рублей по официальному отчёту, +7%. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это отскок после кибератаки 2025-го, не путать с выручкой в таблице.</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -4996,12 +4996,12 @@
     <row r="10" ht="72" customHeight="1" s="6">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Русагро — полугодие</t>
+          <t>Русагро — полгода</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>183 млрд ₽, +9%. Догнать PepsiCo по году ещё рано: полного 2026 нет ни у кого из заводов.</t>
+          <t>183 млрд рублей, +9%. Догнать PepsiCo по году ещё рано: полного 2026 нет ни у кого из заводов.</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -5017,12 +5017,12 @@
     <row r="11" ht="72" customHeight="1" s="6">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Черкизово — полугодие</t>
+          <t>Черкизово — полгода</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>142 млрд ₽, всего +3,5%. Слабее инфляции: дешевле свинина и меньше экспорта в Китай.</t>
+          <t>142 млрд рублей, всего +3,5%. Слабее роста цен в магазинах: дешевле свинина и меньше продаж в Китай.</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -5038,12 +5038,12 @@
     <row r="12" ht="72" customHeight="1" s="6">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Дамате — полугодие</t>
+          <t>Дамате — полгода</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>46 млрд ₽, +19% — один из немногих заводов с двузначным ростом кассы.</t>
+          <t>46 млрд рублей, +19% — один из немногих заводов, у кого продажи выросли сильно.</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Выручку за 2026 пока не раскрыли. Глава холдинга в июне: ждать роста «на несколько процентов», экспорт удержать около 58 млрд ₽.</t>
+          <t>Выручку за 2026 пока не раскрыли. Глава группы в июне: ждать роста «на несколько процентов», продажи за границу удержать около 58 млрд рублей.</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>По большинству региональных сетей и заводов своего рублёвого прогноза на 2026 не было ни в конце 2025, ни в начале 2026. Что находилось: отраслевой фон (INFOLine: топ-10 сетей за год +9–11%; пищепром «около нуля»), рынок e-grocery 1,83–1,84 трлн (Data Insight, это не Ozon и не Лавка), и качественные фразы вроде «проекты начнут окупаться» у ЭФКО. В ячейку это не ставили — это не выручка компании.</t>
+          <t>По большинству сетей из регионов и заводов своего прогноза «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год +9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку выручки это не ставили — это не продажи компании.</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -5101,12 +5101,12 @@
     <row r="15" ht="72" customHeight="1" s="6">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>INFOLine — сети на весь 2026</t>
+          <t>Агентство INFOLine — сети на весь 2026</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (в 1П десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не Мария-Ра и не Командор.</t>
+          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -5122,12 +5122,12 @@
     <row r="16" ht="72" customHeight="1" s="6">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>INFOLine — заводы</t>
+          <t>Агентство INFOLine — заводы</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Светлана Силенина, сентябрь 2026: после эмбарго-2014 крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 динамика лидеров «приблизилась к нулю». KDV как пример: уже 2025 только +1%.</t>
+          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только +1%.</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -5143,12 +5143,12 @@
     <row r="17" ht="72" customHeight="1" s="6">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Data Insight — e-grocery, начало 2026</t>
+          <t>Доставка продуктов, начало 2026</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>В январе агентство заложило рынок доставки продуктов на 1,8 трлн ₽ за 2026 (+24%). К марту 1,83 трлн (+22%), к маю 1,84 трлн. Это весь рынок с НДС и доставкой, не выручка одной Лавки или Ozon Fresh.</t>
+          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (+24%). К марту 1,83 триллиона (+22%), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не выручка одной Лавки или Ozon Fresh.</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -5164,12 +5164,12 @@
     <row r="18" ht="72" customHeight="1" s="6">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Региональные сети — не прогноз кассы, а продажа</t>
+          <t>Сети из регионов — не прогноз продаж, а продажа самой сети</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Верный с октября 2025 ищут покупателя (оценка 25–35 млрд — цена бизнеса). Гулливер в начале 2026 писали как выставленный на продажу. Про Мария-Ра летом 2026 писали, что смотрит Лента. Цифры выручки на 2026 никто из них не давал.</t>
+          <t>«Верный» с октября 2025 ищут покупателя (оценка 25–35 млрд — цена всего бизнеса). «Гулливер» в начале 2026 писали как выставленный на продажу. Про «Мария-Ра» летом 2026 писали, что смотрит «Лента». Цифры выручки на 2026 никто из них не давал.</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -42,6 +42,11 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <sz val="11"/>
     </font>
     <font>
@@ -54,11 +59,6 @@
       <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -106,24 +106,30 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -417,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="6" min="1" max="1"/>
@@ -471,36 +477,48 @@
     <row r="9" ht="64" customHeight="1" s="6">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Чего в ячейках нет</t>
+          <t>Что в столбцах «прибыль» и «маржа»</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных» (в таблице «н/д»). Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей +9–11%, производители еды около нуля, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
+          <t>Прибыль — сколько денег осталось после всех расходов за тот же кусок года, что и в столбце «факт». Маржа — какая это доля от продаж: 2% значит две копейки прибыли с каждого рубля. Цифры есть только там, где компания сама опубликовала и прибыль, и продажи за один период: шесть сетей и четыре завода. Исключение — X5: продажи уже за девять месяцев, прибыль пока только за январь–июнь. У остальных в этих столбцах «нет данных».</t>
         </is>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" s="6">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Были ли прогнозы в конце 2025 / начале 2026</t>
+          <t>Чего в ячейках нет</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Свои в рублях — почти ни у кого из тех, у кого в таблице «нет данных». X5 ещё в марте держала +12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «новые заводы начнут себя окупать», без суммы. У сетей из регионов вместо прогноза продаж были новости про продажу самой сети. Мировые PepsiCo и Nestlé дают прогноз на весь мир, не на Россию.</t>
+          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных». Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей +9–11%, производители еды около нуля, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="64" customHeight="1" s="6">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>Были ли прогнозы в конце 2025 / начале 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Свои в рублях — почти ни у кого из тех, у кого в таблице «нет данных». X5 ещё в марте держала +12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «новые заводы начнут себя окупать», без суммы. У сетей из регионов вместо прогноза продаж были новости про продажу самой сети. Мировые PepsiCo и Nestlé дают прогноз на весь мир, не на Россию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1" s="6">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
           <t>Формат файла</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Списки те же: сети и производители в том же порядке. Добавлен только этот лист и обновлён «Медиа».</t>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Списки те же: сети и производители в том же порядке. К выручке добавлены прибыль и маржа, плюс этот лист и обновлённый «Медиа».</t>
         </is>
       </c>
     </row>
@@ -515,7 +533,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="23.25" customWidth="1" style="6" min="1" max="1"/>
@@ -525,52 +543,64 @@
     <col width="12" customWidth="1" style="6" min="5" max="5"/>
     <col width="18" customWidth="1" style="6" min="6" max="6"/>
     <col width="14" customWidth="1" style="6" min="7" max="7"/>
-    <col width="78" customWidth="1" style="6" min="8" max="8"/>
+    <col width="16" customWidth="1" style="6" min="8" max="8"/>
+    <col width="12" customWidth="1" style="6" min="9" max="9"/>
+    <col width="78" customWidth="1" style="6" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="6">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="6">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Компания</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Тип / формат</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Выручка 2026 факт, млрд ₽</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>За какой кусок года</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Рост к тому же куску 2025, %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Оценка / прогноз на весь 2026, млрд ₽</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Магазины / заводы, шт</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Прибыль за тот же кусок, млрд ₽</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Маржа, %</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Откуда цифра, простыми словами</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" s="6">
+    <row r="2" ht="98" customHeight="1" s="6">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>X5 Group (Пятёрочка, Перекрёсток, Чижик)</t>
@@ -600,13 +630,19 @@
       <c r="G2" s="3" t="n">
         <v>30981</v>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>Сама компания 16 октября 2026, цифры ещё без проверки аудитора. За январь–сентябрь продали на 3 791,5 млрд рублей — на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь: 1 311 млрд (+13%). Пятёрочка за девять месяцев 2 918 (+9,4%), Перекрёсток 413 (+7,1%), Чижик 391 (+31,4%), доставка X5 — 257 (+28,4%). Магазинов 30 981 на конец сентября. Свой прогноз на весь год компания не снимала: рост 12–16%. От выручки 2025 (4 642) это 5 200–5 385. https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1" s="6">
+      <c r="H2" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Сама компания 16 октября 2026, цифры ещё без проверки аудитора. За январь–сентябрь продали на 3 791,5 млрд рублей — на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь: 1 311 млрд (+13%). Пятёрочка за девять месяцев 2 918 (+9,4%), Перекрёсток 413 (+7,1%), Чижик 391 (+31,4%), доставка X5 — 257 (+28,4%). Магазинов 30 981 на конец сентября. Прибыль в таблице — 25,7 млрд, но это не за девять месяцев, а только за январь–июнь. За девять месяцев прибыль ещё не вышла (ждут 29 октября). Маржа 1% — это 25,7 от продаж за те же январь–июнь (2 481 млрд). От 3 792 за девять месяцев считать нельзя: куски года разные. Свой прогноз на весь год компания не снимала: рост 12–16%. От выручки 2025 (4 642) это 5 200–5 385. https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="87" customHeight="1" s="6">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Магнит (вкл. Дикси, Самбери, Азбука вкуса)</t>
@@ -634,13 +670,19 @@
       <c r="G3" s="3" t="n">
         <v>33652</v>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт 28 августа 2026: за полгода продали на 1 887,2 млрд рублей (+12,8%). Из них магазины 1 871. Точек 33 652. Долги минус деньги на счетах ≈ 514,5 млрд. По прибыли группа всё ещё в минусе (около −9,5) — мешают проценты по кредитам. Оценка всего года, если второе полугодие будет как первое: 3 509 × 1,128. Это не отчёт за год. https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1" s="6">
+      <c r="H3" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт 28 августа 2026: за полгода продали на 1 887,2 млрд рублей (+12,8%). Из них магазины 1 871. Точек 33 652. Долги минус деньги на счетах ≈ 514,5 млрд. Прибыль за те же январь–июнь в ячейке −1,9 млрд: сеть пока в минусе, мешают проценты по кредитам. Есть второй счёт того же минуса — около −9,5: там аренду магазинов считают как долг. В ячейке стоит −1,9, без этого правила. Оценка всего года, если второе полугодие будет как первое: 3 509 × 1,128. Это не отчёт за год. https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="61" customHeight="1" s="6">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Mercury Retail (Красное &amp; Белое, Бристоль)</t>
@@ -670,13 +712,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine в «Коммерсанте» 2 сентября 2026: за полгода 878 млрд (+11,2%). Своего сводного отчёта всей группы нет. Оценка года, если темп удержится: 1 660 × 1,112. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" s="6">
+    <row r="5" ht="88" customHeight="1" s="6">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Группа Лента (Гипер/Супер Лента, Монетка, Улыбка радуги, Реми)</t>
@@ -704,13 +756,19 @@
       <c r="G5" s="3" t="n">
         <v>7456</v>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт: за полгода 648,5 млрд (+26,2%); апрель–июнь 341,6 (+28,8%). Магазинов 7 456 на 30 июня. Быстрее всех внутри группы — «Супер Лента» (+30,2%) и «Монетка» (+26,1%), большие магазины +12,9%. В августе купила большие магазины «О’КЕЙ» — с осени в цифрах будут ещё и чужие точки. Оценка года без этой покупки: 1 104 × 1,262. К 2028 сама Лента хочет 2,2 триллиона — это цель на потом, не на 2026. https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" s="6">
+      <c r="H5" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт: за полгода 648,5 млрд (+26,2%); апрель–июнь 341,6 (+28,8%). Магазинов 7 456 на 30 июня. Быстрее всех внутри группы — «Супер Лента» (+30,2%) и «Монетка» (+26,1%), большие магазины +12,9%. Прибыль за те же полгода 13 млрд — примерно 2 копейки с каждого рубля продаж. В августе купила большие магазины «О’КЕЙ» — с осени в цифрах будут ещё и чужие точки. Оценка года без этой покупки: 1 104 × 1,262. К 2028 сама Лента хочет 2,2 триллиона — это цель на потом, не на 2026. https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57" customHeight="1" s="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Светофор / Маяк (ГК Торгсервис)</t>
@@ -740,13 +798,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine / «Коммерсантъ»: за полгода 189 млрд — на 4,5% меньше, чем годом раньше. Оценка года: 394 × 0,955. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" s="6">
+    <row r="7" ht="59" customHeight="1" s="6">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ВкусВилл</t>
@@ -776,13 +844,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine / «Коммерсантъ»: за полгода 191,06 млрд (+7,8%). Обогнал «Светофор» среди пяти крупнейших. Оценка года: 359 × 1,078. https://www.infoline.spb.ru/news/?news=308855</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" s="6">
+    <row r="8" ht="73" customHeight="1" s="6">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Fix Price</t>
@@ -810,13 +888,19 @@
       <c r="G8" s="3" t="n">
         <v>8077</v>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт 27 августа 2026: за полгода 155,3 млрд (+4,8%); апрель–июнь 82,2 (+6,9%). Магазины 138,2, опт 17,1. Точек 8 077. Оценка года: 313 × 1,048. https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" s="6">
+      <c r="H8" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт 27 августа 2026: за полгода 155,3 млрд (+4,8%); апрель–июнь 82,2 (+6,9%). Магазины 138,2, опт 17,1. Точек 8 077. Прибыль за те же полгода 2,7 млрд — это 1,8% от продаж (почти 2 копейки с рубля). Оценка года: 313 × 1,048. https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1" s="6">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Самокат</t>
@@ -846,13 +930,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>Оценка агентства INFOLine / «Коммерсантъ»: за полгода 135 млрд (+15,5%). Оценка года: 279 × 1,155. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" s="6">
+    <row r="10" ht="56" customHeight="1" s="6">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>METRO Россия</t>
@@ -882,13 +976,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine / «Коммерсантъ»: за полгода 118,9 млрд (+0,5%). Оценка года: 260 × 1,005. https://www.kommersant.ru/doc/8923610</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" s="6">
+    <row r="11" ht="57" customHeight="1" s="6">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>АШАН Ритейл Россия</t>
@@ -918,13 +1022,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine / «Коммерсантъ»: за полгода 127 млрд — на 2,5% меньше, чем годом раньше. Оценка года: 250 × 0,975. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" s="6">
+    <row r="12" ht="80" customHeight="1" s="6">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ozon + Ozon Fresh</t>
@@ -960,13 +1074,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>Сколько именно продуктов продал Ozon Fresh в 2026, компания не говорит — ни факта, ни своего прогноза. Что было в начале года: агентство Data Insight в январе ждало, что вся доставка продуктов в России за 2026 год будет около 1,8 триллиона рублей (+24% к 2025). К марту уточнили 1,83 триллиона (+22%), к маю 1,84. Это весь рынок доставки, не цифра Ozon. За апрель–июнь пять сервисов (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) вместе сделали 260 млрд; заказы Ozon Fresh +65%. https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" s="6">
+    <row r="13" ht="72" customHeight="1" s="6">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Яндекс Лавка</t>
@@ -1002,13 +1126,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>Выручку Лавки отдельно не публикуют, своего прогноза по ней тоже не было. Весь интернет-блок Яндекса (Лавка + Маркет + Еда + Деливери) за полгода 247 млрд (+19%) — туда входят не только продукты. Заказов у Лавки за апрель–июнь +5%. Прогноз агентства Data Insight на 2026 — вся доставка продуктов в стране 1,83–1,84 триллиона. Это не цифра Лавки. https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1" s="6">
+    <row r="14" ht="72" customHeight="1" s="6">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>ГК О'КЕЙ / Да!</t>
@@ -1036,13 +1170,19 @@
       <c r="G14" s="3" t="n">
         <v>236</v>
       </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>Большие магазины «О’КЕЙ» в конце 2025 продали. У оставшейся компании на бирже теперь только «ДА!»: за полгода 43,3 млрд (+10,4%), 236 магазинов. Оценка года именно «ДА!»: 80 × 1,104. Большие магазины ООО «О’КЕЙ» за полгода 68,2 (−5,6%) — это уже Лента, с «ДА!» не складывать. https://okeygroup.lu/upload/IFRS%201H2026_RUS_final_.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1" s="6">
+      <c r="H14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Большие магазины «О’КЕЙ» в конце 2025 продали. У оставшейся компании на бирже теперь только «ДА!»: за полгода 43,3 млрд (+10,4%), 236 магазинов. Прибыль только «ДА!» за те же полгода 1,2 млрд — 2,8% от продаж. Оценка года именно «ДА!»: 80 × 1,104. Большие магазины ООО «О’КЕЙ» за полгода 68,2 (−5,6%) — это уже Лента, с «ДА!» не складывать. https://okeygroup.lu/upload/IFRS%201H2026_RUS_final_.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1" s="6">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ТС Победа / Гулливер / Народный амбар (ТК Лето)</t>
@@ -1078,13 +1218,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не было. В начале 2026 про «Гулливер» из той же группы писали: сеть выставлена на продажу. Аналитик Совкомбанка: независимые сети, которые в 2025 продали больше чем на 100 млрд (Победа, Командор, Ярче, Аникс), в ближайшие 2–3 года могут сменить хозяина. Это не цифра выручки. Последнее открытое: 176 млрд за 2025. https://www.kommersant.ru/doc/8364093</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1" s="6">
+    <row r="16" ht="65" customHeight="1" s="6">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Ярче! (Камелот-А, Томск)</t>
@@ -1120,13 +1270,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. В обзорах конца 2025 и 2026 сеть называют как возможную покупку для крупного игрока — не как компанию со своим прогнозом. Последнее открытое: 168 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1" s="6">
+    <row r="17" ht="70" customHeight="1" s="6">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Гиперглобус (Globus)</t>
@@ -1154,13 +1314,23 @@
       <c r="G17" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine / «Коммерсантъ»: за полгода 80,6 млрд без налога (+2,7%). В тех же магазинах, что были год назад, продажи +5,7%, средний чек +7,5%. Своего прогноза выручки на 2026 нет. Новый большой магазин планируют на 2027 (больше 4 млрд на стройку) — это не цифра продаж на этот год. Оценка года: 165,6 × 1,027. https://www.kommersant.ru/doc/9005166</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1" s="6">
+    <row r="18" ht="66" customHeight="1" s="6">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Верный (Союз Святого Иоанна Воина)</t>
@@ -1196,13 +1366,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. В октябре 2025 основатель искал покупателя: сеть оценивали в 25–35 млрд рублей. Это цена всего бизнеса, если его продадут, а не «сколько продадут за год». Российский отчёт за 2025 вышел 1 апреля 2026: 154,4 млрд — это прошлый год. https://www.kommersant.ru/doc/8158706</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1" s="6">
+    <row r="19" ht="62" customHeight="1" s="6">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SPAR Миддл Волга (SPAR, EUROSPAR)</t>
@@ -1232,13 +1412,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>Агентство INFOLine / «Коммерсантъ»: «Спар Миддл Волга, Smart» за полгода 103,57 млрд (+7,8%). Тут шире, чем строка 2025 (тогда только SPAR Миддл Волга — 136 за год). Грубая оценка года: 136 × 1,078. https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" s="6">
+    <row r="20" ht="68" customHeight="1" s="6">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Мария-Ра (Розница К-1)</t>
@@ -1272,13 +1462,23 @@
       <c r="G20" s="3" t="n">
         <v>1303</v>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. Последнее: российский отчёт за 2025 — 127,5 млрд (+5%). На 1 июля 2026 — 1 303 магазина (это штуки, не деньги). Летом 2026 писали, что «Лента» смотрит покупку — сделка не подтверждена и цифры года не даёт. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1" s="6">
+    <row r="21" ht="59" customHeight="1" s="6">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Ермолино (оценка INFOLine, производство + своя розница)</t>
@@ -1314,13 +1514,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза на 2026 нет. Агентство INFOLine считает оценку только когда год уже закрыт. Последнее: около 111 млрд за 2025 (оценка агентства, не официальный отчёт компании).</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1" s="6">
+    <row r="22" ht="62" customHeight="1" s="6">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>ГК Командор (Командор, Аллея, Хороший)</t>
@@ -1356,13 +1566,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. В списках возможных покупок 2026–2028 (Совкомбанк) — без суммы продаж. Последнее открытое: около 100 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1" s="6">
+    <row r="23" ht="78" customHeight="1" s="6">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Винлаб (ПАО ВинЛаб / Novabev)</t>
@@ -1390,9 +1610,15 @@
       <c r="G23" s="3" t="n">
         <v>2222</v>
       </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт 24 августа 2026: за полгода 51,2 млрд (+7,2%), прибыль 0,8, точек 2 225 на 30 июня (2 222 на 30 сентября). Оценка года, если темп полугодия удержится: 95,1 × 1,072. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это не та выручка, что в таблице. https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
+      <c r="H23" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт 24 августа 2026: за полгода 51,2 млрд (+7,2%), прибыль 0,79 млрд (1,5% от продаж — полторы копейки с рубля), точек 2 225 на 30 июня (2 222 на 30 сентября). Оценка года, если темп полугодия удержится: 95,1 × 1,072. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это не та выручка, что в таблице. https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1658,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1474,7 +1710,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1516,7 +1762,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1558,7 +1814,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1600,13 +1866,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1" s="6">
+    <row r="29" ht="63" customHeight="1" s="6">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Аникс (ТС Аникс + Прайд-А)</t>
@@ -1642,7 +1918,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>Прогноза на 2026 нет. Упоминается рядом с «Победой», «Ярче» и «Командором» как сеть, которую крупный игрок может купить. Последнее: 31,3 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
@@ -1684,7 +1970,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1726,7 +2022,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1768,7 +2074,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1810,7 +2126,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1852,7 +2178,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1894,7 +2230,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1936,7 +2282,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -1978,7 +2334,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -2020,7 +2386,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -2062,7 +2438,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -2104,7 +2490,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
         </is>
@@ -2122,7 +2518,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="17.75" customWidth="1" style="6" min="1" max="1"/>
@@ -2132,52 +2528,64 @@
     <col width="12" customWidth="1" style="6" min="5" max="5"/>
     <col width="18" customWidth="1" style="6" min="6" max="6"/>
     <col width="14" customWidth="1" style="6" min="7" max="7"/>
-    <col width="78" customWidth="1" style="6" min="8" max="8"/>
+    <col width="16" customWidth="1" style="6" min="8" max="8"/>
+    <col width="12" customWidth="1" style="6" min="9" max="9"/>
+    <col width="78" customWidth="1" style="6" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="6">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="6">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Компания</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Тип / формат</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Выручка 2026 факт, млрд ₽</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>За какой кусок года</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Рост к тому же куску 2025, %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Оценка / прогноз на весь 2026, млрд ₽</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Магазины / заводы, шт</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Прибыль за тот же кусок, млрд ₽</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Маржа, %</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Откуда цифра, простыми словами</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" s="6">
+    <row r="2" ht="62" customHeight="1" s="6">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PepsiCo Россия (вкл. Вимм-Билль-Данн)</t>
@@ -2213,13 +2621,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Прогноза именно по России в рублях нет: с 2022 мировая PepsiCo российские планы не публикует. В декабре 2025 и весной 2026 мировой прогноз: рост продаж на 2–4% — это весь мир, не «PepsiCo Россия». https://www.interfax.ru/business/1070847</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1" s="6">
+    <row r="3" ht="72" customHeight="1" s="6">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Русагро</t>
@@ -2249,13 +2667,19 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт: за полгода 183,0 млрд (+9,1%). У растениеводства и сахара осень обычно сильнее весны, поэтому полугодие на два не умножали. Оценка года, если темп удержится: 396,5 × 1,091. https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1" s="6">
+      <c r="H3" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт: за полгода 183,0 млрд (+9,1%). Прибыль почти ноль: 56 миллионов рублей, это 0,056 млрд — меньше одной десятой копейки с рубля продаж. У растениеводства и сахара осень обычно сильнее весны, поэтому полугодие на два не умножали. Оценка года, если темп удержится: 396,5 × 1,091. https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="63" customHeight="1" s="6">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ЭФКО</t>
@@ -2291,13 +2715,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>Цифры на 2026 нет. На 2025 сами планировали 440 млрд — не получилось (факт 344, рост ноль). Весной 2026 руководство: новые заводы начнут себя окупать в 2026–2027, ждут рост продаж и прибыли — без конкретной суммы. https://abireg.ru/newsitem/113897/</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" s="6">
+    <row r="5" ht="76" customHeight="1" s="6">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>АПХ Мираторг</t>
@@ -2331,13 +2765,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>Полной выручки за январь–июнь 2026 в открытом виде нет. Глава компании Виктор Линник в июне на Петербургском экономическом форуме: ждать рост продаж «на несколько процентов»; продажи за границу удержать около 58 млрд, как в 2025 (план +20% сняли — рубль слишком крепкий). Оценка года ≈ 342 × 1,03. Прибыль за полгода 19,61 млрд (+26%) — это не выручка. https://echomsk.spb.ru/nws/5317198-miratorg-ogidaet-neznachitelnyj-rost-vyruchki-po-itogam-2026-goda.html</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" s="6">
+    <row r="6" ht="65" customHeight="1" s="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>KDV Group</t>
@@ -2373,13 +2817,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>Прогноза на 2026 нет. Агентство INFOLine берёт KDV как пример торможения: уже 2025 только +1%, а в 2026 у крупных производителей еды рост «около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" s="6">
+    <row r="7" ht="77" customHeight="1" s="6">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Черкизово</t>
@@ -2409,13 +2863,19 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт: за полгода 141,6 млрд (+3,5%). Свой прогноз в рублях на год компания не давала — только «продолжим увеличивать выручку», деньги на стройки в 2026 снова режут. Независимая оценка на сайте для инвесторов: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" s="6">
+      <c r="H7" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт: за полгода 141,6 млрд (+3,5%). Прибыль за те же полгода 14,1 млрд — почти 10 копеек с каждого рубля продаж. Свой прогноз в рублях на год компания не давала — только «продолжим увеличивать выручку», деньги на стройки в 2026 снова режут. Независимая оценка на сайте для инвесторов: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="71" customHeight="1" s="6">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ГАП Ресурс</t>
@@ -2451,13 +2911,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>Прогноза в рублях на 2026 нет. В июне 2025 на Петербургском экономическом форуме: за три года вложат больше 40 млрд в новые птичники, добавка по мясу — в 2027. На 2025 обещали удержать выпуск около 1 070 тысяч тонн — вышло 1 054. Это тонны, не деньги 2026. https://www.agroinvestor.ru/investments/news/44400-gap-resurs-vlozhit-40-mlrd-rubley-v-rasshirenie-proizvodstva/</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" s="6">
+    <row r="9" ht="62" customHeight="1" s="6">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Nestlé Россия</t>
@@ -2493,13 +2963,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>Выручки и прогноза по России на 2026 нет. Оценка аналитиков по всей мировой Nestlé: рост продаж около 3,5–3,7% за год — не российская цифра. https://www.nestle.com/sites/default/files/2026-10/nestle-sa-consensus-pre-Q32026.pdf</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" s="6">
+    <row r="10" ht="51" customHeight="1" s="6">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Mars Россия</t>
@@ -2535,13 +3015,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза выручки по России на 2026 не публиковали.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" s="6">
+    <row r="11" ht="57" customHeight="1" s="6">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Продимекс (сумма предприятий группы)</t>
@@ -2577,13 +3067,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 не было. Открытое — сумма заводов за 2025 (около 220–224 млрд, считают по-разному). Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" s="6">
+    <row r="12" ht="57" customHeight="1" s="6">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Агропромкомплектация</t>
@@ -2619,13 +3119,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>Прогноза всей группы на 2026 нет. Агентство INFOLine за 2025: 204,4 млрд (+15%). Отдельные компании группы (АПК-Курск и другие) отчитываются раз в год.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" s="6">
+    <row r="13" ht="71" customHeight="1" s="6">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Логика молока (ex-Danone / Health&amp;Nutrition)</t>
@@ -2653,13 +3163,23 @@
       <c r="G13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>Сама компания 16 июля 2026: за полгода продали на 84,5 млрд (+3,5%), молочки 510 тысяч тонн (+2,7%). Ориентир на год — не деньги, а «сделать больше 1 миллиона тонн готовой продукции». На стройки и оборудование до 2030 заложили 120 млрд. Оценка рублей на год: 167,1 × 1,035. https://logikamoloka.ru/press-centr/news/logika-moloka-podvodit-rezultaty-i-polugodiya-2026-goda/</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1" s="6">
+    <row r="14" ht="65" customHeight="1" s="6">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Напитки вместе (ex-AB InBev Efes)</t>
@@ -2695,13 +3215,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>Выручки 2026 нет. План без суммы: пиво — больше 30% рынка, напитки без алкоголя — больше 8% продаж за первое полугодие, 700 миллионов в завод в Саранске в 2026. https://napitkivmeste.ru/odin-god-pod-brendom-napitki-vmeste-bolee-30-novyh-produktov-i-rekordnye-vlozheniya-v-zavody/</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" s="6">
+    <row r="15" ht="60" customHeight="1" s="6">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Балтика (ООО ПК Балтика)</t>
@@ -2737,13 +3267,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. В 2025 выпуск пива упал на 16% — компания сама сказала, что так и задумала: обновляли заводы. Это про прошлый год, не про 2026. https://www.kommersant.ru/doc/8401281</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1" s="6">
+    <row r="16" ht="68" customHeight="1" s="6">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Сибагро (совокупность компаний группы)</t>
@@ -2779,13 +3319,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. После убытка 2025 (около 4,2 млрд) группа сама сказала: новые большие стройки пока не начинаем, сначала надо выйти в плюс; точечно около 500 миллионов в Томскую птицефабрику. https://www.akm.ru/news/gruppa_kompaniy_sibagro_narastila_vyruchku_na_14_odnako_zakonchila_2025_god_s_chistym_ubytkom/</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1" s="6">
+    <row r="17" ht="59" customHeight="1" s="6">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Объединённые кондитеры (ООО, дистрибуция группы)</t>
@@ -2821,13 +3371,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>Прогноза на 2026 нет. В конце 2025 ходили слухи, что группу продадут — владельцы («Гута») опровергли. Последнее открытое: около 113 млрд за 2025. https://www.kommersant.ru/doc/8339681</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1" s="6">
+    <row r="18" ht="54" customHeight="1" s="6">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>АБИ (ABI Product)</t>
@@ -2863,13 +3423,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза выручки на 2026 не публиковали. Последнее: около 88 млрд за 2025 (агентство INFOLine).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1" s="6">
+    <row r="19" ht="61" customHeight="1" s="6">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Дамате</t>
@@ -2899,13 +3469,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>Пресс-служба 7 сентября 2026: за полгода 46,3 млрд (+19%). Оценка года: 82,8 × 1,19. https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" s="6">
+    <row r="20" ht="59" customHeight="1" s="6">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Комос Групп (молочный контур рейтинга)</t>
@@ -2941,13 +3521,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. Агентство INFOLine отмечает группу среди быстрорастущих молочников 2025, без цифры на этот год. Последнее: только молочная часть 63,1 млрд за 2025.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1" s="6">
+    <row r="21" ht="52" customHeight="1" s="6">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Орими Трейд (Tess, Greenfield, Jardin)</t>
@@ -2983,7 +3573,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза по России на 2026 не публиковали. Последнее: 62,3 млрд за 2025.</t>
         </is>
@@ -3025,7 +3625,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3067,13 +3677,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1" s="6">
+    <row r="24" ht="68" customHeight="1" s="6">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Агроэко</t>
@@ -3103,13 +3723,19 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт за полгода: 24,63 млрд — на 6,4% меньше, чем 26,31 годом раньше. Прибыль 1,99 (−40%). Оценка года: 56,4 × 0,936. Свинины в тоннах сделали на 10% больше, но она подешевела. https://www.tbank.ru/invest/social/profile/Marten_Resting/cbc77ff8-2a7f-49ae-8534-59a60c86da65/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1" s="6">
+      <c r="H24" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт за полгода: 24,63 млрд — на 6,4% меньше, чем 26,31 годом раньше. Прибыль 1,99 млрд (−40% к прошлому году) — это 8,1% от продаж. Оценка года: 56,4 × 0,936. Свинины в тоннах сделали на 10% больше, но она подешевела. https://www.tbank.ru/invest/social/profile/Marten_Resting/cbc77ff8-2a7f-49ae-8534-59a60c86da65/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1" s="6">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Прогресс (ФрутоНяня / Малышам)</t>
@@ -3145,13 +3771,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>Прогноза на 2026 нет. В марте 2026 вышел отчёт за 2025: выручка 52,1 (+8%), прибыль 10,2. https://www.kommersant.ru/doc/8552221</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1" s="6">
+    <row r="26" ht="63" customHeight="1" s="6">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>ГК Молвест</t>
@@ -3187,13 +3823,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. Июль 2026: до 2028 вложат около 13 млрд в новые линии (белки из молока и другие ингредиенты) — это деньги на стройку, не «сколько продадут за год». https://milknews.ru/index/molochnye-produkty/molvest-13-mlrd-investicii.html</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1" s="6">
+    <row r="27" ht="56" customHeight="1" s="6">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Эссен Продакшн (Махеевъ)</t>
@@ -3229,7 +3875,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>Прогноза выручки на 2026 нет. У кондитеров в целом дорогое какао и упаковка — без цифры именно этой компании. Последнее: 50,2 млрд за 2025.</t>
         </is>
@@ -3271,13 +3927,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1" s="6">
+    <row r="29" ht="65" customHeight="1" s="6">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Сады Придонья</t>
@@ -3313,7 +3979,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>Выручку 2026 в деньгах не публиковали. За январь–март продали на 7,5% больше в тоннах, бренды «Сады Придонья» +11%, Nemoloko +19%. Прогноза в рублях на год нет. https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
         </is>
@@ -3355,7 +4031,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3397,7 +4083,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3439,7 +4135,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3481,13 +4187,23 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1" s="6">
+    <row r="34" ht="67" customHeight="1" s="6">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>ГК ЭкоНива (молочный контур рейтинга)</t>
@@ -3519,9 +4235,15 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
-        <is>
-          <t>Официальный отчёт всей группы за полгода: 45,2 млрд (−2,8%), прибыль 1,1. Это ВСЯ компания, а не только молочная часть, которую агентство INFOLine считало за 2025 (29,8). С 29,8 сравнивать нельзя. Оценку года только для молочки не ставили. https://abireg.ru/newsitem/116916/</t>
+      <c r="H34" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>Официальный отчёт всей группы за полгода: 45,2 млрд (−2,8%), прибыль 1,1 млрд — 2,4% от продаж всей группы. Это ВСЯ компания, а не только молочная часть, которую агентство INFOLine считало за 2025 (29,8). С 29,8 сравнивать нельзя. Оценку года только для молочки не ставили. https://abireg.ru/newsitem/116916/</t>
         </is>
       </c>
     </row>
@@ -3561,7 +4283,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3603,7 +4335,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3645,7 +4387,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3687,7 +4439,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3729,7 +4491,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3771,7 +4543,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3813,7 +4595,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3855,7 +4647,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3897,7 +4699,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3939,7 +4751,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -3981,7 +4803,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4023,7 +4855,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4065,7 +4907,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4107,7 +4959,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4149,7 +5011,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4191,7 +5063,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4233,7 +5115,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4275,7 +5167,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J52" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4317,7 +5219,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4359,7 +5271,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J54" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4401,7 +5323,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J55" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4443,7 +5375,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J56" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4485,7 +5427,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J57" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4527,7 +5479,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J58" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4569,7 +5531,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J59" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4611,7 +5583,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4653,7 +5635,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4695,7 +5687,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4737,7 +5739,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4779,7 +5791,17 @@
           <t>нет данных</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J64" s="13" t="inlineStr">
         <is>
           <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
         </is>
@@ -4796,7 +5818,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -4826,17 +5848,17 @@
       <c r="G1" s="4" t="n"/>
     </row>
     <row r="2" ht="72" customHeight="1" s="6">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Как читать цифру 2026</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Года ещё нет (сейчас октябрь 2026), полного отчёта за весь 2026 ни у кого нет. В столбце «факт» — уже опубликованный кусок: девять месяцев, полгода или квартал. «Оценка года» — не отчёт, а арифметика: либо прогноз самой компании, либо выручка 2025, умноженная на рост уже вышедшего куска 2026. Где куска нет — «нет данных», ничего не додумано.</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Года ещё нет (сейчас октябрь 2026), полного отчёта за весь 2026 ни у кого нет. В столбце «факт» — уже опубликованный кусок: девять месяцев, полгода или квартал. «Оценка года» — не отчёт, а арифметика: либо прогноз самой компании, либо выручка 2025, умноженная на рост уже вышедшего куска 2026. Где куска нет — «нет данных», ничего не додумано. Прибыль и маржа стоят только там, где компания сама их опубликовала за тот же кусок года.</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>https://www.x5.ru/ru/investors/financial-and-operational-results/</t>
         </is>
@@ -4847,17 +5869,17 @@
       <c r="G2" s="3" t="n"/>
     </row>
     <row r="3" ht="72" customHeight="1" s="6">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>X5 — январь–сентябрь</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Продали за январь–сентябрь на 3,79 триллиона рублей, на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь быстрее полугодия: +13% до 1,31 триллиона. Чижик по-прежнему самый быстрый внутри группы (+31% за девять месяцев, +35% за квартал). Компания свой прогноз на весь год не снимала: +12–16%.</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
         </is>
@@ -4868,17 +5890,17 @@
       <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="72" customHeight="1" s="6">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>X5 — свой прогноз на год</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>В марте и снова в июне президент Екатерина Лобачева: прогноз роста выручки 12–16% на 2026 держим. От выручки 2025 (4,642 триллиона) это примерно 5,20–5,39 триллиона за полный год. Девять месяцев идут ближе к нижней границе.</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>https://www.x5.ru/ru/news/x5-predstavila-prognozy-i-orientiry-na-2026-god/</t>
         </is>
@@ -4889,17 +5911,17 @@
       <c r="G4" s="3" t="n"/>
     </row>
     <row r="5" ht="72" customHeight="1" s="6">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Магнит — полгода</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1 887 млрд рублей за полгода, +12,8%. Магазины работают, продажи растут, по прибыли группа всё ещё в минусе: мешают проценты по кредитам. Это тот же сюжет, что в 2025: полка живая, кредиты тяжёлые.</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>1 887 млрд рублей за полгода, +12,8%. Магазины работают, продажи растут, по прибыли группа всё ещё в минусе: −1,9 млрд (без правила «аренда как долг»). Если аренду магазинов считать долгом, минус около −9,5. Мешают проценты по кредитам. Это тот же сюжет, что в 2025: полка живая, кредиты тяжёлые.</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
         </is>
@@ -4910,19 +5932,19 @@
       <c r="G5" s="3" t="n"/>
     </row>
     <row r="6" ht="72" customHeight="1" s="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Десять крупнейших сетей, январь–июнь 2026</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Агентство INFOLine сложила десятку: 6,76 триллиона рублей, +11,6% (годом раньше десятка росла на 17%). Лента +26% — самый быстрый из крупных. Светофор и Ашан продали меньше, чем год назад. На весь 2026 агентство ждёт рост крупнейших сетей примерно 9–11%.</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>https://www.kommersant.ru/doc/8923592</t>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Прибыль и маржа — у кого уже есть</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Официальную прибыль за январь–июнь 2026 опубликовали шесть сетей и четыре завода. Сети: X5 25,7 млрд (маржа 1% — от продаж за январь–июнь 2 481, не от девяти месяцев), Магнит −1,9, Лента 13 (2%), Fix Price 2,7 (1,8%), «ДА!» 1,2 (2,8%), Винлаб 0,79 (1,5%). Заводы: Черкизово 14,1 (почти 10 копеек с рубля), Русагро почти ноль (0,056), Агроэко 1,99 (8,1%), ЭкоНива 1,1 (2,4% от всей группы). У остальных в этих столбцах «нет данных»: отчёта с прибылью за 2026 ещё нет. Мираторг писал прибыль 19,61 без полной выручки — в ячейку не ставили, маржу от этого не посчитать.</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>https://www.x5.ru/ru/investors/financial-and-operational-results/</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
@@ -4931,19 +5953,19 @@
       <c r="G6" s="3" t="n"/>
     </row>
     <row r="7" ht="72" customHeight="1" s="6">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Лента — полгода</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>648 млрд рублей за полгода, +26%. Тянут «Супер Лента» и «Монетка». В августе купила большие магазины «О’КЕЙ» — со второго полугодия в цифрах будут ещё и эти магазины.</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Десять крупнейших сетей, январь–июнь 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Агентство INFOLine сложила десятку: 6,76 триллиона рублей, +11,6% (годом раньше десятка росла на 17%). Лента +26% — самый быстрый из крупных. Светофор и Ашан продали меньше, чем год назад. На весь 2026 агентство ждёт рост крупнейших сетей примерно 9–11%.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -4952,19 +5974,19 @@
       <c r="G7" s="3" t="n"/>
     </row>
     <row r="8" ht="72" customHeight="1" s="6">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Fix Price — полгода</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>155 млрд рублей, +4,8%. Медленнее больших продуктовых сетей: цены фиксированные, в ассортименте не только еда.</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Лента — полгода</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>648 млрд рублей за полгода, +26%. Тянут «Супер Лента» и «Монетка». В августе купила большие магазины «О’КЕЙ» — со второго полугодия в цифрах будут ещё и эти магазины.</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -4973,19 +5995,19 @@
       <c r="G8" s="3" t="n"/>
     </row>
     <row r="9" ht="72" customHeight="1" s="6">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Винлаб — полгода</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>51 млрд рублей по официальному отчёту, +7%. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это отскок после кибератаки 2025-го, не путать с выручкой в таблице.</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Fix Price — полгода</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>155 млрд рублей, +4,8%. Медленнее больших продуктовых сетей: цены фиксированные, в ассортименте не только еда.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -4994,19 +6016,19 @@
       <c r="G9" s="3" t="n"/>
     </row>
     <row r="10" ht="72" customHeight="1" s="6">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Русагро — полгода</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>183 млрд рублей, +9%. Догнать PepsiCo по году ещё рано: полного 2026 нет ни у кого из заводов.</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Винлаб — полгода</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>51 млрд рублей по официальному отчёту, +7%. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это отскок после кибератаки 2025-го, не путать с выручкой в таблице.</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -5015,19 +6037,19 @@
       <c r="G10" s="3" t="n"/>
     </row>
     <row r="11" ht="72" customHeight="1" s="6">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Черкизово — полгода</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>142 млрд рублей, всего +3,5%. Слабее роста цен в магазинах: дешевле свинина и меньше продаж в Китай.</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>https://www.interfax.ru/business/1111410</t>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Русагро — полгода</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>183 млрд рублей, +9%. Догнать PepsiCo по году ещё рано: полного 2026 нет ни у кого из заводов.</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -5036,19 +6058,19 @@
       <c r="G11" s="3" t="n"/>
     </row>
     <row r="12" ht="72" customHeight="1" s="6">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Дамате — полгода</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>46 млрд рублей, +19% — один из немногих заводов, у кого продажи выросли сильно.</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Черкизово — полгода</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>142 млрд рублей, всего +3,5%. Слабее роста цен в магазинах: дешевле свинина и меньше продаж в Китай.</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>https://www.interfax.ru/business/1111410</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -5057,19 +6079,19 @@
       <c r="G12" s="3" t="n"/>
     </row>
     <row r="13" ht="72" customHeight="1" s="6">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Мираторг — прогноз, не факт</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Выручку за 2026 пока не раскрыли. Глава группы в июне: ждать роста «на несколько процентов», продажи за границу удержать около 58 млрд рублей.</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>https://news.mail.ru/economics/71212403/</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Дамате — полгода</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>46 млрд рублей, +19% — один из немногих заводов, у кого продажи выросли сильно.</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -5078,19 +6100,19 @@
       <c r="G13" s="3" t="n"/>
     </row>
     <row r="14" ht="72" customHeight="1" s="6">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Что было вместо цифры, если её нет</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>По большинству сетей из регионов и заводов своего прогноза «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год +9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку выручки это не ставили — это не продажи компании.</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Мираторг — прогноз, не факт</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Выручку за 2026 пока не раскрыли. Глава группы в июне: ждать роста «на несколько процентов», продажи за границу удержать около 58 млрд рублей.</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>https://news.mail.ru/economics/71212403/</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -5099,19 +6121,19 @@
       <c r="G14" s="3" t="n"/>
     </row>
     <row r="15" ht="72" customHeight="1" s="6">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Агентство INFOLine — сети на весь 2026</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>https://www.kommersant.ru/doc/8923592</t>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Что было вместо цифры, если её нет</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>По большинству сетей из регионов и заводов своего прогноза «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год +9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку выручки это не ставили — это не продажи компании.</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -5120,19 +6142,19 @@
       <c r="G15" s="3" t="n"/>
     </row>
     <row r="16" ht="72" customHeight="1" s="6">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Агентство INFOLine — заводы</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только +1%.</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Агентство INFOLine — сети на весь 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -5141,19 +6163,19 @@
       <c r="G16" s="3" t="n"/>
     </row>
     <row r="17" ht="72" customHeight="1" s="6">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Доставка продуктов, начало 2026</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (+24%). К марту 1,83 триллиона (+22%), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не выручка одной Лавки или Ozon Fresh.</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>https://datainsight.ru/DI_eGrocery_april_2026</t>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Агентство INFOLine — заводы</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только +1%.</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -5162,25 +6184,46 @@
       <c r="G17" s="3" t="n"/>
     </row>
     <row r="18" ht="72" customHeight="1" s="6">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Сети из регионов — не прогноз продаж, а продажа самой сети</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>«Верный» с октября 2025 ищут покупателя (оценка 25–35 млрд — цена всего бизнеса). «Гулливер» в начале 2026 писали как выставленный на продажу. Про «Мария-Ра» летом 2026 писали, что смотрит «Лента». Цифры выручки на 2026 никто из них не давал.</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>https://www.kommersant.ru/doc/8158706</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Доставка продуктов, начало 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (+24%). К марту 1,83 триллиона (+22%), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не выручка одной Лавки или Ozon Fresh.</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>https://datainsight.ru/DI_eGrocery_april_2026</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="72" customHeight="1" s="6">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Сети из регионов — не прогноз продаж, а продажа самой сети</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>«Верный» с октября 2025 ищут покупателя (оценка 25–35 млрд — цена всего бизнеса). «Гулливер» в начале 2026 писали как выставленный на продажу. Про «Мария-Ра» летом 2026 писали, что смотрит «Лента». Цифры выручки на 2026 никто из них не давал.</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>https://www.kommersant.ru/doc/8158706</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5201,6 +6244,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -6,9 +6,12 @@
     <sheet name="Как читать 2026" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Сети" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Производители" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Медиа" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Регионы" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Медиа" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Регионы'!$A$1:$J$25</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -86,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -131,6 +134,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="6" min="1" max="1"/>
@@ -446,7 +465,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Сегодня 19 октября 2026. Год закроется 31 декабря. Полные годовые отчёты компании обычно публикуют весной 2027. Поэтому в таблице два разных числа: уже вышедший кусок года и, где можно, оценка полного года.</t>
+          <t>Сегодня 29 октября 2026. Год закроется 31 декабря. Полные годовые отчёты компании обычно публикуют весной 2027. Поэтому в таблице два разных числа: уже вышедший кусок года и, где можно, оценка полного года.</t>
         </is>
       </c>
     </row>
@@ -518,7 +537,19 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Списки те же: сети и производители в том же порядке. К выручке добавлены прибыль и маржа, плюс этот лист и обновлённый «Медиа».</t>
+          <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Те же десять колонок на листах «Сети», «Производители» и «Регионы». К выручке добавлены прибыль и маржа, плюс этот лист и обновлённый «Медиа».</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1" s="6">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Лист «Регионы» — зачем и как читать ИТ</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Это сети на 30–200 точек и заводы поменьше. Выручки за кусок 2026 у них почти нет — в столбцах денег стоит «нет данных», чтобы не подменять 2026 закрытым 2025-м. В комментарии два слоя: последний закрытый год (чтобы видеть маржу и прибыль) и что видно на 2026–27 (открывают, склеивают сети, режут издержки, закрывают магазин). Никто из них не публикует «бюджет ИТ в рублях». Сигнал такой: растёт и строит склад / склеивает юрлица после сделки — ИТ скорее не режут; продажи уже падали, убыток, закрывают гипермаркет — скорее заморозка; тонкая маржа и «год эффективности» — ИТ только если окупается на издержках.</t>
         </is>
       </c>
     </row>
@@ -606,31 +637,31 @@
           <t>X5 Group (Пятёрочка, Перекрёсток, Чижик)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>у дома / супер / хард-дискаунтер / e-grocery</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="12" t="n">
         <v>3791.5</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>январь–сентябрь</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="12" t="n">
         <v>11.4</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>5200–5385</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="12" t="n">
         <v>30981</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="12" t="n">
         <v>25.7</v>
       </c>
       <c r="I2" s="12" t="n">
@@ -648,29 +679,29 @@
           <t>Магнит (вкл. Дикси, Самбери, Азбука вкуса)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>у дома / супер / гипер / косметик / e-com</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="12" t="n">
         <v>1887.2</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="12" t="n">
         <v>12.8</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="12" t="n">
         <v>3958</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="12" t="n">
         <v>33652</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="12" t="n">
         <v>-1.9</v>
       </c>
       <c r="I3" s="12" t="n">
@@ -688,31 +719,31 @@
           <t>Mercury Retail (Красное &amp; Белое, Бристоль)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>алкоголь / у дома</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="12" t="n">
         <v>878</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="12" t="n">
         <v>11.2</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="12" t="n">
         <v>1846</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -734,29 +765,29 @@
           <t>Группа Лента (Гипер/Супер Лента, Монетка, Улыбка радуги, Реми)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>гипер / супер / у дома / дрогери</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="12" t="n">
         <v>648.49</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="12" t="n">
         <v>26.2</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="12" t="n">
         <v>1393</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="12" t="n">
         <v>7456</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I5" s="12" t="n">
@@ -774,31 +805,31 @@
           <t>Светофор / Маяк (ГК Торгсервис)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>хард-дискаунтер</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="12" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -820,31 +851,31 @@
           <t>ВкусВилл</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>у дома / dark store / e-grocery</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="12" t="n">
         <v>191.06</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="12" t="n">
         <v>7.8</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="12" t="n">
         <v>387</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -866,29 +897,29 @@
           <t>Fix Price</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>value-ритейл, смешанный FMCG</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="12" t="n">
         <v>155.3</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="12" t="n">
         <v>4.8</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="12" t="n">
         <v>8077</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="12" t="n">
         <v>2.7</v>
       </c>
       <c r="I8" s="12" t="n">
@@ -906,31 +937,31 @@
           <t>Самокат</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>e-grocery / dark store</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -952,31 +983,31 @@
           <t>METRO Россия</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>cash&amp;carry / гипер</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="12" t="n">
         <v>118.9</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -998,31 +1029,31 @@
           <t>АШАН Ритейл Россия</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>гипер / супер</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="12" t="n">
         <v>127.01</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="12" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1044,37 +1075,37 @@
           <t>Ozon + Ozon Fresh</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>e-grocery / маркетплейс</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1096,37 +1127,37 @@
           <t>Яндекс Лавка</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>e-grocery / dark store</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1148,29 +1179,29 @@
           <t>ГК О'КЕЙ / Да!</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>гипер продан / дискаунтер Да!</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="12" t="n">
         <v>43.3</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>январь–июнь, только «ДА!»</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="12" t="n">
         <v>10.4</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="12" t="n">
         <v>1.2</v>
       </c>
       <c r="I14" s="12" t="n">
@@ -1188,37 +1219,37 @@
           <t>ТС Победа / Гулливер / Народный амбар (ТК Лето)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>у дома / супер, Поволжье</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1240,37 +1271,37 @@
           <t>Ярче! (Камелот-А, Томск)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>у дома / супер, Сибирь</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1292,29 +1323,29 @@
           <t>Гиперглобус (Globus)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>гипер</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="12" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="12" t="n">
         <v>2.7</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1336,37 +1367,37 @@
           <t>Верный (Союз Святого Иоанна Воина)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>у дома, ЦФО</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1388,31 +1419,31 @@
           <t>SPAR Миддл Волга (SPAR, EUROSPAR)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>супер / у дома</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="12" t="n">
         <v>103.57</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="12" t="n">
         <v>7.8</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1434,35 +1465,35 @@
           <t>Мария-Ра (Розница К-1)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>у дома / супер, Сибирь</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
         <v>1303</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1484,37 +1515,37 @@
           <t>Ермолино (оценка INFOLine, производство + своя розница)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>у дома / производство+розница</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1536,37 +1567,37 @@
           <t>ГК Командор (Командор, Аллея, Хороший)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>супер / гипер / дискаунтер, Красноярск</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1588,29 +1619,29 @@
           <t>Винлаб (ПАО ВинЛаб / Novabev)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>алкоголь</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="12" t="n">
         <v>51.2</v>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="12" t="n">
         <v>7.2</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="12" t="n">
         <v>2222</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="12" t="n">
         <v>0.79</v>
       </c>
       <c r="I23" s="12" t="n">
@@ -1628,37 +1659,37 @@
           <t>Находка (ООО Табыш)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>хард-дискаунтер, Поволжье</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1680,37 +1711,37 @@
           <t>Семишагофф (ООО ТК Прогресс)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>хард-дискаунтер, СЗФО</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1732,37 +1763,37 @@
           <t>Авокадо (франшиза ГК Сладкая жизнь)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>франчайзи у дома</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1784,37 +1815,37 @@
           <t>Линия (ООО Гипермаркет Линия / Гринн)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>гипер, Черноземье</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1836,37 +1867,37 @@
           <t>Лама (SPAR / Первоцен / F City; сумма 4 юрлиц)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>супер / у дома, Томск–Новосибирск</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1888,37 +1919,37 @@
           <t>Аникс (ТС Аникс + Прайд-А)</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>у дома, Алтай</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1940,37 +1971,37 @@
           <t>Европа (ООО Европа, Курск)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>гипер / супер, Черноземье</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -1992,37 +2023,37 @@
           <t>Бегемаг (ООО Универсамы Бегемаг)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>у дома / SPAR, Кузбасс</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2044,37 +2075,37 @@
           <t>Низкоцен (ООО Холлифуд)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>хард-дискаунтер, Сибирь/Урал</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2096,37 +2127,37 @@
           <t>Победа Омск (ООО Формат; не ТК Лето)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>у дома / дискаунтер, Омск</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2148,37 +2179,37 @@
           <t>Доброцен (одно юрлицо, не вся сеть)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>хард-дискаунтер</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2200,37 +2231,37 @@
           <t>Быстроном (ООО Мегаторг)</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>у дома, Новосибирск</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2252,37 +2283,37 @@
           <t>Бахетле (ООО Бахетле-1, Татарстан)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>супер, Татарстан</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2304,37 +2335,37 @@
           <t>Бахетле Новосибирск (ООО Гастромаркет)</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>супер, Новосибирск</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2356,37 +2387,37 @@
           <t>Макси (юрлицо, Вологда)</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>гипер / супер, СЗФО</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2408,37 +2439,37 @@
           <t>Добрянка (ООО Русская поварня)</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>супер, регионы</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2460,37 +2491,37 @@
           <t>Форне (ООО Форне Кондитер)</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>кондитерская розница, Бийск</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2591,37 +2622,37 @@
           <t>PepsiCo Россия (вкл. Вимм-Билль-Данн)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>напитки / снеки / молочка</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2643,31 +2674,31 @@
           <t>Русагро</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>масложир / сахар / мясо / агро</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="12" t="n">
         <v>9.1</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="n">
         <v>0.056</v>
       </c>
       <c r="I3" s="12" t="n">
@@ -2685,37 +2716,37 @@
           <t>ЭФКО</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>масложир / B2C / экспорт</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2737,35 +2768,35 @@
           <t>АПХ Мираторг</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>мясо / от поля до прилавка</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
         <v>350</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2787,37 +2818,37 @@
           <t>KDV Group</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>кондитерка / снеки</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2839,31 +2870,31 @@
           <t>Черкизово</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>мясо / птица / мясопереработка</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="12" t="n">
         <v>141.6</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="12" t="n">
         <v>3.5</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="12" t="n">
         <v>299</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>14.1</v>
       </c>
       <c r="I7" s="12" t="n">
@@ -2881,37 +2912,37 @@
           <t>ГАП Ресурс</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>птица / мясо</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2933,37 +2964,37 @@
           <t>Nestlé Россия</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>кофе / корма / кулинария</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -2985,37 +3016,37 @@
           <t>Mars Россия</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>корма / кондитерка / еда</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3037,37 +3068,37 @@
           <t>Продимекс (сумма предприятий группы)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>сахар / агро; внутригрупповые обороты возможны</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3089,37 +3120,37 @@
           <t>Агропромкомплектация</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>мясо / молоко / агро</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3141,29 +3172,29 @@
           <t>Логика молока (ex-Danone / Health&amp;Nutrition)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>молочка / детское питание</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="12" t="n">
         <v>84.5</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="12" t="n">
         <v>3.5</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3185,37 +3216,37 @@
           <t>Напитки вместе (ex-AB InBev Efes)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>пиво / безалкогольные</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3237,37 +3268,37 @@
           <t>Балтика (ООО ПК Балтика)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>пиво / вода</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3289,37 +3320,37 @@
           <t>Сибагро (совокупность компаний группы)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>свинина / мясо, Сибирь</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3341,37 +3372,37 @@
           <t>Объединённые кондитеры (ООО, дистрибуция группы)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>кондитерка</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3393,37 +3424,37 @@
           <t>АБИ (ABI Product)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>мясопереработка / полуфабрикаты</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3445,31 +3476,31 @@
           <t>Дамате</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>индейка / молоко / баранина</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="12" t="n">
         <v>46.3</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3491,37 +3522,37 @@
           <t>Комос Групп (молочный контур рейтинга)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>молоко / мясо / птица</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3543,37 +3574,37 @@
           <t>Орими Трейд (Tess, Greenfield, Jardin)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>чай / кофе</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3595,37 +3626,37 @@
           <t>Hochland Russland</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>сыр / молочка</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3647,37 +3678,37 @@
           <t>ГК Ренна</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>мороженое / сгущёнка</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3699,31 +3730,31 @@
           <t>Агроэко</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>свинина / мясо</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="12" t="n">
         <v>24.63</v>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>январь–июнь</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="12" t="n">
         <v>-6.4</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n">
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>1.99</v>
       </c>
       <c r="I24" s="12" t="n">
@@ -3741,37 +3772,37 @@
           <t>Прогресс (ФрутоНяня / Малышам)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>детское питание / соки</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3793,37 +3824,37 @@
           <t>ГК Молвест</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3845,37 +3876,37 @@
           <t>Эссен Продакшн (Махеевъ)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>соусы / консервация / кондитерка</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3897,37 +3928,37 @@
           <t>Юговской комбинат молочных продуктов</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>молочка / сыр</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -3949,37 +3980,37 @@
           <t>Сады Придонья</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>соки / пюре / растениеводство</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>январь–март, только тонны</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4001,37 +4032,37 @@
           <t>Ehrmann Россия</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>молочка / десерты</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4053,37 +4084,37 @@
           <t>ГК Фудлэнд</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>сыр / молочка</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4105,37 +4136,37 @@
           <t>Инвест Альянс (производство Ермолино)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>полуфабрикаты; связано с розницей Ермолино</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4157,37 +4188,37 @@
           <t>Lactalis Россия</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>сыр / молочка</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4209,33 +4240,33 @@
           <t>ГК ЭкоНива (молочный контур рейтинга)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>молочка / агро</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="12" t="n">
         <v>45.2</v>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>январь–июнь, вся группа</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="12" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n">
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>1.1</v>
       </c>
       <c r="I34" s="12" t="n">
@@ -4253,37 +4284,37 @@
           <t>ГК Айсберри</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>мороженое</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4305,37 +4336,37 @@
           <t>МПБК Очаково</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>пиво / квас / напитки</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4357,37 +4388,37 @@
           <t>ГК Российское Молоко</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4409,37 +4440,37 @@
           <t>ГК Экомилк</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4461,37 +4492,37 @@
           <t>АМП Дамол</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4513,37 +4544,37 @@
           <t>ГК Русское молоко</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4565,37 +4596,37 @@
           <t>ГК РостАгроКомплекс</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>молочка / творожные</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4617,37 +4648,37 @@
           <t>ГК Сыробогатов</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>сыр</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4669,37 +4700,37 @@
           <t>Арнест ЮниРусь</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>молочка / мороженое</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4721,37 +4752,37 @@
           <t>Нэфис Косметикс</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>бытовая химия</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4773,37 +4804,37 @@
           <t>Агрокомплекс им. Н.И. Ткачёва (молочный контур)</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>молочка / агро, Юг</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4825,37 +4856,37 @@
           <t>ГК Доминант (молочный контур)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>молочка / сахар смежно</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4877,37 +4908,37 @@
           <t>MLK Group (Ува-молоко)</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4929,37 +4960,37 @@
           <t>Ровеньки-Маслосырзавод</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>сыр / молочка</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -4981,37 +5012,37 @@
           <t>Брянский молочный комбинат</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5033,37 +5064,37 @@
           <t>ГК Мультипро</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>молочка / ингредиенты</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5085,37 +5116,37 @@
           <t>Зеленодольский МК</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5137,37 +5168,37 @@
           <t>Лебедяньмолоко</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5189,37 +5220,37 @@
           <t>Froneri Россия</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>мороженое</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5241,37 +5272,37 @@
           <t>ГК Руслакто</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5293,37 +5324,37 @@
           <t>ГК ВАМИН</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>молочка, Татарстан</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5345,37 +5376,37 @@
           <t>СК Ичалковский / СЗ Сармич</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>сыр / молочка</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5397,37 +5428,37 @@
           <t>Ирбитский молочный завод</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5449,37 +5480,37 @@
           <t>ТнВ Сыр Стародубский</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>сыр</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5501,37 +5532,37 @@
           <t>МилкЭкспресс</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5553,37 +5584,37 @@
           <t>Пискарёвский молочный завод</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>молочка, СЗФО</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5605,37 +5636,37 @@
           <t>Барнаульский молочный комбинат</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5657,37 +5688,37 @@
           <t>DMK Group</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5709,37 +5740,37 @@
           <t>ГК Галактика</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>молочка</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5761,37 +5792,37 @@
           <t>Виола</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>сыр / молочка</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
@@ -5815,10 +5846,1190 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A2C4C9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23.25" customWidth="1" style="6" min="1" max="1"/>
+    <col width="21.63" customWidth="1" style="6" min="2" max="2"/>
+    <col width="18" customWidth="1" style="6" min="3" max="3"/>
+    <col width="16" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" customWidth="1" style="6" min="5" max="5"/>
+    <col width="18" customWidth="1" style="6" min="6" max="6"/>
+    <col width="14" customWidth="1" style="6" min="7" max="7"/>
+    <col width="16" customWidth="1" style="6" min="8" max="8"/>
+    <col width="12" customWidth="1" style="6" min="9" max="9"/>
+    <col width="78" customWidth="1" style="6" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="6">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Компания</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Тип / формат</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Выручка 2026 факт, млрд ₽</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>За какой кусок года</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>Рост к тому же куску 2025, %</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Оценка / прогноз на весь 2026, млрд ₽</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>Магазины / заводы, шт</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
+        <is>
+          <t>Прибыль за тот же кусок, млрд ₽</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>Маржа, %</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>Откуда цифра, простыми словами</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="6">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Сети: от ~30 точек, не федеральные гиганты</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+    </row>
+    <row r="3" ht="83" customHeight="1" s="6">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Семишагофф (ООО ТК Прогресс)</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>жёсткий дискаунтер, Петербург и Ленобласть</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>190</v>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 компания не публиковала. Последний закрытый год — весь 2025: 70,67 млрд (+29%), прибыль 0,955 млрд, маржа 1,4 копейки с рубля. К 2025–началу 2026 около 190 магазинов. В 2025 купили склад в Шушарах почти на 1,5 млрд — это не «сворачиваемся». В августе 2026 агентство INFOLine: с метра площади в 2025-м впервые больше 1 млн рублей, второе место в стране после «Азбуки вкуса». Сигнал для ИТ на 2026–27: резать незачем. Сеть растёт, склад свой, кассы и учёт будут нужны на большом обороте. https://checko.ru/company/tk-progress-1127847102338</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1" s="6">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>SPAR Калининград (ООО Евроритейл)</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>супермаркет, Калининградская область</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025 у ООО «Евроритейл»: 32,68 млрд (+15%), прибыль 0,563 млрд, маржа 1,7 копейки с рубля. Не путать с ООО «Спар-Калининград» (54 млн и 2 человека — это не магазины). Апрель 2026, замгендиректора: больше 100 магазинов, «Пятёрочка» уже около 200, с ней по числу точек и по цене в массовом сегменте не гонятся. В 2025 открыли шесть магазинов. В 2025 директор говорила: каждый год +10 точек и 20–25 реконструкций, электронные ценники уже стоят. Сигнал для ИТ: не урезают «под закрытие». Деньги скорее на реконструкцию, ценники и логистику через паром, чем на гонку с «Пятёрочкой». https://kaliningrad-news.net/society/2026/04/17/281609.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="88" customHeight="1" s="6">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Лама (SPAR / Первоцен / F City; сумма 4 юрлиц)</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>супер / у дома, Томск и Новосибирск</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>103</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — сумма четырёх магазинных юрлиц за 2025: 5,6 + 7 + 8,7 + 11 = 32,3 млрд, прибыль 0,335 млрд, маржа около 1 копейки с рубля. Управляющую «Ламу» (134 млн) с магазинами не складывали. ФАС 20 октября 2025 согласовала, чтобы «Лама» полностью управляла SPAR, «Первоценом» и F City в Томской и Новосибирской областях. У самой «Ламы» тогда 103 магазина. Сигнал для ИТ на 2026–27: скорее потратят на склейку касс, справочников и склада после сделки, чем выкинут систему. Своего «в 2026 продадим на столько-то» не было. https://retailer.ru/fas-soglasovala-pokupku-lamoj-seti-spar-v-tomskoj-i-novosibirskoj-oblastjah/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="81" customHeight="1" s="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Аникс (ТС Аникс + Прайд-А)</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>у дома, Алтай</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>165</v>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — два юрлица за 2025: 18,3 + 13,0 = 31,3 млрд, прибыль 0,414 млрд, маржа 1,3 копейки с рубля. Своих магазинов 165, ещё 109 франшиза «Корзинка». В 2025 прибыль выросла. Своего плана продаж на 2026 не публиковали. Сигнал для ИТ: живой региональный игрок с прибылью, не «режим выживания». Но и программы «тратим на цифру столько-то» нет — бюджет ИТ в рублях никто не раскрывал. https://tolknews.ru/ekonomika/214569-skolko-zarabotali-krupneyshie-seti-altaya-mariya-ra-i-aniks-v-godu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" s="6">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Европа (ООО Европа, Курск)</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>гипер / супер, Черноземье</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 31 млрд (+2,7%), прибыль 1,1 млрд, маржа 3,6 копейки с рубля — для продуктов густо. Директор: 47 магазинов (34 гипер, 7 супер, 6 у дома). На сайте компании «около 60 предприятий». Рост продаж слабый. Своего прогноза на 2026 нет. Сигнал для ИТ: сеть на ногах и не продаётся федералам (слова директора). Больших строек и «режем всё» в открытом виде тоже нет — скорее держат текущие системы. https://www.audit-it.ru/contragent/1074632016205_ooo-evropa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1" s="6">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Бегемаг / SPAR Кузбасс (ООО Универсамы Бегемаг)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>у дома / SPAR, Кемеровская область</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>74</v>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 12,87 млрд (+1%), прибыль всего 65 млн, маржа полкопейки с рубля. На начало 2026: 74 магазина, закрытий не было. В 2025 новые точки почти не открывали: эффективность, аренда, тарифы. Запустили SPAR-Express и кассы самообслуживания. Июль 2026: в нацпроекте «Производительность труда» — торты пекут вдвое быстрее, выработка на человека +27%. Сигнал для ИТ: не на открытие сети, а на то, что режет издержки (самообслуживание, бережливое производство). Большой «бюджет на цифровизацию» не обещали. https://www.retail.ru/articles/kak-rosli-riteylery-v-2025-godu-ekspansiya-optimizatsiya-i-znachimye-resheniya-vedushchikh-setey/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="73" customHeight="1" s="6">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Низкоцен (ООО Холлифуд)</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>жёсткий дискаунтер, Сибирь и Урал</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 9,5 млрд (−2%), прибыль 61 млн, маржа 0,6 копейки с рубля. На сайте 71 магазин, новые объекты ищут. Сигнал для ИТ: осторожно. Продажи уже не росли, маржа тонкая. Скорее заморозка лишнего, чем новая платформа. Своего плана на 2026 нет. https://ksonline.ru/605083/skolko-zarabotali-krupnye-sibirskie-produktovye-seti-v-2025-godu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1" s="6">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>OFFPRICE (ООО Оффпрайс)</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>аутлет одежды, не продукты; Москва и ещё города</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>Это не продукты. Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 4,85 млрд (+1,8%), прибыль 0,113 млрд, маржа 2,3 копейки с рубля. На сайте «30+ аутлетов»; вы называли 40. Рост почти остановился. Сигнал для ИТ: слабый рост, не FMCG. Большого «режем / строим» в открытом виде нет. https://firmoteka.ru/7725844967</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1" s="6">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>КЗВС (вет. аптеки, Краснодарский край)</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>ветеринарные аптеки, не человеческая аптека</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — ООО «КЗВС» весь 2025: 1,13 млрд (+2,6%), прибыль 0,108 млрд, маржа почти 10 копеек с рубля — для розницы жирно. На сайте 200 вет. аптек, в штате юрлица 92 человека: часть точек, скорее всего, партнёры. Сигнал для ИТ: маржа позволяет не резать всё подряд, но это одно юрлицо, не холдинг. Своего плана «в 2026 откроем столько-то» не нашли. https://www.testfirm.ru/result/2312208833_ooo-kzvs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="74" customHeight="1" s="6">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>АО «Иркутская аптека»</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>муниципальные аптеки, Иркутск</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 1,1 млрд (−2%), убыток 4,5 млн. На 1 января 2026 — 43 точки (вы называли 44). Городская сеть, в 2025-м из МУП сделали АО. Сигнал для ИТ на 2026–27: скорее заморозка и обязательные госсистемы, чем новая коммерческая платформа. Убыток и муниципальный хозяин — плохой фон для лишних проектов. https://ircity.ru/text/business/2026/09/07/76621885/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="6">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Заводы поменьше: 2026 почти не раскрывают, смотрим стройки и прибыль 2025</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="79" customHeight="1" s="6">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Любятово (ООО; ГК Черноголовка)</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>сухие завтраки / печенье, 3 площадки</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 13,2 млрд (+25%), прибыль 0,847 млрд, маржа 6,4 копейки с рубля. Площадки: Воронеж, Псков, Вязьма. Февраль 2026: в Воронеже обсуждали производственно-складской комплекс, в прессе оценка около 4 млрд. Сентябрь 2026: в Вязьме — новые линии и склад на 2026–2027. Сигнал для ИТ: капекс точно не режут. Заводу, который строит корпус и склад, учёт и линии будут нужны. Это не прогноз выручки на год. https://www.kommersant.ru/doc/8476994</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1" s="6">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Иркутский масложиркомбинат</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>масло / жмых, Иркутск</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 16,35 млрд (−0,9%), прибыль 2,33 млрд. Маржа 14 копеек с рубля, но заметная часть — проценты по деньгам на счетах, не от продажи масла. Агентство INFOLine, сентябрь 2026: у крупных производителей еды рост «около нуля» — это рынок, не этот завод. Сигнал для ИТ: денег после 2025 много, своего плана строек на 2026 не нашли. Не «режим порезок», но и не анонс цифры. https://finscanner.ru/company/3811185573/finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="68" customHeight="1" s="6">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Каравай (ОАО, Санкт-Петербург)</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>хлеб, 6 площадок</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 11,12 млрд (+15%), прибыль 0,709 млрд, маржа 6,4 копейки с рубля. Не путать с ангарским «Караваем». Сигнал для ИТ: 2025 прибыльный. Своего плана на 2026 нет. По рынку заводов рост около нуля. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="67" customHeight="1" s="6">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>СМАК (АО, Екатеринбург)</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>хлеб, 3 площадки</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 9,79 млрд (+18%), прибыль 1,11 млрд, маржа 11 копеек с рубля. Три площадки, включая Раменское. Сигнал для ИТ: маржа высокая, 2025 сильный. Своего «в 2026 продадим на столько-то» нет. https://www.smakhleb.ru/predpriyatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1" s="6">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Лимак (АО, Липецк)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>хлеб / мука, 10 площадок</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 8,93 млрд (+8%), прибыль 0,22 млрд, маржа 2,5 копейки с рубля — для хлеба скромно. Девять хлебозаводов плюс мельница. Сигнал для ИТ: сеть площадок живая, но маржа тонкая. Лишнего ИТ без окупаемости, скорее всего, не купят. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1" s="6">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Первый хлебокомбинат (АО, Челябинск)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>хлеб</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 8,00 млрд (+10%), прибыль 1,16 млрд, маржа 14,5 копейки с рубля. Сколько площадок — не нашли. Сигнал для ИТ: прибыль 2025 большая, плана 2026 нет. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="73" customHeight="1" s="6">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Вологодское мороженое (ООО)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>мороженое, 3 фабрики</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 6,63 млрд (−7%), прибыль 2,78 млрд, маржа 42 копейки с рубля — для мороженого необычно много, причину компания не объясняла. Сигнал для ИТ: продажи падали, прибыль огромная. На «режем ИТ из-за дыры» не похоже, на «строим новую цифру» тоже ничего не анонсировали. https://nalogovaya.ru/egrul/companies/1033500071505/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1" s="6">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Покровский хлеб (АО, Пермь)</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>хлеб, 3 завода в Перми</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 5,5 млрд (+17%), прибыль 0,82 млрд, маржа почти 15 копеек с рубля. Три пермских завода. Сигнал для ИТ: 2025 сильный. Своего плана капекса на 2026–27 не нашли. https://www.kommersant.ru/doc/8552543</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="6">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Ваши примеры: точки есть, денег за 2026 нет</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+      <c r="J22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="76" customHeight="1" s="6">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>Дружба (Рыбинск, Ярославская область)</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>супер / гипер, местная сеть</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t>Сводной выручки сети нет — ни за 2026, ни за 2025. Сайт: 28 точек, 12 500 м², 1 700 человек. Юрлицо ООО «Дружба» (66 млн и 14 человек) — не эта сеть, в таблицу не ставили. Июнь 2026: закрывают гипермаркет в ТЦ «Космос» (работал ~15 лет), дата около 20 июля. Сигнал для ИТ: сжимаются, не расширяются. Новый дорогой софт на этом фоне маловероятен. https://ngs76.ru/gorod/v-rybinske-zakroetsya-gipermarket-druzhba-magazin-prorabotal-15-let-id341441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="72" customHeight="1" s="6">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Ёвар (Таджикистан)</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>супермаркеты, Таджикистан</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
+        <is>
+          <t>Выручки в открытом виде нет. Октябрь 2025: сеть писала про 30 супермаркетов и новый зал в City Mall. Вы называли 62 — 62 в открытых текстах не подтвердили. Сигнал для ИТ: по словам самой сети — расширение географии, не сжатие. Суммы и ИТ-бюджет неизвестны. https://koinotinav.tj/news/set-supermarketov-evar-ukreplyaet-pozicii-i-rasshiryaet-geografiyu-prisutstviya</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="65" customHeight="1" s="6">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Centr Fayz (Ташкент)</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>супермаркеты, Узбекистан</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="H25" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>62 точки — как вы указали. Открытой выручки нет. Попадаются «Fayz» и «Kredit Fayz» (техника) — это не обязательно та же сеть, деньги не ставили. Сигнал для ИТ: по открытым источникам ничего; ни «режем», ни «строим» подтвердить нельзя.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -5863,10 +7074,10 @@
           <t>https://www.x5.ru/ru/investors/financial-and-operational-results/</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
     </row>
     <row r="3" ht="72" customHeight="1" s="6">
       <c r="A3" s="14" t="inlineStr">
@@ -5884,10 +7095,10 @@
           <t>https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
     </row>
     <row r="4" ht="72" customHeight="1" s="6">
       <c r="A4" s="14" t="inlineStr">
@@ -5905,10 +7116,10 @@
           <t>https://www.x5.ru/ru/news/x5-predstavila-prognozy-i-orientiry-na-2026-god/</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
     </row>
     <row r="5" ht="72" customHeight="1" s="6">
       <c r="A5" s="14" t="inlineStr">
@@ -5926,10 +7137,10 @@
           <t>https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
     </row>
     <row r="6" ht="72" customHeight="1" s="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5947,10 +7158,10 @@
           <t>https://www.x5.ru/ru/investors/financial-and-operational-results/</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
     </row>
     <row r="7" ht="72" customHeight="1" s="6">
       <c r="A7" s="14" t="inlineStr">
@@ -5968,10 +7179,10 @@
           <t>https://www.kommersant.ru/doc/8923592</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="72" customHeight="1" s="6">
       <c r="A8" s="14" t="inlineStr">
@@ -5989,10 +7200,10 @@
           <t>https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="9" ht="72" customHeight="1" s="6">
       <c r="A9" s="14" t="inlineStr">
@@ -6010,10 +7221,10 @@
           <t>https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
     </row>
     <row r="10" ht="72" customHeight="1" s="6">
       <c r="A10" s="14" t="inlineStr">
@@ -6031,10 +7242,10 @@
           <t>https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
     </row>
     <row r="11" ht="72" customHeight="1" s="6">
       <c r="A11" s="14" t="inlineStr">
@@ -6052,10 +7263,10 @@
           <t>https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
     </row>
     <row r="12" ht="72" customHeight="1" s="6">
       <c r="A12" s="14" t="inlineStr">
@@ -6073,10 +7284,10 @@
           <t>https://www.interfax.ru/business/1111410</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
     </row>
     <row r="13" ht="72" customHeight="1" s="6">
       <c r="A13" s="14" t="inlineStr">
@@ -6094,10 +7305,10 @@
           <t>https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
     </row>
     <row r="14" ht="72" customHeight="1" s="6">
       <c r="A14" s="14" t="inlineStr">
@@ -6115,10 +7326,10 @@
           <t>https://news.mail.ru/economics/71212403/</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
     </row>
     <row r="15" ht="72" customHeight="1" s="6">
       <c r="A15" s="14" t="inlineStr">
@@ -6128,7 +7339,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>По большинству сетей из регионов и заводов своего прогноза «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год +9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку выручки это не ставили — это не продажи компании.</t>
+          <t>По большинству сетей из регионов и заводов своего прогноза «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год +9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку выручки это не ставили — это не продажи компании. Регионы меньшего масштаба и сигнал «режут ли ИТ» — на листе «Регионы».</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -6136,94 +7347,162 @@
           <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
     </row>
     <row r="16" ht="72" customHeight="1" s="6">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Агентство INFOLine — сети на весь 2026</t>
+          <t>Регионы меньшего масштаба — 2026 и ИТ</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
+          <t>У сетей на 30–200 точек своего отчёта за кусок 2026 почти нет. На листе «Регионы» те же десять колонок, что у крупных. В деньгах за 2026 чаще «нет данных». В комментарии — последний закрытый 2025 и что видно на 2026–27: открывают, склеивают сети, режут издержки или закрывают магазин. Это не «бюджет ИТ в рублях», такого никто не публикует.</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>https://www.kommersant.ru/doc/8923592</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
+          <t>https://www.kommersant.ru/doc/8937600</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
     </row>
     <row r="17" ht="72" customHeight="1" s="6">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Агентство INFOLine — заводы</t>
+          <t>Открытия магазинов замедлились, лето 2026</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только +1%.</t>
+          <t>Агентство INFOLine: у крупнейших сетей за год до июня 2026 точек стало больше только на 4,9% (годом раньше было +10,8%). Новый магазин дороже на 8–12%. Часть денег уходит в доставку и цифру. Это фон рынка, не строка «Семишагофф».</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
+          <t>https://www.kommersant.ru/doc/8937600</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
     </row>
     <row r="18" ht="72" customHeight="1" s="6">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Доставка продуктов, начало 2026</t>
+          <t>SPAR Калининград — не путать юрлица</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (+24%). К марту 1,83 триллиона (+22%), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не выручка одной Лавки или Ozon Fresh.</t>
+          <t>Операционная компания ООО «Евроритейл»: за 2025 продали на 32,7 млрд (+15%), прибыль 0,56 млрд. ООО «Спар-Калининград» — другое юрлицо, 54 млн выручки: это не магазины. Директор сети в июне 2025: 105 магазинов.</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>https://datainsight.ru/DI_eGrocery_april_2026</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
+          <t>https://firmoteka.ru/3906321175</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
     </row>
     <row r="19" ht="72" customHeight="1" s="6">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>Сибирские сети, апрель 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>«Континент Сибирь» разобрал российские отчёты: «Лама» — сумма четырёх магазинных юрлиц 32,3 млрд, «Аникс» отдельно, «Бегемаг» 13 млрд при прибыли всего 65 млн, «Низкоцен» 9,5 млрд. Управляющую компанию «Лама» (134 млн) с магазинами складывать нельзя.</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>https://ksonline.ru/605083/skolko-zarabotali-krupnye-sibirskie-produktovye-seti-v-2025-godu/</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="72" customHeight="1" s="6">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Агентство INFOLine — сети на весь 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>https://www.kommersant.ru/doc/8923592</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1" s="6">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Агентство INFOLine — заводы</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только +1%.</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1" s="6">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Доставка продуктов, начало 2026</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (+24%). К марту 1,83 триллиона (+22%), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не выручка одной Лавки или Ozon Fresh.</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>https://datainsight.ru/DI_eGrocery_april_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1" s="6">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
           <t>Сети из регионов — не прогноз продаж, а продажа самой сети</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>«Верный» с октября 2025 ищут покупателя (оценка 25–35 млрд — цена всего бизнеса). «Гулливер» в начале 2026 писали как выставленный на продажу. Про «Мария-Ра» летом 2026 писали, что смотрит «Лента». Цифры выручки на 2026 никто из них не давал.</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>https://www.kommersant.ru/doc/8158706</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6245,6 +7524,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -5983,7 +5983,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="6">
+    <row r="4" ht="98" customHeight="1" s="6">
       <c r="A4" s="18" t="inlineStr">
         <is>
           <t>SPAR Калининград (ООО Евроритейл)</t>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025 у ООО «Евроритейл»: 32,68 млрд (+15%), прибыль 0,563 млрд, маржа 1,7 копейки с рубля. Не путать с ООО «Спар-Калининград» (54 млн и 2 человека — это не магазины). Апрель 2026, замгендиректора: больше 100 магазинов, «Пятёрочка» уже около 200, с ней по числу точек и по цене в массовом сегменте не гонятся. В 2025 открыли шесть магазинов. В 2025 директор говорила: каждый год +10 точек и 20–25 реконструкций, электронные ценники уже стоят. Сигнал для ИТ: не урезают «под закрытие». Деньги скорее на реконструкцию, ценники и логистику через паром, чем на гонку с «Пятёрочкой». https://kaliningrad-news.net/society/2026/04/17/281609.html</t>
+          <t>За 2026 продаж компания не публиковала. Что есть — весь 2025 у ООО «Евроритейл»: 32,68 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 563 миллиона — это 1,7 копейки с каждого рубля. Рядом есть другое ООО — «Спар-Калининград»: 54 миллиона выручки и двое сотрудников. Это не магазины, их цифры сюда не относятся. В апреле 2026 замгендиректора сказал: магазинов уже больше ста. «Пятёрочка» в области около двухсот — по числу точек и по цене с ней не соревнуются. За 2025 открыли шесть магазинов. Директор раньше говорила: каждый год плюс десять новых и 20–25 ремонтов старых. Электронные ценники уже стоят. Для ИТ это значит: сеть живая, не сворачивается. Деньги скорее на ремонт магазинов, ценники и доставку через паром, чем на то, чтобы догнать «Пятёрочку». https://kaliningrad-news.net/society/2026/04/17/281609.html</t>
         </is>
       </c>
     </row>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -460,12 +460,12 @@
     <row r="3" ht="64" customHeight="1" s="6">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Почему нет колонки «выручка за весь 2026»</t>
+          <t>Почему нет колонки «продажи за весь 2026»</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Сегодня 29 октября 2026. Год закроется 31 декабря. Полные годовые отчёты компании обычно публикуют весной 2027. Поэтому в таблице два разных числа: уже вышедший кусок года и, где можно, оценка полного года.</t>
+          <t>Сегодня 29 октября 2026. Год закроется 31 декабря. Полные годовые отчёты компании обычно публикуют весной 2027. Поэтому в таблице два разных числа: уже вышедший период и, где можно, оценка полного года.</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Только опубликованная выручка за девять месяцев, полгода или (редко) квартал. X5 — единственная из крупных, у кого на октябрь уже есть девять месяцев. Магнит, Лента, Fix Price, Русагро, Черкизово — полгода. Светофор, Mercury, Самокат, Ашан, Metro — оценки агентства INFOLine за полгода, не их собственный отчёт.</t>
+          <t>Только опубликованные продажи за девять месяцев, полгода или (редко) квартал. X5 — единственная из крупных, у кого на октябрь уже есть девять месяцев. Магнит, Лента, Fix Price, Русагро, Черкизово — полгода. Светофор, Mercury, Самокат, Ашан, Metro — оценки агентства INFOLine за полгода, не их собственный отчёт.</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Либо слова самой компании (X5: рост 12–16%; Мираторг: «несколько процентов»), либо простая арифметика: выручка 2025, умноженная на рост уже вышедшего куска 2026. Это не отчёт и не гарантия. У «Русагро» осень обычно сильнее весны — поэтому полугодие на два не умножали.</t>
+          <t>Либо слова самой компании (X5: рост 12–16%; Мираторг: «несколько процентов»), либо простая арифметика: продажи 2025, умноженные на рост уже вышедшего периода 2026. Это не отчёт и не гарантия. У «Русагро» осень обычно сильнее весны — поэтому полугодие на два не умножали.</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Прибыль — сколько денег осталось после всех расходов за тот же кусок года, что и в столбце «факт». Маржа — какая это доля от продаж: 2% значит две копейки прибыли с каждого рубля. Цифры есть только там, где компания сама опубликовала и прибыль, и продажи за один период: шесть сетей и четыре завода. Исключение — X5: продажи уже за девять месяцев, прибыль пока только за январь–июнь. У остальных в этих столбцах «нет данных».</t>
+          <t>Прибыль — сколько денег осталось после всех расходов за тот же период, что и в столбце «факт». Маржа — какая это доля от продаж: 2% значит две копейки прибыли с каждого рубля. Цифры есть только там, где компания сама опубликовала и прибыль, и продажи за один период: шесть сетей и четыре завода. Исключение — X5: продажи уже за девять месяцев, прибыль пока только за январь–июнь. У остальных в этих столбцах «нет данных».</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных». Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей +9–11%, производители еды около нуля, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
+          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных». Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей плюс 9–11%, производители еды около нуля, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Свои в рублях — почти ни у кого из тех, у кого в таблице «нет данных». X5 ещё в марте держала +12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «новые заводы начнут себя окупать», без суммы. У сетей из регионов вместо прогноза продаж были новости про продажу самой сети. Мировые PepsiCo и Nestlé дают прогноз на весь мир, не на Россию.</t>
+          <t>Свои в рублях — почти ни у кого из тех, у кого в таблице «нет данных». X5 ещё в марте держала плюс 12–16% (это уже в таблице). Мираторг в июне сказал «несколько процентов». ЭФКО — «новые заводы начнут себя окупать», без суммы. У сетей из регионов вместо прогноза продаж были новости про продажу самой сети. Мировые PepsiCo и Nestlé дают прогноз на весь мир, не на Россию.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Те же десять колонок на листах «Сети», «Производители» и «Регионы». К выручке добавлены прибыль и маржа, плюс этот лист и обновлённый «Медиа».</t>
+          <t>Шрифт Times New Roman 11, шапка и столбец «Компания» — заливка #A2C4C9, как в вашей Google-таблице. Те же десять колонок на листах «Сети», «Производители» и «Регионы». К продажам добавлены прибыль и маржа, плюс этот лист и обновлённый «Медиа».</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Это сети на 30–200 точек и заводы поменьше. Выручки за кусок 2026 у них почти нет — в столбцах денег стоит «нет данных», чтобы не подменять 2026 закрытым 2025-м. В комментарии два слоя: последний закрытый год (чтобы видеть маржу и прибыль) и что видно на 2026–27 (открывают, склеивают сети, режут издержки, закрывают магазин). Никто из них не публикует «бюджет ИТ в рублях». Сигнал такой: растёт и строит склад / склеивает юрлица после сделки — ИТ скорее не режут; продажи уже падали, убыток, закрывают гипермаркет — скорее заморозка; тонкая маржа и «год эффективности» — ИТ только если окупается на издержках.</t>
+          <t>Это сети на 30–200 точек и заводы поменьше. Продаж за период 2026 у них почти нет — в столбцах денег стоит «нет данных», чтобы не подменять 2026 закрытым 2025-м. В комментарии два слоя: закрытый год (чтобы видеть прибыль) и что видно на 2026–27 (открывают, склеивают сети, режут расходы, закрывают магазин). Никто из них не публикует «бюджет ИТ в рублях». Читать так: растёт и строит склад / склеивает компании после сделки — ИТ скорее не режут; продажи уже падали, убыток, закрывают гипермаркет — скорее заморозка; прибыли мало и «год эффективности» — ИТ только если окупается на расходах.</t>
         </is>
       </c>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>За какой кусок года</t>
+          <t>За какой период</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Рост к тому же куску 2025, %</t>
+          <t>Рост к тому же периоду 2025, %</t>
         </is>
       </c>
       <c r="F1" s="11" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="H1" s="11" t="inlineStr">
         <is>
-          <t>Прибыль за тот же кусок, млрд ₽</t>
+          <t>Прибыль за тот же период, млрд ₽</t>
         </is>
       </c>
       <c r="I1" s="11" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="98" customHeight="1" s="6">
+    <row r="2" ht="101" customHeight="1" s="6">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>X5 Group (Пятёрочка, Перекрёсток, Чижик)</t>
@@ -669,11 +669,11 @@
       </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
-          <t>Сама компания 16 октября 2026, цифры ещё без проверки аудитора. За январь–сентябрь продали на 3 791,5 млрд рублей — на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь: 1 311 млрд (+13%). Пятёрочка за девять месяцев 2 918 (+9,4%), Перекрёсток 413 (+7,1%), Чижик 391 (+31,4%), доставка X5 — 257 (+28,4%). Магазинов 30 981 на конец сентября. Прибыль в таблице — 25,7 млрд, но это не за девять месяцев, а только за январь–июнь. За девять месяцев прибыль ещё не вышла (ждут 29 октября). Маржа 1% — это 25,7 от продаж за те же январь–июнь (2 481 млрд). От 3 792 за девять месяцев считать нельзя: куски года разные. Свой прогноз на весь год компания не снимала: рост 12–16%. От выручки 2025 (4 642) это 5 200–5 385. https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="87" customHeight="1" s="6">
+          <t>Сама компания 16 октября 2026, аудитор эти цифры ещё не проверял. За январь–сентябрь продали на 3 791,5 млрд рублей — на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь: 1 311 млрд, на 13% больше. Пятёрочка за девять месяцев 2 918 млрд (на 9,4% больше), Перекрёсток 413 (на 7,1% больше), Чижик 391 (на 31,4% больше), доставка X5 — 257 (на 28,4% больше). Магазинов 30 981 на конец сентября. Прибыль в таблице — 25,7 млрд, но это не за девять месяцев, а только за январь–июнь. Прибыль за девять месяцев ещё не вышла (ждали 29 октября). 1% в столбце маржи — это 25,7 от продаж за те же январь–июнь (2 481 млрд). От 3 792 за девять месяцев считать нельзя: это разные периоды. Свой прогноз на весь год компания не меняла: рост 12–16%. От продаж 2025 (4 642) это 5 200–5 385. https://www.x5.ru/wp-content/uploads/2026/10/q3_2026_trading_update_rus.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1" s="6">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Магнит (вкл. Дикси, Самбери, Азбука вкуса)</t>
@@ -709,11 +709,11 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт 28 августа 2026: за полгода продали на 1 887,2 млрд рублей (+12,8%). Из них магазины 1 871. Точек 33 652. Долги минус деньги на счетах ≈ 514,5 млрд. Прибыль за те же январь–июнь в ячейке −1,9 млрд: сеть пока в минусе, мешают проценты по кредитам. Есть второй счёт того же минуса — около −9,5: там аренду магазинов считают как долг. В ячейке стоит −1,9, без этого правила. Оценка всего года, если второе полугодие будет как первое: 3 509 × 1,128. Это не отчёт за год. https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="61" customHeight="1" s="6">
+          <t>Официальный отчёт 28 августа 2026: за полгода продали на 1 887,2 млрд рублей — на 12,8% больше, чем годом раньше. Из них магазины 1 871. Точек 33 652. Долги минус деньги на счетах примерно 514,5 млрд. Прибыль за те же январь–июнь в ячейке −1,9 млрд: сеть пока в минусе, мешают проценты по кредитам. Есть другой способ считать тот же минус — около −9,5: там аренду магазинов считают как долг. В ячейке стоит −1,9, без этого правила. Оценка всего года, если второе полугодие будет как первое: 3 509 × 1,128. Это не отчёт за год. https://www.magnit.com/ru/media/press-releases/magnit-obyavlyaet-operatstionnye-i-finansovye-rezultaty-deyatelnosti-za-pervoe-polugodie-2026-goda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="63" customHeight="1" s="6">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Mercury Retail (Красное &amp; Белое, Бристоль)</t>
@@ -755,11 +755,11 @@
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
-          <t>Агентство INFOLine в «Коммерсанте» 2 сентября 2026: за полгода 878 млрд (+11,2%). Своего сводного отчёта всей группы нет. Оценка года, если темп удержится: 1 660 × 1,112. https://www.kommersant.ru/doc/8923592</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="88" customHeight="1" s="6">
+          <t>Агентство INFOLine в «Коммерсанте» 2 сентября 2026: за полгода 878 млрд — на 11,2% больше, чем годом раньше. Своего сводного отчёта всей группы нет. Оценка года, если тот же темп удержится: 1 660 × 1,112. https://www.kommersant.ru/doc/8923592</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="6">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Группа Лента (Гипер/Супер Лента, Монетка, Улыбка радуги, Реми)</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт: за полгода 648,5 млрд (+26,2%); апрель–июнь 341,6 (+28,8%). Магазинов 7 456 на 30 июня. Быстрее всех внутри группы — «Супер Лента» (+30,2%) и «Монетка» (+26,1%), большие магазины +12,9%. Прибыль за те же полгода 13 млрд — примерно 2 копейки с каждого рубля продаж. В августе купила большие магазины «О’КЕЙ» — с осени в цифрах будут ещё и чужие точки. Оценка года без этой покупки: 1 104 × 1,262. К 2028 сама Лента хочет 2,2 триллиона — это цель на потом, не на 2026. https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
+          <t>Официальный отчёт: за полгода 648,5 млрд — на 26,2% больше, чем годом раньше; апрель–июнь 341,6 млрд, на 28,8% больше. Магазинов 7 456 на 30 июня. Быстрее всех внутри группы — «Супер Лента» (на 30,2% больше) и «Монетка» (на 26,1% больше), большие магазины — на 12,9% больше. Прибыль за те же полгода 13 млрд — примерно 2 копейки с каждого рубля продаж. В августе купила большие магазины «О’КЕЙ» — с осени в цифрах будут ещё и эти точки. Оценка года без этой покупки: 1 104 × 1,262. К 2028 сама Лента хочет 2,2 триллиона — это цель на потом, не на 2026. https://www.lentagroup.ru/ru/media/news-and-press-releases/gruppa-lenta-obyavlyaet-o-roste-vyruchki-na-28-8-roste-lfl-prodazh-na-6-5-vo-2-kvartale-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="59" customHeight="1" s="6">
+    <row r="7" ht="61" customHeight="1" s="6">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ВкусВилл</t>
@@ -887,11 +887,11 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 191,06 млрд (+7,8%). Обогнал «Светофор» среди пяти крупнейших. Оценка года: 359 × 1,078. https://www.infoline.spb.ru/news/?news=308855</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="73" customHeight="1" s="6">
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 191,06 млрд — на 7,8% больше, чем годом раньше. Обогнал «Светофор» среди пяти крупнейших. Оценка года: 359 × 1,078. https://www.infoline.spb.ru/news/?news=308855</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1" s="6">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Fix Price</t>
@@ -927,11 +927,11 @@
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт 27 августа 2026: за полгода 155,3 млрд (+4,8%); апрель–июнь 82,2 (+6,9%). Магазины 138,2, опт 17,1. Точек 8 077. Прибыль за те же полгода 2,7 млрд — это 1,8% от продаж (почти 2 копейки с рубля). Оценка года: 313 × 1,048. https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1" s="6">
+          <t>Официальный отчёт 27 августа 2026: за полгода 155,3 млрд — на 4,8% больше, чем годом раньше; апрель–июнь 82,2 млрд, на 6,9% больше. Магазины 138,2, опт 17,1. Точек 8 077. Прибыль за те же полгода 2,7 млрд — это 1,8% от продаж (почти 2 копейки с рубля). Оценка года: 313 × 1,048. https://investors.fix-price.ru/upload/iblock/927/qomfciov5lu66hurwrrsb5bn5wkxeut0/PJSC_Fix_Price_announces_key_operating_and_financial_results_for_Q2_2026_RUS.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="6">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Самокат</t>
@@ -973,11 +973,11 @@
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>Оценка агентства INFOLine / «Коммерсантъ»: за полгода 135 млрд (+15,5%). Оценка года: 279 × 1,155. https://www.kommersant.ru/doc/8923592</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1" s="6">
+          <t>Оценка агентства INFOLine / «Коммерсантъ»: за полгода 135 млрд — на 15,5% больше, чем годом раньше. Оценка года: 279 × 1,155. https://www.kommersant.ru/doc/8923592</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="57" customHeight="1" s="6">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>METRO Россия</t>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 118,9 млрд (+0,5%). Оценка года: 260 × 1,005. https://www.kommersant.ru/doc/8923610</t>
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 118,9 млрд — на 0,5% больше, чем годом раньше. Оценка года: 260 × 1,005. https://www.kommersant.ru/doc/8923610</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="80" customHeight="1" s="6">
+    <row r="12" ht="83" customHeight="1" s="6">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ozon + Ozon Fresh</t>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>Сколько именно продуктов продал Ozon Fresh в 2026, компания не говорит — ни факта, ни своего прогноза. Что было в начале года: агентство Data Insight в январе ждало, что вся доставка продуктов в России за 2026 год будет около 1,8 триллиона рублей (+24% к 2025). К марту уточнили 1,83 триллиона (+22%), к маю 1,84. Это весь рынок доставки, не цифра Ozon. За апрель–июнь пять сервисов (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) вместе сделали 260 млрд; заказы Ozon Fresh +65%. https://datainsight.ru/DI_eGrocery_april_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="72" customHeight="1" s="6">
+          <t>Сколько именно продуктов продал Ozon Fresh в 2026, компания не говорит — ни факта, ни своего прогноза. Что было в начале года: агентство Data Insight в январе ждало, что вся доставка продуктов в России за 2026 год будет около 1,8 триллиона рублей (на 24% больше, чем в 2025). К марту уточнили 1,83 триллиона (на 22% больше), к маю 1,84. Это весь рынок доставки, не цифра Ozon. За апрель–июнь пять сервисов (Самокат, ВкусВилл, Лавка, Пятёрочка, Ozon Fresh) вместе сделали 260 млрд; заказы Ozon Fresh выросли на 65%. https://datainsight.ru/DI_eGrocery_april_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="74" customHeight="1" s="6">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Яндекс Лавка</t>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Выручку Лавки отдельно не публикуют, своего прогноза по ней тоже не было. Весь интернет-блок Яндекса (Лавка + Маркет + Еда + Деливери) за полгода 247 млрд (+19%) — туда входят не только продукты. Заказов у Лавки за апрель–июнь +5%. Прогноз агентства Data Insight на 2026 — вся доставка продуктов в стране 1,83–1,84 триллиона. Это не цифра Лавки. https://datainsight.ru/DI_eGrocery_april_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="72" customHeight="1" s="6">
+          <t>Продажи Лавки отдельно не публикуют, своего прогноза по ней тоже не было. Весь интернет-блок Яндекса (Лавка + Маркет + Еда + Деливери) за полгода 247 млрд — на 19% больше, чем годом раньше. Туда входят не только продукты. Заказов у Лавки за апрель–июнь на 5% больше. Прогноз агентства Data Insight на 2026 — вся доставка продуктов в стране 1,83–1,84 триллиона. Это не цифра Лавки. https://datainsight.ru/DI_eGrocery_april_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76" customHeight="1" s="6">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>ГК О'КЕЙ / Да!</t>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>Большие магазины «О’КЕЙ» в конце 2025 продали. У оставшейся компании на бирже теперь только «ДА!»: за полгода 43,3 млрд (+10,4%), 236 магазинов. Прибыль только «ДА!» за те же полгода 1,2 млрд — 2,8% от продаж. Оценка года именно «ДА!»: 80 × 1,104. Большие магазины ООО «О’КЕЙ» за полгода 68,2 (−5,6%) — это уже Лента, с «ДА!» не складывать. https://okeygroup.lu/upload/IFRS%201H2026_RUS_final_.pdf</t>
+          <t>Большие магазины «О’КЕЙ» в конце 2025 продали. У оставшейся компании на бирже теперь только «ДА!»: за полгода 43,3 млрд — на 10,4% больше, чем годом раньше, 236 магазинов. Прибыль только «ДА!» за те же полгода 1,2 млрд — 2,8% от продаж. Оценка года именно «ДА!»: 80 × 1,104. Большие магазины ООО «О’КЕЙ» за полгода 68,2 млрд — на 5,6% меньше, чем годом раньше. Это уже Лента, с «ДА!» не складывать. https://okeygroup.lu/upload/IFRS%201H2026_RUS_final_.pdf</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не было. В начале 2026 про «Гулливер» из той же группы писали: сеть выставлена на продажу. Аналитик Совкомбанка: независимые сети, которые в 2025 продали больше чем на 100 млрд (Победа, Командор, Ярче, Аникс), в ближайшие 2–3 года могут сменить хозяина. Это не цифра выручки. Последнее открытое: 176 млрд за 2025. https://www.kommersant.ru/doc/8364093</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не было. В начале 2026 про «Гулливер» из той же группы писали: сеть выставлена на продажу. Аналитик Совкомбанка: независимые сети, которые в 2025 продали больше чем на 100 млрд (Победа, Командор, Ярче, Аникс), в ближайшие 2–3 года могут сменить хозяина. Это не цифра продаж. Последнее открытое: 176 млрд за 2025. https://www.kommersant.ru/doc/8364093</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. В обзорах конца 2025 и 2026 сеть называют как возможную покупку для крупного игрока — не как компанию со своим прогнозом. Последнее открытое: 168 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customHeight="1" s="6">
+          <t>Прогноза продаж на 2026 нет. В обзорах конца 2025 и 2026 сеть называют как возможную покупку для крупного игрока — не как компанию со своим прогнозом. Последнее открытое: 168 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="72" customHeight="1" s="6">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Гиперглобус (Globus)</t>
@@ -1357,11 +1357,11 @@
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 80,6 млрд без налога (+2,7%). В тех же магазинах, что были год назад, продажи +5,7%, средний чек +7,5%. Своего прогноза выручки на 2026 нет. Новый большой магазин планируют на 2027 (больше 4 млрд на стройку) — это не цифра продаж на этот год. Оценка года: 165,6 × 1,027. https://www.kommersant.ru/doc/9005166</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="66" customHeight="1" s="6">
+          <t>Агентство INFOLine / «Коммерсантъ»: за полгода 80,6 млрд без налога — на 2,7% больше, чем годом раньше. В тех же магазинах, что были год назад, продажи выросли на 5,7%, средний чек — на 7,5%. Своего прогноза продаж на 2026 нет. Новый большой магазин планируют на 2027 (больше 4 млрд на стройку) — это не цифра продаж на этот год. Оценка года: 165,6 × 1,027. https://www.kommersant.ru/doc/9005166</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1" s="6">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Верный (Союз Святого Иоанна Воина)</t>
@@ -1409,11 +1409,11 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. В октябре 2025 основатель искал покупателя: сеть оценивали в 25–35 млрд рублей. Это цена всего бизнеса, если его продадут, а не «сколько продадут за год». Российский отчёт за 2025 вышел 1 апреля 2026: 154,4 млрд — это прошлый год. https://www.kommersant.ru/doc/8158706</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="62" customHeight="1" s="6">
+          <t>Прогноза продаж на 2026 нет. В октябре 2025 основатель искал покупателя: сеть оценивали в 25–35 млрд рублей. Это цена всего бизнеса, если его продадут, а не «сколько продадут за год». Отчёт за 2025 вышел 1 апреля 2026: 154,4 млрд — это прошлый год. https://www.kommersant.ru/doc/8158706</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" s="6">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SPAR Миддл Волга (SPAR, EUROSPAR)</t>
@@ -1455,11 +1455,11 @@
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>Агентство INFOLine / «Коммерсантъ»: «Спар Миддл Волга, Smart» за полгода 103,57 млрд (+7,8%). Тут шире, чем строка 2025 (тогда только SPAR Миддл Волга — 136 за год). Грубая оценка года: 136 × 1,078. https://www.kommersant.ru/doc/8923592</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="68" customHeight="1" s="6">
+          <t>Агентство INFOLine / «Коммерсантъ»: «Спар Миддл Волга, Smart» за полгода 103,57 млрд — на 7,8% больше, чем годом раньше. Тут шире, чем строка 2025 (тогда только SPAR Миддл Волга — 136 за год). Грубая оценка года: 136 × 1,078. https://www.kommersant.ru/doc/8923592</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="69" customHeight="1" s="6">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Мария-Ра (Розница К-1)</t>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. Последнее: российский отчёт за 2025 — 127,5 млрд (+5%). На 1 июля 2026 — 1 303 магазина (это штуки, не деньги). Летом 2026 писали, что «Лента» смотрит покупку — сделка не подтверждена и цифры года не даёт. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+          <t>Прогноза продаж на 2026 нет. Последнее: отчёт за 2025 — 127,5 млрд, на 5% больше, чем годом раньше. На 1 июля 2026 — 1 303 магазина (это штуки, не деньги). Летом 2026 писали, что «Лента» смотрит покупку — сделка не подтверждена и цифры года не даёт. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1609,11 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. В списках возможных покупок 2026–2028 (Совкомбанк) — без суммы продаж. Последнее открытое: около 100 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="78" customHeight="1" s="6">
+          <t>Прогноза продаж на 2026 нет. В списках возможных покупок 2026–2028 (Совкомбанк) — без суммы продаж. Последнее открытое: около 100 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1" s="6">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Винлаб (ПАО ВинЛаб / Novabev)</t>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт 24 августа 2026: за полгода 51,2 млрд (+7,2%), прибыль 0,79 млрд (1,5% от продаж — полторы копейки с рубля), точек 2 225 на 30 июня (2 222 на 30 сентября). Оценка года, если темп полугодия удержится: 95,1 × 1,072. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это не та выручка, что в таблице. https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
+          <t>Официальный отчёт 24 августа 2026: за полгода 51,2 млрд — на 7,2% больше, чем годом раньше, прибыль 0,79 млрд (1,5% от продаж — полторы копейки с рубля), точек 2 225 на 30 июня (2 222 на 30 сентября). Оценка года, если темп полугодия удержится: 95,1 × 1,072. Отдельно компания хвалится продажами с налогом за девять месяцев (на 24% больше) — это не те продажи, что в таблице. https://corp.winelab.ru/ru/press-center/news-and-press-releases/vyruchka-vinlab-vyrosla-na-7-2-i-prevysila-51-mlrd-rubley-v-pervom-polugodii-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. Упоминается рядом с «Победой», «Ярче» и «Командором» как сеть, которую крупный игрок может купить. Последнее: 31,3 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
+          <t>Прогноза на 2026 нет. Упоминается рядом с «Победой», «Ярче» и «Командором» как сеть, которую крупный игрок может купить. Последнее открытое: 31,3 млрд за 2025. https://iz.ru/2152177/denis-kuznetcov/lenta-mozhet-poglotit-krupneyshego-riteylera-sibiri</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — выручка 2025. Российский отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей +9–11% за год) — не прогноз именно этой сети.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали — ни в конце 2025, ни в начале 2026. Последняя открытая цифра — продажи за 2025. Отчёт за 2026 выйдет весной 2027. Общий фон рынка (десять крупнейших сетей за год плюс 9–11%) — не прогноз именно этой сети.</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>За какой кусок года</t>
+          <t>За какой период</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Рост к тому же куску 2025, %</t>
+          <t>Рост к тому же периоду 2025, %</t>
         </is>
       </c>
       <c r="F1" s="11" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="H1" s="11" t="inlineStr">
         <is>
-          <t>Прибыль за тот же кусок, млрд ₽</t>
+          <t>Прибыль за тот же период, млрд ₽</t>
         </is>
       </c>
       <c r="I1" s="11" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" s="6">
+    <row r="3" ht="74" customHeight="1" s="6">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Русагро</t>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт: за полгода 183,0 млрд (+9,1%). Прибыль почти ноль: 56 миллионов рублей, это 0,056 млрд — меньше одной десятой копейки с рубля продаж. У растениеводства и сахара осень обычно сильнее весны, поэтому полугодие на два не умножали. Оценка года, если темп удержится: 396,5 × 1,091. https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
+          <t>Официальный отчёт: за полгода 183,0 млрд — на 9,1% больше, чем годом раньше. Прибыль почти ноль: 56 миллионов рублей, это 0,056 млрд — меньше одной десятой копейки с рубля продаж. У растениеводства и сахара осень обычно сильнее весны, поэтому полугодие на два не умножали. Оценка года, если тот же темп удержится: 396,5 × 1,091. https://www.rusagrogroup.ru/fileadmin/files/reports/ru/pdf/Rusagro_Group_PJSC_IFRS_6m_2026_RUS.pdf</t>
         </is>
       </c>
     </row>
@@ -2758,11 +2758,11 @@
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
-          <t>Цифры на 2026 нет. На 2025 сами планировали 440 млрд — не получилось (факт 344, рост ноль). Весной 2026 руководство: новые заводы начнут себя окупать в 2026–2027, ждут рост продаж и прибыли — без конкретной суммы. https://abireg.ru/newsitem/113897/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="76" customHeight="1" s="6">
+          <t>Цифр на 2026 нет. На 2025 сами планировали 440 млрд — не получилось (факт 344, рост ноль). Весной 2026 руководство: новые заводы начнут себя окупать в 2026–2027, ждут рост продаж и прибыли — без конкретной суммы. https://abireg.ru/newsitem/113897/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="79" customHeight="1" s="6">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>АПХ Мираторг</t>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>Полной выручки за январь–июнь 2026 в открытом виде нет. Глава компании Виктор Линник в июне на Петербургском экономическом форуме: ждать рост продаж «на несколько процентов»; продажи за границу удержать около 58 млрд, как в 2025 (план +20% сняли — рубль слишком крепкий). Оценка года ≈ 342 × 1,03. Прибыль за полгода 19,61 млрд (+26%) — это не выручка. https://echomsk.spb.ru/nws/5317198-miratorg-ogidaet-neznachitelnyj-rost-vyruchki-po-itogam-2026-goda.html</t>
+          <t>Полных продаж за январь–июнь 2026 в открытом виде нет. Глава компании Виктор Линник в июне на Петербургском экономическом форуме: ждать рост продаж «на несколько процентов»; продажи за границу удержать около 58 млрд, как в 2025 (план «плюс 20%» сняли — рубль слишком крепкий). Оценка года примерно 342 × 1,03. Прибыль за полгода 19,61 млрд — на 26% больше, чем годом раньше. Это не продажи. https://echomsk.spb.ru/nws/5317198-miratorg-ogidaet-neznachitelnyj-rost-vyruchki-po-itogam-2026-goda.html</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. Агентство INFOLine берёт KDV как пример торможения: уже 2025 только +1%, а в 2026 у крупных производителей еды рост «около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="77" customHeight="1" s="6">
+          <t>Прогноза на 2026 нет. Агентство INFOLine берёт KDV как пример торможения: уже 2025 только на 1% больше, а в 2026 у крупных производителей еды рост «около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="79" customHeight="1" s="6">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Черкизово</t>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт: за полгода 141,6 млрд (+3,5%). Прибыль за те же полгода 14,1 млрд — почти 10 копеек с каждого рубля продаж. Свой прогноз в рублях на год компания не давала — только «продолжим увеличивать выручку», деньги на стройки в 2026 снова режут. Независимая оценка на сайте для инвесторов: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
+          <t>Официальный отчёт: за полгода 141,6 млрд — на 3,5% больше, чем годом раньше. Прибыль за те же полгода 14,1 млрд — почти 10 копеек с каждого рубля продаж. Свой прогноз в рублях на год компания не давала — только «продолжим увеличивать продажи», деньги на стройки в 2026 снова режут. Независимая оценка на сайте для инвесторов: 305–315 млрд за год (это не отчёт компании). В ячейке оценки — 288,7 × 1,035. https://cherkizovo-group.com/press/gruppa-cherkizovo-obyavlyaet-finansovye-rezultaty-za-2025-god/</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>Выручки и прогноза по России на 2026 нет. Оценка аналитиков по всей мировой Nestlé: рост продаж около 3,5–3,7% за год — не российская цифра. https://www.nestle.com/sites/default/files/2026-10/nestle-sa-consensus-pre-Q32026.pdf</t>
+          <t>Продаж и прогноза по России на 2026 нет. Оценка аналитиков по всей мировой Nestlé: рост продаж около 3,5–3,7% за год — не российская цифра. https://www.nestle.com/sites/default/files/2026-10/nestle-sa-consensus-pre-Q32026.pdf</t>
         </is>
       </c>
     </row>
@@ -3058,11 +3058,11 @@
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза выручки по России на 2026 не публиковали.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="57" customHeight="1" s="6">
+          <t>Своего прогноза продаж по России на 2026 не публиковали.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1" s="6">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Продимекс (сумма предприятий группы)</t>
@@ -3110,11 +3110,11 @@
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 не было. Открытое — сумма заводов за 2025 (около 220–224 млрд, считают по-разному). Российский отчёт за 2026 выйдет весной 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="57" customHeight="1" s="6">
+          <t>Прогноза продаж на 2026 не было. Открытое — сумма заводов за 2025 (около 220–224 млрд, считают по-разному). Отчёт за 2026 выйдет весной 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="59" customHeight="1" s="6">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Агропромкомплектация</t>
@@ -3162,11 +3162,11 @@
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>Прогноза всей группы на 2026 нет. Агентство INFOLine за 2025: 204,4 млрд (+15%). Отдельные компании группы (АПК-Курск и другие) отчитываются раз в год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="71" customHeight="1" s="6">
+          <t>Прогноза всей группы на 2026 нет. Агентство INFOLine за 2025: 204,4 млрд — на 15% больше, чем годом раньше. Отдельные компании группы (АПК-Курск и другие) отчитываются раз в год.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="73" customHeight="1" s="6">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Логика молока (ex-Danone / Health&amp;Nutrition)</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Сама компания 16 июля 2026: за полгода продали на 84,5 млрд (+3,5%), молочки 510 тысяч тонн (+2,7%). Ориентир на год — не деньги, а «сделать больше 1 миллиона тонн готовой продукции». На стройки и оборудование до 2030 заложили 120 млрд. Оценка рублей на год: 167,1 × 1,035. https://logikamoloka.ru/press-centr/news/logika-moloka-podvodit-rezultaty-i-polugodiya-2026-goda/</t>
+          <t>Сама компания 16 июля 2026: за полгода продали на 84,5 млрд — на 3,5% больше, чем годом раньше, молочки 510 тысяч тонн (на 2,7% больше). Ориентир на год — не деньги, а «сделать больше 1 миллиона тонн готовой продукции». На стройки и оборудование до 2030 заложили 120 млрд. Оценка рублей на год: 167,1 × 1,035. https://logikamoloka.ru/press-centr/news/logika-moloka-podvodit-rezultaty-i-polugodiya-2026-goda/</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>Выручки 2026 нет. План без суммы: пиво — больше 30% рынка, напитки без алкоголя — больше 8% продаж за первое полугодие, 700 миллионов в завод в Саранске в 2026. https://napitkivmeste.ru/odin-god-pod-brendom-napitki-vmeste-bolee-30-novyh-produktov-i-rekordnye-vlozheniya-v-zavody/</t>
+          <t>Продаж за 2026 нет. План без суммы: пиво — больше 30% рынка, напитки без алкоголя — больше 8% продаж за первое полугодие, 700 миллионов в завод в Саранске в 2026. https://napitkivmeste.ru/odin-god-pod-brendom-napitki-vmeste-bolee-30-novyh-produktov-i-rekordnye-vlozheniya-v-zavody/</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. В 2025 выпуск пива упал на 16% — компания сама сказала, что так и задумала: обновляли заводы. Это про прошлый год, не про 2026. https://www.kommersant.ru/doc/8401281</t>
+          <t>Прогноза продаж на 2026 нет. В 2025 выпуск пива упал на 16% — компания сама сказала, что так и задумала: обновляли заводы. Это про прошлый год, не про 2026. https://www.kommersant.ru/doc/8401281</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. После убытка 2025 (около 4,2 млрд) группа сама сказала: новые большие стройки пока не начинаем, сначала надо выйти в плюс; точечно около 500 миллионов в Томскую птицефабрику. https://www.akm.ru/news/gruppa_kompaniy_sibagro_narastila_vyruchku_na_14_odnako_zakonchila_2025_god_s_chistym_ubytkom/</t>
+          <t>Прогноза продаж на 2026 нет. После убытка 2025 (около 4,2 млрд) группа сама сказала: новые большие стройки пока не начинаем, сначала надо выйти в плюс; точечно около 500 миллионов в Томскую птицефабрику. https://www.akm.ru/news/gruppa_kompaniy_sibagro_narastila_vyruchku_na_14_odnako_zakonchila_2025_god_s_chistym_ubytkom/</t>
         </is>
       </c>
     </row>
@@ -3466,11 +3466,11 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза выручки на 2026 не публиковали. Последнее: около 88 млрд за 2025 (агентство INFOLine).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="61" customHeight="1" s="6">
+          <t>Своего прогноза продаж на 2026 не публиковали. Последнее: около 88 млрд за 2025 (агентство INFOLine).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1" s="6">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Дамате</t>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>Пресс-служба 7 сентября 2026: за полгода 46,3 млрд (+19%). Оценка года: 82,8 × 1,19. https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
+          <t>Пресс-служба 7 сентября 2026: за полгода 46,3 млрд — на 19% больше, чем годом раньше. Оценка года: 82,8 × 1,19. https://www.acdamate.com/press-center/press/vyruchka-damate-v-i-polugodii-2026-goda-vyrosla-na-19-i-prevysila-46-mlrd-rubley/</t>
         </is>
       </c>
     </row>
@@ -3564,11 +3564,11 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. Агентство INFOLine отмечает группу среди быстрорастущих молочников 2025, без цифры на этот год. Последнее: только молочная часть 63,1 млрд за 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1" s="6">
+          <t>Прогноза продаж на 2026 нет. Агентство INFOLine отмечает группу среди быстрорастущих молочников 2025, без цифры на этот год. Последнее: только молочная часть 63,1 млрд за 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="53" customHeight="1" s="6">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Орими Трейд (Tess, Greenfield, Jardin)</t>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза по России на 2026 не публиковали. Последнее: 62,3 млрд за 2025.</t>
+          <t>Своего прогноза по России на 2026 не публиковали. Последнее открытое: 62,3 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3762,11 +3762,11 @@
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт за полгода: 24,63 млрд — на 6,4% меньше, чем 26,31 годом раньше. Прибыль 1,99 млрд (−40% к прошлому году) — это 8,1% от продаж. Оценка года: 56,4 × 0,936. Свинины в тоннах сделали на 10% больше, но она подешевела. https://www.tbank.ru/invest/social/profile/Marten_Resting/cbc77ff8-2a7f-49ae-8534-59a60c86da65/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="55" customHeight="1" s="6">
+          <t>Официальный отчёт за полгода: 24,63 млрд — на 6,4% меньше, чем 26,31 годом раньше. Прибыль 1,99 млрд (на 40% меньше, чем год назад) — это 8,1% от продаж. Оценка года: 56,4 × 0,936. Свинины в тоннах сделали на 10% больше, но она подешевела. https://www.tbank.ru/invest/social/profile/Marten_Resting/cbc77ff8-2a7f-49ae-8534-59a60c86da65/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="57" customHeight="1" s="6">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Прогресс (ФрутоНяня / Малышам)</t>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. В марте 2026 вышел отчёт за 2025: выручка 52,1 (+8%), прибыль 10,2. https://www.kommersant.ru/doc/8552221</t>
+          <t>Прогноза на 2026 нет. В марте 2026 вышел отчёт за 2025: продажи 52,1 млрд — на 8% больше, чем годом раньше, прибыль 10,2. https://www.kommersant.ru/doc/8552221</t>
         </is>
       </c>
     </row>
@@ -3866,11 +3866,11 @@
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. Июль 2026: до 2028 вложат около 13 млрд в новые линии (белки из молока и другие ингредиенты) — это деньги на стройку, не «сколько продадут за год». https://milknews.ru/index/molochnye-produkty/molvest-13-mlrd-investicii.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="56" customHeight="1" s="6">
+          <t>Прогноза продаж на 2026 нет. Июль 2026: до 2028 вложат около 13 млрд в новые линии (белки из молока и другие ингредиенты) — это деньги на стройку, не «сколько продадут за год». https://milknews.ru/index/molochnye-produkty/molvest-13-mlrd-investicii.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="57" customHeight="1" s="6">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Эссен Продакшн (Махеевъ)</t>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>Прогноза выручки на 2026 нет. У кондитеров в целом дорогое какао и упаковка — без цифры именно этой компании. Последнее: 50,2 млрд за 2025.</t>
+          <t>Прогноза продаж на 2026 нет. У кондитеров в целом дорогое какао и упаковка — без цифры именно этой компании. Последнее открытое: 50,2 млрд за 2025.</t>
         </is>
       </c>
     </row>
@@ -3970,11 +3970,11 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1" s="6">
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="66" customHeight="1" s="6">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Сады Придонья</t>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>Выручку 2026 в деньгах не публиковали. За январь–март продали на 7,5% больше в тоннах, бренды «Сады Придонья» +11%, Nemoloko +19%. Прогноза в рублях на год нет. https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
+          <t>Продажи 2026 в деньгах не публиковали. За январь–март продали на 7,5% больше в тоннах, бренды «Сады Придонья» — на 11% больше, Nemoloko — на 19% больше. Прогноза в рублях на год нет. https://companies.rbc.ru/news/kwQXFC9CLJ/kak-sadyi-pridonya-adaptiruyutsya-v-usloviyah-ryinochnoj-neopredelennosti/</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4230,11 +4230,11 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="67" customHeight="1" s="6">
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="68" customHeight="1" s="6">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>ГК ЭкоНива (молочный контур рейтинга)</t>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>Официальный отчёт всей группы за полгода: 45,2 млрд (−2,8%), прибыль 1,1 млрд — 2,4% от продаж всей группы. Это ВСЯ компания, а не только молочная часть, которую агентство INFOLine считало за 2025 (29,8). С 29,8 сравнивать нельзя. Оценку года только для молочки не ставили. https://abireg.ru/newsitem/116916/</t>
+          <t>Официальный отчёт всей группы за полгода: 45,2 млрд — на 2,8% меньше, чем годом раньше, прибыль 1,1 млрд — 2,4% от продаж всей группы. Это вся компания, а не только молочная часть, которую агентство INFOLine считало за 2025 (29,8). С 29,8 сравнивать нельзя. Оценку года только для молочки не ставили. https://abireg.ru/newsitem/116916/</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="J61" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="J64" s="13" t="inlineStr">
         <is>
-          <t>Своего прогноза «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Российский отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="D1" s="17" t="inlineStr">
         <is>
-          <t>За какой кусок года</t>
+          <t>За какой период</t>
         </is>
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>Рост к тому же куску 2025, %</t>
+          <t>Рост к тому же периоду 2025, %</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="H1" s="17" t="inlineStr">
         <is>
-          <t>Прибыль за тот же кусок, млрд ₽</t>
+          <t>Прибыль за тот же период, млрд ₽</t>
         </is>
       </c>
       <c r="I1" s="17" t="inlineStr">
@@ -5933,7 +5933,7 @@
       <c r="I2" s="17" t="n"/>
       <c r="J2" s="17" t="n"/>
     </row>
-    <row r="3" ht="83" customHeight="1" s="6">
+    <row r="3" ht="85" customHeight="1" s="6">
       <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Семишагофф (ООО ТК Прогресс)</t>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="J3" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 компания не публиковала. Последний закрытый год — весь 2025: 70,67 млрд (+29%), прибыль 0,955 млрд, маржа 1,4 копейки с рубля. К 2025–началу 2026 около 190 магазинов. В 2025 купили склад в Шушарах почти на 1,5 млрд — это не «сворачиваемся». В августе 2026 агентство INFOLine: с метра площади в 2025-м впервые больше 1 млн рублей, второе место в стране после «Азбуки вкуса». Сигнал для ИТ на 2026–27: резать незачем. Сеть растёт, склад свой, кассы и учёт будут нужны на большом обороте. https://checko.ru/company/tk-progress-1127847102338</t>
+          <t>За 2026 продаж компания не публиковала. Что есть — весь 2025: 70,67 млрд рублей, на 29% больше, чем годом раньше. После расходов осталось 955 миллионов — это 1,4 копейки с каждого рубля. К началу 2026 около 190 магазинов. В 2025 купили склад в Шушарах почти за 1,5 млрд — так не делают, если собираются сворачиваться. В августе 2026 агентство INFOLine: с квадратного метра в 2025-м впервые больше миллиона рублей, второе место в стране после «Азбуки вкуса». Для ИТ это значит: резать незачем. Сеть растёт, склад свой, кассы и учёт будут нужны. https://checko.ru/company/tk-progress-1127847102338</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="88" customHeight="1" s="6">
+    <row r="5" ht="90" customHeight="1" s="6">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Лама (SPAR / Первоцен / F City; сумма 4 юрлиц)</t>
@@ -6079,11 +6079,11 @@
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — сумма четырёх магазинных юрлиц за 2025: 5,6 + 7 + 8,7 + 11 = 32,3 млрд, прибыль 0,335 млрд, маржа около 1 копейки с рубля. Управляющую «Ламу» (134 млн) с магазинами не складывали. ФАС 20 октября 2025 согласовала, чтобы «Лама» полностью управляла SPAR, «Первоценом» и F City в Томской и Новосибирской областях. У самой «Ламы» тогда 103 магазина. Сигнал для ИТ на 2026–27: скорее потратят на склейку касс, справочников и склада после сделки, чем выкинут систему. Своего «в 2026 продадим на столько-то» не было. https://retailer.ru/fas-soglasovala-pokupku-lamoj-seti-spar-v-tomskoj-i-novosibirskoj-oblastjah/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="81" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — сумма четырёх магазинных компаний за 2025: 5,6 + 7 + 8,7 + 11 = 32,3 млрд рублей. После расходов осталось 335 миллионов — около одной копейки с рубля. Управляющую компанию «Лама» (134 млн) с магазинами не складывали. 20 октября 2025 антимонопольная служба разрешила «Ламе» полностью управлять SPAR, «Первоценом» и F City в Томской и Новосибирской областях. Тогда у «Ламы» было 103 магазина. Для ИТ это значит: скорее потратят на то, чтобы склеить кассы, справочники и склад после сделки, чем выкинут систему. Своего плана «в 2026 продадим на столько-то» не было. https://retailer.ru/fas-soglasovala-pokupku-lamoj-seti-spar-v-tomskoj-i-novosibirskoj-oblastjah/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="79" customHeight="1" s="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Аникс (ТС Аникс + Прайд-А)</t>
@@ -6129,11 +6129,11 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — два юрлица за 2025: 18,3 + 13,0 = 31,3 млрд, прибыль 0,414 млрд, маржа 1,3 копейки с рубля. Своих магазинов 165, ещё 109 франшиза «Корзинка». В 2025 прибыль выросла. Своего плана продаж на 2026 не публиковали. Сигнал для ИТ: живой региональный игрок с прибылью, не «режим выживания». Но и программы «тратим на цифру столько-то» нет — бюджет ИТ в рублях никто не раскрывал. https://tolknews.ru/ekonomika/214569-skolko-zarabotali-krupneyshie-seti-altaya-mariya-ra-i-aniks-v-godu</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — две компании за 2025: 18,3 + 13,0 = 31,3 млрд рублей. После расходов осталось 414 миллионов — 1,3 копейки с рубля. Своих магазинов 165, ещё 109 работают как франшиза «Корзинка». В 2025 прибыль выросла. Плана продаж на 2026 не публиковали. Для ИТ это значит: сеть живая и с прибылью, не экономит на всём. Но сколько именно тратят на ИТ — никто не говорит. https://tolknews.ru/ekonomika/214569-skolko-zarabotali-krupneyshie-seti-altaya-mariya-ra-i-aniks-v-godu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="82" customHeight="1" s="6">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Европа (ООО Европа, Курск)</t>
@@ -6179,11 +6179,11 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 31 млрд (+2,7%), прибыль 1,1 млрд, маржа 3,6 копейки с рубля — для продуктов густо. Директор: 47 магазинов (34 гипер, 7 супер, 6 у дома). На сайте компании «около 60 предприятий». Рост продаж слабый. Своего прогноза на 2026 нет. Сигнал для ИТ: сеть на ногах и не продаётся федералам (слова директора). Больших строек и «режем всё» в открытом виде тоже нет — скорее держат текущие системы. https://www.audit-it.ru/contragent/1074632016205_ooo-evropa</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 31 млрд рублей, на 2,7% больше, чем годом раньше. После расходов осталось 1,1 млрд — 3,6 копейки с рубля, для продуктов это много. Директор говорит: 47 магазинов (34 больших, 7 супермаркетов, 6 у дома). На сайте компании «около 60 предприятий». Продажи почти не растут. Прогноза на 2026 нет. Для ИТ это значит: сеть на ногах и, по словам директора, федералам не продаётся. Больших строек и «режем всё» тоже не видно — скорее держат то, что уже есть. https://www.audit-it.ru/contragent/1074632016205_ooo-evropa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1" s="6">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Бегемаг / SPAR Кузбасс (ООО Универсамы Бегемаг)</t>
@@ -6229,11 +6229,11 @@
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 12,87 млрд (+1%), прибыль всего 65 млн, маржа полкопейки с рубля. На начало 2026: 74 магазина, закрытий не было. В 2025 новые точки почти не открывали: эффективность, аренда, тарифы. Запустили SPAR-Express и кассы самообслуживания. Июль 2026: в нацпроекте «Производительность труда» — торты пекут вдвое быстрее, выработка на человека +27%. Сигнал для ИТ: не на открытие сети, а на то, что режет издержки (самообслуживание, бережливое производство). Большой «бюджет на цифровизацию» не обещали. https://www.retail.ru/articles/kak-rosli-riteylery-v-2025-godu-ekspansiya-optimizatsiya-i-znachimye-resheniya-vedushchikh-setey/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="73" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 12,87 млрд рублей, почти как годом раньше (на 1% больше). После расходов осталось всего 65 миллионов — полкопейки с рубля. На начало 2026: 74 магазина, закрытий не было. В 2025 новые точки почти не открывали: смотрели эффективность, аренду, тарифы. Запустили SPAR-Express и кассы, где покупатель бьёт товар сам. В июле 2026 участвовали в нацпроекте «Производительность труда»: торты пекут вдвое быстрее, один человек делает на 27% больше. Для ИТ это значит: деньги не на новые магазины, а на то, что снижает расходы. Большого «тратим на программы» не обещали. https://www.retail.ru/articles/kak-rosli-riteylery-v-2025-godu-ekspansiya-optimizatsiya-i-znachimye-resheniya-vedushchikh-setey/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1" s="6">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Низкоцен (ООО Холлифуд)</t>
@@ -6279,11 +6279,11 @@
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 9,5 млрд (−2%), прибыль 61 млн, маржа 0,6 копейки с рубля. На сайте 71 магазин, новые объекты ищут. Сигнал для ИТ: осторожно. Продажи уже не росли, маржа тонкая. Скорее заморозка лишнего, чем новая платформа. Своего плана на 2026 нет. https://ksonline.ru/605083/skolko-zarabotali-krupnye-sibirskie-produktovye-seti-v-2025-godu/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 9,5 млрд рублей, на 2% меньше, чем годом раньше. После расходов осталось 61 миллион — 0,6 копейки с рубля. На сайте 71 магазин, новые помещения ищут. Для ИТ это значит: осторожно. Продажи уже не росли, прибыли мало. Скорее заморозят лишнее, чем купят новую платформу. Своего плана на 2026 нет. https://ksonline.ru/605083/skolko-zarabotali-krupnye-sibirskie-produktovye-seti-v-2025-godu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="73" customHeight="1" s="6">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>OFFPRICE (ООО Оффпрайс)</t>
@@ -6329,11 +6329,11 @@
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>Это не продукты. Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 4,85 млрд (+1,8%), прибыль 0,113 млрд, маржа 2,3 копейки с рубля. На сайте «30+ аутлетов»; вы называли 40. Рост почти остановился. Сигнал для ИТ: слабый рост, не FMCG. Большого «режем / строим» в открытом виде нет. https://firmoteka.ru/7725844967</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1" s="6">
+          <t>Это одежда, не продукты. За 2026 продаж нет. Что есть — весь 2025: 4,85 млрд рублей, на 1,8% больше, чем годом раньше. После расходов осталось 113 миллионов — 2,3 копейки с рубля. На сайте «30+ аутлетов»; вы называли 40. Рост почти остановился. Для ИТ это значит: слабый рост, и это не продуктовая сеть. Ни «режем», ни «строим» в открытом виде не видно. https://firmoteka.ru/7725844967</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="79" customHeight="1" s="6">
       <c r="A11" s="18" t="inlineStr">
         <is>
           <t>КЗВС (вет. аптеки, Краснодарский край)</t>
@@ -6379,11 +6379,11 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — ООО «КЗВС» весь 2025: 1,13 млрд (+2,6%), прибыль 0,108 млрд, маржа почти 10 копеек с рубля — для розницы жирно. На сайте 200 вет. аптек, в штате юрлица 92 человека: часть точек, скорее всего, партнёры. Сигнал для ИТ: маржа позволяет не резать всё подряд, но это одно юрлицо, не холдинг. Своего плана «в 2026 откроем столько-то» не нашли. https://www.testfirm.ru/result/2312208833_ooo-kzvs</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="74" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — ООО «КЗВС» за весь 2025: 1,13 млрд рублей, на 2,6% больше, чем годом раньше. После расходов осталось 108 миллионов — почти 10 копеек с рубля, для розницы это много. На сайте 200 вет. аптек, в штате этой компании 92 человека: часть точек, скорее всего, партнёры. Для ИТ это значит: прибыль позволяет не резать всё подряд, но это одна компания, не большая группа. Плана «в 2026 откроем столько-то» не нашли. https://www.testfirm.ru/result/2312208833_ooo-kzvs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" s="6">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>АО «Иркутская аптека»</t>
@@ -6429,14 +6429,14 @@
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 1,1 млрд (−2%), убыток 4,5 млн. На 1 января 2026 — 43 точки (вы называли 44). Городская сеть, в 2025-м из МУП сделали АО. Сигнал для ИТ на 2026–27: скорее заморозка и обязательные госсистемы, чем новая коммерческая платформа. Убыток и муниципальный хозяин — плохой фон для лишних проектов. https://ircity.ru/text/business/2026/09/07/76621885/</t>
+          <t>За 2026 продаж нет. Что есть — весь 2025: 1,1 млрд рублей, на 2% меньше, чем годом раньше. После расходов минус 4,5 миллиона — сеть в убытке. На 1 января 2026 — 43 точки (вы называли 44). Это городская сеть: в 2025-м из муниципального предприятия сделали акционерное общество. Для ИТ на 2026–27 это значит: скорее заморозка и обязательные государственные системы, чем новая коммерческая программа. Убыток и город как хозяин — плохой фон для лишних проектов. https://ircity.ru/text/business/2026/09/07/76621885/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" s="6">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Заводы поменьше: 2026 почти не раскрывают, смотрим стройки и прибыль 2025</t>
+          <t>Заводы поменьше: продаж за 2026 почти нет, смотрим стройки и прибыль 2025</t>
         </is>
       </c>
       <c r="B13" s="17" t="n"/>
@@ -6449,7 +6449,7 @@
       <c r="I13" s="17" t="n"/>
       <c r="J13" s="17" t="n"/>
     </row>
-    <row r="14" ht="79" customHeight="1" s="6">
+    <row r="14" ht="81" customHeight="1" s="6">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Любятово (ООО; ГК Черноголовка)</t>
@@ -6495,11 +6495,11 @@
       </c>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 13,2 млрд (+25%), прибыль 0,847 млрд, маржа 6,4 копейки с рубля. Площадки: Воронеж, Псков, Вязьма. Февраль 2026: в Воронеже обсуждали производственно-складской комплекс, в прессе оценка около 4 млрд. Сентябрь 2026: в Вязьме — новые линии и склад на 2026–2027. Сигнал для ИТ: капекс точно не режут. Заводу, который строит корпус и склад, учёт и линии будут нужны. Это не прогноз выручки на год. https://www.kommersant.ru/doc/8476994</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="78" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 13,2 млрд рублей, на 25% больше, чем годом раньше. После расходов осталось 847 миллионов — 6,4 копейки с рубля. Площадки: Воронеж, Псков, Вязьма. В феврале 2026 в Воронеже обсуждали новый производственно-складской комплекс, в прессе оценка около 4 млрд. В сентябре 2026 в Вязьме — новые линии и склад на 2026–2027. Для ИТ это значит: стройки не режут. Заводу, который ставит корпус и склад, учёт и линии будут нужны. Это не прогноз продаж на год. https://www.kommersant.ru/doc/8476994</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="82" customHeight="1" s="6">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Иркутский масложиркомбинат</t>
@@ -6545,11 +6545,11 @@
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 16,35 млрд (−0,9%), прибыль 2,33 млрд. Маржа 14 копеек с рубля, но заметная часть — проценты по деньгам на счетах, не от продажи масла. Агентство INFOLine, сентябрь 2026: у крупных производителей еды рост «около нуля» — это рынок, не этот завод. Сигнал для ИТ: денег после 2025 много, своего плана строек на 2026 не нашли. Не «режим порезок», но и не анонс цифры. https://finscanner.ru/company/3811185573/finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="68" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 16,35 млрд рублей, почти как годом раньше (на 0,9% меньше). После расходов осталось 2,33 млрд. Это 14 копеек с рубля, но заметная часть — проценты по деньгам на счетах, не от продажи масла. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не этот завод. Для ИТ это значит: денег после 2025 много, своего плана строек на 2026 не нашли. Не похоже на режим порезок, но и анонса «тратим на программы» нет. https://finscanner.ru/company/3811185573/finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1" s="6">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Каравай (ОАО, Санкт-Петербург)</t>
@@ -6595,11 +6595,11 @@
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 11,12 млрд (+15%), прибыль 0,709 млрд, маржа 6,4 копейки с рубля. Не путать с ангарским «Караваем». Сигнал для ИТ: 2025 прибыльный. Своего плана на 2026 нет. По рынку заводов рост около нуля. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="67" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 11,12 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 709 миллионов — 6,4 копейки с рубля. Есть ещё ангарский «Каравай» — это другая компания, сюда не относится. Для ИТ это значит: 2025 был прибыльным. Своего плана на 2026 нет. По рынку заводов рост около нуля. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="69" customHeight="1" s="6">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>СМАК (АО, Екатеринбург)</t>
@@ -6645,11 +6645,11 @@
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 9,79 млрд (+18%), прибыль 1,11 млрд, маржа 11 копеек с рубля. Три площадки, включая Раменское. Сигнал для ИТ: маржа высокая, 2025 сильный. Своего «в 2026 продадим на столько-то» нет. https://www.smakhleb.ru/predpriyatie</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="70" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 9,79 млрд рублей, на 18% больше, чем годом раньше. После расходов осталось 1,11 млрд — 11 копеек с рубля. Три площадки, включая Раменское. Для ИТ это значит: прибыль высокая, 2025 сильный. Своего «в 2026 продадим на столько-то» нет. https://www.smakhleb.ru/predpriyatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1" s="6">
       <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Лимак (АО, Липецк)</t>
@@ -6695,11 +6695,11 @@
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 8,93 млрд (+8%), прибыль 0,22 млрд, маржа 2,5 копейки с рубля — для хлеба скромно. Девять хлебозаводов плюс мельница. Сигнал для ИТ: сеть площадок живая, но маржа тонкая. Лишнего ИТ без окупаемости, скорее всего, не купят. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="66" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 8,93 млрд рублей, на 8% больше, чем годом раньше. После расходов осталось 220 миллионов — 2,5 копейки с рубля, для хлеба скромно. Девять хлебозаводов плюс мельница. Для ИТ это значит: площадки живые, но прибыли мало. Лишний софт без понятной экономии, скорее всего, не купят. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="67" customHeight="1" s="6">
       <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Первый хлебокомбинат (АО, Челябинск)</t>
@@ -6747,11 +6747,11 @@
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 8,00 млрд (+10%), прибыль 1,16 млрд, маржа 14,5 копейки с рубля. Сколько площадок — не нашли. Сигнал для ИТ: прибыль 2025 большая, плана 2026 нет. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="73" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 8,00 млрд рублей, на 10% больше, чем годом раньше. После расходов осталось 1,16 млрд — 14,5 копейки с рубля. Сколько площадок — не нашли. Для ИТ это значит: прибыль 2025 большая, плана на 2026 нет. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1" s="6">
       <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Вологодское мороженое (ООО)</t>
@@ -6797,11 +6797,11 @@
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 6,63 млрд (−7%), прибыль 2,78 млрд, маржа 42 копейки с рубля — для мороженого необычно много, причину компания не объясняла. Сигнал для ИТ: продажи падали, прибыль огромная. На «режем ИТ из-за дыры» не похоже, на «строим новую цифру» тоже ничего не анонсировали. https://nalogovaya.ru/egrul/companies/1033500071505/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="66" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 6,63 млрд рублей, на 7% меньше, чем годом раньше. После расходов осталось 2,78 млрд — 42 копейки с рубля. Для мороженого это необычно много, причину компания не объясняла. Для ИТ это значит: продажи падали, но дыры в деньгах нет. На «режем ИТ из-за убытка» не похоже, на «строим новую систему» тоже ничего не анонсировали. https://nalogovaya.ru/egrul/companies/1033500071505/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="68" customHeight="1" s="6">
       <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Покровский хлеб (АО, Пермь)</t>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t>Выручки за кусок 2026 нет. Последний закрытый год — весь 2025: 5,5 млрд (+17%), прибыль 0,82 млрд, маржа почти 15 копеек с рубля. Три пермских завода. Сигнал для ИТ: 2025 сильный. Своего плана капекса на 2026–27 не нашли. https://www.kommersant.ru/doc/8552543</t>
+          <t>За 2026 продаж нет. Что есть — весь 2025: 5,5 млрд рублей, на 17% больше, чем годом раньше. После расходов осталось 820 миллионов — почти 15 копеек с рубля. Три завода в Перми. Для ИТ это значит: 2025 сильный. Своего плана строек на 2026–27 не нашли. https://www.kommersant.ru/doc/8552543</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       <c r="I22" s="17" t="n"/>
       <c r="J22" s="17" t="n"/>
     </row>
-    <row r="23" ht="76" customHeight="1" s="6">
+    <row r="23" ht="80" customHeight="1" s="6">
       <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Дружба (Рыбинск, Ярославская область)</t>
@@ -6913,11 +6913,11 @@
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t>Сводной выручки сети нет — ни за 2026, ни за 2025. Сайт: 28 точек, 12 500 м², 1 700 человек. Юрлицо ООО «Дружба» (66 млн и 14 человек) — не эта сеть, в таблицу не ставили. Июнь 2026: закрывают гипермаркет в ТЦ «Космос» (работал ~15 лет), дата около 20 июля. Сигнал для ИТ: сжимаются, не расширяются. Новый дорогой софт на этом фоне маловероятен. https://ngs76.ru/gorod/v-rybinske-zakroetsya-gipermarket-druzhba-magazin-prorabotal-15-let-id341441/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="72" customHeight="1" s="6">
+          <t>Сводных продаж сети нет — ни за 2026, ни за 2025. Сайт: 28 точек, 12 500 квадратных метров, 1 700 человек. Есть ООО «Дружба» с 66 миллионами выручки и 14 людьми — это не эта сеть, в таблицу не ставили. В июне 2026 объявили, что закрывают гипермаркет в ТЦ «Космос» (работал около 15 лет), дата около 20 июля. Для ИТ это значит: сеть сжимается, не расширяется. Новый дорогой софт на этом фоне маловероятен. https://ngs76.ru/gorod/v-rybinske-zakroetsya-gipermarket-druzhba-magazin-prorabotal-15-let-id341441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="71" customHeight="1" s="6">
       <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Ёвар (Таджикистан)</t>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>Выручки в открытом виде нет. Октябрь 2025: сеть писала про 30 супермаркетов и новый зал в City Mall. Вы называли 62 — 62 в открытых текстах не подтвердили. Сигнал для ИТ: по словам самой сети — расширение географии, не сжатие. Суммы и ИТ-бюджет неизвестны. https://koinotinav.tj/news/set-supermarketov-evar-ukreplyaet-pozicii-i-rasshiryaet-geografiyu-prisutstviya</t>
+          <t>Открытых цифр продаж нет. В октябре 2025 сеть писала про 30 супермаркетов и новый зал в City Mall. Вы называли 62 — в открытых текстах 62 не нашли. Для ИТ это значит: по словам самой сети — расширение, не сжатие. Суммы и бюджет ИТ неизвестны. https://koinotinav.tj/news/set-supermarketov-evar-ukreplyaet-pozicii-i-rasshiryaet-geografiyu-prisutstviya</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t>62 точки — как вы указали. Открытой выручки нет. Попадаются «Fayz» и «Kredit Fayz» (техника) — это не обязательно та же сеть, деньги не ставили. Сигнал для ИТ: по открытым источникам ничего; ни «режем», ни «строим» подтвердить нельзя.</t>
+          <t>62 точки — как вы указали. Открытых продаж нет. Попадаются «Fayz» и «Kredit Fayz» (техника) — это не обязательно та же сеть, деньги не ставили. Для ИТ по открытым источникам ничего не видно: ни «режем», ни «строим» подтвердить нельзя.</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Года ещё нет (сейчас октябрь 2026), полного отчёта за весь 2026 ни у кого нет. В столбце «факт» — уже опубликованный кусок: девять месяцев, полгода или квартал. «Оценка года» — не отчёт, а арифметика: либо прогноз самой компании, либо выручка 2025, умноженная на рост уже вышедшего куска 2026. Где куска нет — «нет данных», ничего не додумано. Прибыль и маржа стоят только там, где компания сама их опубликовала за тот же кусок года.</t>
+          <t>Года ещё нет (сейчас октябрь 2026), полного отчёта за весь 2026 ни у кого нет. В столбце «факт» — уже опубликованный период: девять месяцев, полгода или квартал. «Оценка года» — не отчёт, а арифметика: либо прогноз самой компании, либо продажи 2025, умноженные на рост уже вышедшего периода 2026. Где периода нет — «нет данных», ничего не додумано. Прибыль и маржа стоят только там, где компания сама их опубликовала за тот же период.</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Продали за январь–сентябрь на 3,79 триллиона рублей, на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь быстрее полугодия: +13% до 1,31 триллиона. Чижик по-прежнему самый быстрый внутри группы (+31% за девять месяцев, +35% за квартал). Компания свой прогноз на весь год не снимала: +12–16%.</t>
+          <t>Продали за январь–сентябрь на 3,79 триллиона рублей, на 11,4% больше, чем за те же девять месяцев 2025-го. Июль–сентябрь быстрее полугодия: на 13% больше, до 1,31 триллиона. Чижик по-прежнему самый быстрый внутри группы (на 31% больше за девять месяцев, на 35% больше за квартал). Компания свой прогноз на весь год не меняла: плюс 12–16%.</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>В марте и снова в июне президент Екатерина Лобачева: прогноз роста выручки 12–16% на 2026 держим. От выручки 2025 (4,642 триллиона) это примерно 5,20–5,39 триллиона за полный год. Девять месяцев идут ближе к нижней границе.</t>
+          <t>В марте и снова в июне президент Екатерина Лобачева: прогноз роста продаж 12–16% на 2026 держим. От продаж 2025 (4,642 триллиона) это примерно 5,20–5,39 триллиона за полный год. Девять месяцев идут ближе к нижней границе.</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>1 887 млрд рублей за полгода, +12,8%. Магазины работают, продажи растут, по прибыли группа всё ещё в минусе: −1,9 млрд (без правила «аренда как долг»). Если аренду магазинов считать долгом, минус около −9,5. Мешают проценты по кредитам. Это тот же сюжет, что в 2025: полка живая, кредиты тяжёлые.</t>
+          <t>1 887 млрд рублей за полгода, на 12,8% больше, чем годом раньше. Магазины работают, продажи растут, по прибыли группа всё ещё в минусе: −1,9 млрд (без правила «аренда как долг»). Если аренду магазинов считать долгом, минус около −9,5. Мешают проценты по кредитам. Это тот же сюжет, что в 2025: полка живая, кредиты тяжёлые.</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Официальную прибыль за январь–июнь 2026 опубликовали шесть сетей и четыре завода. Сети: X5 25,7 млрд (маржа 1% — от продаж за январь–июнь 2 481, не от девяти месяцев), Магнит −1,9, Лента 13 (2%), Fix Price 2,7 (1,8%), «ДА!» 1,2 (2,8%), Винлаб 0,79 (1,5%). Заводы: Черкизово 14,1 (почти 10 копеек с рубля), Русагро почти ноль (0,056), Агроэко 1,99 (8,1%), ЭкоНива 1,1 (2,4% от всей группы). У остальных в этих столбцах «нет данных»: отчёта с прибылью за 2026 ещё нет. Мираторг писал прибыль 19,61 без полной выручки — в ячейку не ставили, маржу от этого не посчитать.</t>
+          <t>Официальную прибыль за январь–июнь 2026 опубликовали шесть сетей и четыре завода. Сети: X5 25,7 млрд (1% — от продаж за январь–июнь 2 481, не от девяти месяцев), Магнит −1,9, Лента 13 (2%), Fix Price 2,7 (1,8%), «ДА!» 1,2 (2,8%), Винлаб 0,79 (1,5%). Заводы: Черкизово 14,1 (почти 10 копеек с рубля), Русагро почти ноль (0,056), Агроэко 1,99 (8,1%), ЭкоНива 1,1 (2,4% от всей группы). У остальных в этих столбцах «нет данных»: отчёта с прибылью за 2026 ещё нет. Мираторг писал прибыль 19,61 без полных продаж — в ячейку не ставили, долю от этого не посчитать.</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Агентство INFOLine сложила десятку: 6,76 триллиона рублей, +11,6% (годом раньше десятка росла на 17%). Лента +26% — самый быстрый из крупных. Светофор и Ашан продали меньше, чем год назад. На весь 2026 агентство ждёт рост крупнейших сетей примерно 9–11%.</t>
+          <t>Агентство INFOLine сложила десятку: 6,76 триллиона рублей, на 11,6% больше (годом раньше десятка росла на 17%). Лента — на 26% больше, самый быстрый из крупных. Светофор и Ашан продали меньше, чем год назад. На весь 2026 агентство ждёт рост крупнейших сетей примерно 9–11%.</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>648 млрд рублей за полгода, +26%. Тянут «Супер Лента» и «Монетка». В августе купила большие магазины «О’КЕЙ» — со второго полугодия в цифрах будут ещё и эти магазины.</t>
+          <t>648 млрд рублей за полгода, на 26% больше, чем годом раньше. Тянут «Супер Лента» и «Монетка». В августе купила большие магазины «О’КЕЙ» — со второго полугодия в цифрах будут ещё и эти магазины.</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>155 млрд рублей, +4,8%. Медленнее больших продуктовых сетей: цены фиксированные, в ассортименте не только еда.</t>
+          <t>155 млрд рублей, на 4,8% больше, чем годом раньше. Медленнее больших продуктовых сетей: цены фиксированные, в ассортименте не только еда.</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>51 млрд рублей по официальному отчёту, +7%. Отдельно компания хвалится продажами с налогом за девять месяцев (+24%) — это отскок после кибератаки 2025-го, не путать с выручкой в таблице.</t>
+          <t>51 млрд рублей по официальному отчёту, на 7% больше, чем годом раньше. Отдельно компания хвалится продажами с налогом за девять месяцев (на 24% больше) — это отскок после кибератаки 2025-го, не те продажи, что в таблице.</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>183 млрд рублей, +9%. Догнать PepsiCo по году ещё рано: полного 2026 нет ни у кого из заводов.</t>
+          <t>183 млрд рублей, на 9% больше, чем годом раньше. Догнать PepsiCo по году ещё рано: полного 2026 нет ни у кого из заводов.</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>142 млрд рублей, всего +3,5%. Слабее роста цен в магазинах: дешевле свинина и меньше продаж в Китай.</t>
+          <t>142 млрд рублей, всего на 3,5% больше, чем годом раньше. Слабее роста цен в магазинах: дешевле свинина и меньше продаж в Китай.</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>46 млрд рублей, +19% — один из немногих заводов, у кого продажи выросли сильно.</t>
+          <t>46 млрд рублей, на 19% больше, чем годом раньше — один из немногих заводов, у кого продажи выросли сильно.</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Выручку за 2026 пока не раскрыли. Глава группы в июне: ждать роста «на несколько процентов», продажи за границу удержать около 58 млрд рублей.</t>
+          <t>Продажи за 2026 пока не раскрыли. Глава группы в июне: ждать роста «на несколько процентов», продажи за границу удержать около 58 млрд рублей.</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>По большинству сетей из регионов и заводов своего прогноза «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год +9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку выручки это не ставили — это не продажи компании. Регионы меньшего масштаба и сигнал «режут ли ИТ» — на листе «Регионы».</t>
+          <t>По большинству сетей из регионов и заводов своего плана «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год плюс 9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку продаж это не ставили — это не продажи компании. Сети поменьше и то, режут ли они ИТ, — на листе «Регионы».</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -7355,12 +7355,12 @@
     <row r="16" ht="72" customHeight="1" s="6">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Регионы меньшего масштаба — 2026 и ИТ</t>
+          <t>Регионы поменьше — 2026 и ИТ</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>У сетей на 30–200 точек своего отчёта за кусок 2026 почти нет. На листе «Регионы» те же десять колонок, что у крупных. В деньгах за 2026 чаще «нет данных». В комментарии — последний закрытый 2025 и что видно на 2026–27: открывают, склеивают сети, режут издержки или закрывают магазин. Это не «бюджет ИТ в рублях», такого никто не публикует.</t>
+          <t>У сетей на 30–200 точек своего отчёта за период 2026 почти нет. На листе «Регионы» те же десять колонок, что у крупных. В деньгах за 2026 чаще «нет данных». В комментарии — закрытый 2025 и что видно на 2026–27: открывают, склеивают сети, режут расходы или закрывают магазин. Это не «бюджет ИТ в рублях», такого никто не публикует.</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Агентство INFOLine: у крупнейших сетей за год до июня 2026 точек стало больше только на 4,9% (годом раньше было +10,8%). Новый магазин дороже на 8–12%. Часть денег уходит в доставку и цифру. Это фон рынка, не строка «Семишагофф».</t>
+          <t>Агентство INFOLine: у крупнейших сетей за год до июня 2026 точек стало больше только на 4,9% (годом раньше было на 10,8% больше). Новый магазин дороже на 8–12%. Часть денег уходит в доставку и программы. Это фон рынка, не строка «Семишагофф».</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -7397,12 +7397,12 @@
     <row r="18" ht="72" customHeight="1" s="6">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>SPAR Калининград — не путать юрлица</t>
+          <t>SPAR Калининград — две разные компании</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Операционная компания ООО «Евроритейл»: за 2025 продали на 32,7 млрд (+15%), прибыль 0,56 млрд. ООО «Спар-Калининград» — другое юрлицо, 54 млн выручки: это не магазины. Директор сети в июне 2025: 105 магазинов.</t>
+          <t>Магазины — это ООО «Евроритейл»: за 2025 продали на 32,7 млрд, на 15% больше, чем годом раньше, прибыль 0,56 млрд. ООО «Спар-Калининград» — другая компания, 54 млн продаж: это не магазины. Директор сети в июне 2025: 105 магазинов.</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>«Континент Сибирь» разобрал российские отчёты: «Лама» — сумма четырёх магазинных юрлиц 32,3 млрд, «Аникс» отдельно, «Бегемаг» 13 млрд при прибыли всего 65 млн, «Низкоцен» 9,5 млрд. Управляющую компанию «Лама» (134 млн) с магазинами складывать нельзя.</t>
+          <t>«Континент Сибирь» разобрал российские отчёты: «Лама» — сумма четырёх магазинных компаний 32,3 млрд, «Аникс» отдельно, «Бегемаг» 13 млрд при прибыли всего 65 млн, «Низкоцен» 9,5 млрд. Управляющую компанию «Лама» (134 млн) с магазинами складывать нельзя.</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже +11,6%, годом раньше было +17%). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
+          <t>После полугодия агентство ждало рост крупнейших продуктовых сетей примерно 9–11% за полный год (за январь–июнь десятка уже на 11,6% больше, годом раньше было на 17% больше). Это прогноз десятки, не «Мария-Ра» и не «Командор».</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже +0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только +1%.</t>
+          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже плюс 0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только на 1% больше.</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (+24%). К марту 1,83 триллиона (+22%), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не выручка одной Лавки или Ozon Fresh.</t>
+          <t>В январе агентство Data Insight заложило всю доставку продуктов в России на 1,8 триллиона рублей за 2026 (на 24% больше). К марту 1,83 триллиона (на 22% больше), к маю 1,84. Это весь рынок вместе с налогом и платой за доставку, не продажи одной Лавки или Ozon Fresh.</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>«Верный» с октября 2025 ищут покупателя (оценка 25–35 млрд — цена всего бизнеса). «Гулливер» в начале 2026 писали как выставленный на продажу. Про «Мария-Ра» летом 2026 писали, что смотрит «Лента». Цифры выручки на 2026 никто из них не давал.</t>
+          <t>«Верный» с октября 2025 ищут покупателя (оценка 25–35 млрд — цена всего бизнеса). «Гулливер» в начале 2026 писали как выставленный на продажу. Про «Мария-Ра» летом 2026 писали, что смотрит «Лента». Цифры продаж на 2026 никто из них не давал.</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -5983,7 +5983,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="98" customHeight="1" s="6">
+    <row r="4" ht="107" customHeight="1" s="6">
       <c r="A4" s="18" t="inlineStr">
         <is>
           <t>SPAR Калининград (ООО Евроритейл)</t>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>За 2026 продаж компания не публиковала. Что есть — весь 2025 у ООО «Евроритейл»: 32,68 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 563 миллиона — это 1,7 копейки с каждого рубля. Рядом есть другое ООО — «Спар-Калининград»: 54 миллиона выручки и двое сотрудников. Это не магазины, их цифры сюда не относятся. В апреле 2026 замгендиректора сказал: магазинов уже больше ста. «Пятёрочка» в области около двухсот — по числу точек и по цене с ней не соревнуются. За 2025 открыли шесть магазинов. Директор раньше говорила: каждый год плюс десять новых и 20–25 ремонтов старых. Электронные ценники уже стоят. Для ИТ это значит: сеть живая, не сворачивается. Деньги скорее на ремонт магазинов, ценники и доставку через паром, чем на то, чтобы догнать «Пятёрочку». https://kaliningrad-news.net/society/2026/04/17/281609.html</t>
+          <t>За 2026 продаж компания не публиковала. Что есть — весь 2025 у ООО «Евроритейл»: 32,68 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 563 миллиона — это 1,7 копейки с каждого рубля. Есть ещё фирма с похожим именем — ООО «Спар-Калининград». Это не магазины: она сдаёт в аренду товарные знаки и за 2025 показала 54 миллиона продаж. В налоговой у неё в штате в среднем двое людей. У сети SPAR больше ста магазинов — такие цифры к ней не относятся, в таблицу их не ставили. В апреле 2026 замгендиректора сказал: магазинов уже больше ста. «Пятёрочка» в области около двухсот — по числу точек и по цене с ней не соревнуются. За 2025 открыли шесть магазинов. Директор раньше говорила: каждый год плюс десять новых и 20–25 ремонтов старых. Электронные ценники уже стоят. Для ИТ это значит: сеть живая, не сворачивается. Деньги скорее на ремонт магазинов, ценники и доставку через паром, чем на то, чтобы догнать «Пятёрочку». https://kaliningrad-news.net/society/2026/04/17/281609.html</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       <c r="I22" s="17" t="n"/>
       <c r="J22" s="17" t="n"/>
     </row>
-    <row r="23" ht="80" customHeight="1" s="6">
+    <row r="23" ht="83" customHeight="1" s="6">
       <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Дружба (Рыбинск, Ярославская область)</t>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t>Сводных продаж сети нет — ни за 2026, ни за 2025. Сайт: 28 точек, 12 500 квадратных метров, 1 700 человек. Есть ООО «Дружба» с 66 миллионами выручки и 14 людьми — это не эта сеть, в таблицу не ставили. В июне 2026 объявили, что закрывают гипермаркет в ТЦ «Космос» (работал около 15 лет), дата около 20 июля. Для ИТ это значит: сеть сжимается, не расширяется. Новый дорогой софт на этом фоне маловероятен. https://ngs76.ru/gorod/v-rybinske-zakroetsya-gipermarket-druzhba-magazin-prorabotal-15-let-id341441/</t>
+          <t>Сводных продаж сети нет — ни за 2026, ни за 2025. Сайт: 28 точек, 12 500 квадратных метров, 1 700 человек. Есть ООО «Дружба» с 66 миллионами продаж и 14 людьми в налоговой. На сайте сети — 28 магазинов и 1 700 человек. Это разные фирмы, 66 миллионов в таблицу не ставили. В июне 2026 объявили, что закрывают гипермаркет в ТЦ «Космос» (работал около 15 лет), дата около 20 июля. Для ИТ это значит: сеть сжимается, не расширяется. Новый дорогой софт на этом фоне маловероятен. https://ngs76.ru/gorod/v-rybinske-zakroetsya-gipermarket-druzhba-magazin-prorabotal-15-let-id341441/</t>
         </is>
       </c>
     </row>
@@ -7402,12 +7402,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Магазины — это ООО «Евроритейл»: за 2025 продали на 32,7 млрд, на 15% больше, чем годом раньше, прибыль 0,56 млрд. ООО «Спар-Калининград» — другая компания, 54 млн продаж: это не магазины. Директор сети в июне 2025: 105 магазинов.</t>
+          <t>Магазины — это ООО «Евроритейл»: за 2025 продали на 32,7 млрд, на 15% больше, чем годом раньше, прибыль 0,56 млрд. ООО «Спар-Калининград» — другая фирма: сдаёт в аренду товарные знаки, 54 млн продаж и двое в штате по налоговой. Это не сто магазинов SPAR. Директор сети в июне 2025: 105 магазинов.</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>https://firmoteka.ru/3906321175</t>
+          <t>https://checko.ru/company/spar-kaliningrad-1133926040819</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -6083,7 +6083,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="79" customHeight="1" s="6">
+    <row r="6" ht="97" customHeight="1" s="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Аникс (ТС Аникс + Прайд-А)</t>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>у дома, Алтай</t>
+          <t>продукты у дома, Алтай</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>За 2026 продаж нет. Что есть — две компании за 2025: 18,3 + 13,0 = 31,3 млрд рублей. После расходов осталось 414 миллионов — 1,3 копейки с рубля. Своих магазинов 165, ещё 109 работают как франшиза «Корзинка». В 2025 прибыль выросла. Плана продаж на 2026 не публиковали. Для ИТ это значит: сеть живая и с прибылью, не экономит на всём. Но сколько именно тратят на ИТ — никто не говорит. https://tolknews.ru/ekonomika/214569-skolko-zarabotali-krupneyshie-seti-altaya-mariya-ra-i-aniks-v-godu</t>
+          <t>Да, продукты: магазины у дома в Алтайском крае, Республике Алтай и Новосибирской области. За 2026 продаж нет. Что есть — две компании за 2025. ООО «ТС Аникс» (сами магазины): 18,3 млрд, на 10% больше, чем годом раньше, прибыль 305 млн. ООО «Прайд-А» (опт продуктов на ту же сеть): 13,0 млрд, на 10% больше, прибыль 109 млн. Вместе 31,3 млрд и 414 млн — 1,3 копейки с рубля, для продуктов обычно. Местная пресса в апреле 2026: прибыль выросла больше чем на 70 млн, «повысили эффективность». Своих магазинов 165, ещё франшиза «Корзинка». Плана продаж на 2026 нет. Для ИТ это значит: по закрытому 2025 сеть не в убытке и продажи росли. Из этого не следует, что «не экономят»: сколько тратят на ИТ, никто не публиковал. https://tolknews.ru/ekonomika/214569-skolko-zarabotali-krupneyshie-seti-altaya-mariya-ra-i-aniks-v-godu</t>
         </is>
       </c>
     </row>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -6283,7 +6283,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="73" customHeight="1" s="6">
+    <row r="10" ht="89" customHeight="1" s="6">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>OFFPRICE (ООО Оффпрайс)</t>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>Это одежда, не продукты. За 2026 продаж нет. Что есть — весь 2025: 4,85 млрд рублей, на 1,8% больше, чем годом раньше. После расходов осталось 113 миллионов — 2,3 копейки с рубля. На сайте «30+ аутлетов»; вы называли 40. Рост почти остановился. Для ИТ это значит: слабый рост, и это не продуктовая сеть. Ни «режем», ни «строим» в открытом виде не видно. https://firmoteka.ru/7725844967</t>
+          <t>Это одежда, не продукты. За 2026 продаж нет. Что есть — весь 2025: 4,85 млрд рублей, всего на 1,8% больше, чем годом раньше — продажи почти не выросли. После расходов осталось 113 миллионов — 2,3 копейки с рубля. Для розницы это хорошо (у продуктов обычно около одной копейки), противоречия тут нет: с каждого рубля оставляют нормально, но сам оборот почти не растёт. Прибыль даже чуть села: на 15% меньше, чем в 2024-м. На сайте «30+ аутлетов»; вы называли 40. Сколько точек открыли за год — в открытом виде не нашли. Для ИТ это значит: не «режим порезок из-за дыры», но и не история про быстрое расширение. Бюджет ИТ никто не публиковал. https://firmoteka.ru/7725844967</t>
         </is>
       </c>
     </row>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -6549,7 +6549,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="72" customHeight="1" s="6">
+    <row r="16" ht="86" customHeight="1" s="6">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Каравай (ОАО, Санкт-Петербург)</t>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>За 2026 продаж нет. Что есть — весь 2025: 11,12 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 709 миллионов — 6,4 копейки с рубля. Есть ещё ангарский «Каравай» — это другая компания, сюда не относится. Для ИТ это значит: 2025 был прибыльным. Своего плана на 2026 нет. По рынку заводов рост около нуля. https://firmoteka.ru/rating-by-revenue-10_71_1</t>
+          <t>За 2026 продаж нет. Что есть — весь 2025: 11,12 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 709 миллионов — 6,4 копейки с рубля. Есть ещё ангарский «Каравай» — это другая компания, сюда не относится. Для ИТ это значит: 2025 был прибыльным. Своего плана на 2026 нет. Фраза про «рост около нуля» — не про этот завод. Агентство INFOLine в сентябре 2026: у крупных производителей еды продажи в 2026 почти стоят (ни плюс, ни минус). Это весь рынок, не цифра «Каравая». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
     </row>

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных». Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей плюс 9–11%, производители еды около нуля, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
+          <t>Пустых «примерно» без источника. Если открытой цифры нет — «нет данных». Сети из регионов и большинство молочных заводов так и стоят: они отчитаются в 2027-м. Общий фон рынка (десять крупнейших сетей плюс 9–11%, у крупных заводов за полгода 2026 рост уже слабый, вся доставка продуктов 1,83 триллиона) в строку конкретной компании не ставили.</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1" s="6">
+    <row r="6" ht="73" customHeight="1" s="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>KDV Group</t>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>Прогноза на 2026 нет. Агентство INFOLine берёт KDV как пример торможения: уже 2025 только на 1% больше, а в 2026 у крупных производителей еды рост «около нуля». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+          <t>Прогноза на 2026 нет. Агентство INFOLine берёт KDV как пример торможения: уже 2025 только на 1% больше. В сентябре 2026 они смотрели полгода у крупных (Русагро плюс 9%, Черкизово плюс 3,5%) и сказали, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра KDV. https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="J61" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="J64" s="13" t="inlineStr">
         <is>
-          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не эта компания. Отчёт за 2026 выйдет весной 2027.</t>
+          <t>Своего плана «в 2026 продадим на столько-то» не публиковали. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных заводов и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этой компании. Отчёт за 2026 выйдет весной 2027.</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="82" customHeight="1" s="6">
+    <row r="15" ht="89" customHeight="1" s="6">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Иркутский масложиркомбинат</t>
@@ -6545,11 +6545,11 @@
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t>За 2026 продаж нет. Что есть — весь 2025: 16,35 млрд рублей, почти как годом раньше (на 0,9% меньше). После расходов осталось 2,33 млрд. Это 14 копеек с рубля, но заметная часть — проценты по деньгам на счетах, не от продажи масла. Агентство INFOLine в сентябре 2026: у крупных производителей еды рост «около нуля» — это весь рынок, не этот завод. Для ИТ это значит: денег после 2025 много, своего плана строек на 2026 не нашли. Не похоже на режим порезок, но и анонса «тратим на программы» нет. https://finscanner.ru/company/3811185573/finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="86" customHeight="1" s="6">
+          <t>За 2026 продаж нет. Что есть — весь 2025: 16,35 млрд рублей, почти как годом раньше (на 0,9% меньше). После расходов осталось 2,33 млрд. Это 14 копеек с рубля, но заметная часть — проценты по деньгам на счетах, не от продажи масла. Агентство INFOLine в сентябре 2026 смотрело уже вышедшие полгода у крупных заводов (Русагро плюс 9%, Черкизово плюс 3,5%, ЭкоНива минус 2,4%) и сказало, что рост лидеров «приблизился к нулю». Это не отчёт за весь 2026 и не цифра этого завода. Для ИТ это значит: денег после 2025 много, своего плана строек на 2026 не нашли. Не похоже на режим порезок, но и анонса «тратим на программы» нет. https://finscanner.ru/company/3811185573/finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1" s="6">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Каравай (ОАО, Санкт-Петербург)</t>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>За 2026 продаж нет. Что есть — весь 2025: 11,12 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 709 миллионов — 6,4 копейки с рубля. Есть ещё ангарский «Каравай» — это другая компания, сюда не относится. Для ИТ это значит: 2025 был прибыльным. Своего плана на 2026 нет. Фраза про «рост около нуля» — не про этот завод. Агентство INFOLine в сентябре 2026: у крупных производителей еды продажи в 2026 почти стоят (ни плюс, ни минус). Это весь рынок, не цифра «Каравая». https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
+          <t>За 2026 продаж нет. Что есть — весь 2025: 11,12 млрд рублей, на 15% больше, чем годом раньше. После расходов осталось 709 миллионов — 6,4 копейки с рубля. Есть ещё ангарский «Каравай» — это другая компания, сюда не относится. Для ИТ это значит: 2025 был прибыльным. Своего плана на 2026 нет. Фраза про «рост около нуля» — не про этот завод и не отчёт за весь 2026. Агентство INFOLine в сентябре 2026 смотрело полгода у крупных: Русагро плюс 9%, Черкизово плюс 3,5%, ЭкоНива минус 2,4% — и отсюда сказало, что рост лидеров «приблизился к нулю». К «Караваю» это не цифра. https://www.retail.ru/news/infoline-vyruchka-krupneyshikh-proizvoditeley-produktov-pitaniya-padaet-16-sentyabrya-2026-282211/</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже плюс 0,4%, в 2026 рост лидеров «приблизился к нулю». KDV как пример: уже 2025 только на 1% больше.</t>
+          <t>Светлана Силенина, сентябрь 2026: после запрета на ввоз еды в 2014 году крупные производители росли на 11–16% в год, в 2025 среднее уже плюс 0,4%. За весь 2026 отчёта нет — они смотрели первое полугодие: Русагро плюс 9% (годом раньше за весь год было плюс 16,6%), Черкизово плюс 3,5% (было плюс 11,4%), «Логика молока» плюс 3,5%, ЭкоНива минус 2,4%. Отсюда слова, что рост лидеров «приблизился к нулю». KDV как пример торможения ещё по 2025: только плюс 1%.</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">

--- a/FMCG_RF_vyruchka_2026.xlsx
+++ b/FMCG_RF_vyruchka_2026.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="6" min="1" max="1"/>
@@ -493,7 +493,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" s="6">
+    <row r="9" ht="100" customHeight="1" s="6">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Что в столбцах «прибыль» и «маржа»</t>
@@ -549,7 +549,19 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Это сети на 30–200 точек и заводы поменьше. Продаж за период 2026 у них почти нет — в столбцах денег стоит «нет данных», чтобы не подменять 2026 закрытым 2025-м. В комментарии два слоя: закрытый год (чтобы видеть прибыль) и что видно на 2026–27 (открывают, склеивают сети, режут расходы, закрывают магазин). Никто из них не публикует «бюджет ИТ в рублях». Читать так: растёт и строит склад / склеивает компании после сделки — ИТ скорее не режут; продажи уже падали, убыток, закрывают гипермаркет — скорее заморозка; прибыли мало и «год эффективности» — ИТ только если окупается на расходах.</t>
+          <t>Это сети на 30–200 точек и заводы поменьше. Продаж за период 2026 у них почти нет — в столбцах денег стоит «нет данных», чтобы не подменять 2026 закрытым 2025-м. В комментарии: закрытый год и что видно на 2026–27. Бюджет ИТ в рублях никто не публикует.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="100" customHeight="1" s="6">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Что видно по регионам на 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Никто из этих сетей не заявил план активно открывать точки в 2026. По закрытому 2025 картина осторожная: кто-то чуть подрос в продажах, кто-то чуть в прибыли с рубля, кто-то почти ноль или минус по объёму («Низкоцен», «Иркутская аптека», гипермаркет «Дружбы»). Где тратят — чаще на оснащение уже работающих магазинов: электронные ценники, кассы самообслуживания, ремонт, склейка касс после сделки. Это не «режем ИТ под ноль», но и не гонка за новыми точками — с расходами аккуратничают. Исключения, где стройка всё же видна: склад «Семишагофф», корпус и склад «Любятово». Крупные федералы (X5, Лента) — другой слой: продажи за 2026 ещё растут, но новые магазины и у них открывают медленнее, чем год назад.</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7351,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>По большинству сетей из регионов и заводов своего плана «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год плюс 9–11%; крупные производители еды почти без роста), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку продаж это не ставили — это не продажи компании. Сети поменьше и то, режут ли они ИТ, — на листе «Регионы».</t>
+          <t>По большинству сетей из регионов и заводов своего плана «в 2026 продадим на столько-то» не было ни в конце 2025, ни в начале 2026. Что находилось: общий фон рынка (десять крупнейших сетей за год плюс 9–11%; у крупных заводов за полгода 2026 рост уже слабый), вся доставка продуктов в стране 1,83–1,84 триллиона (это не Ozon и не Лавка), и фразы вроде «новые заводы начнут себя окупать» у ЭФКО. В ячейку продаж это не ставили — это не продажи компании. Сети поменьше и то, режут ли они ИТ, — на листе «Регионы».</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -7360,7 +7372,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>У сетей на 30–200 точек своего отчёта за период 2026 почти нет. На листе «Регионы» те же десять колонок, что у крупных. В деньгах за 2026 чаще «нет данных». В комментарии — закрытый 2025 и что видно на 2026–27: открывают, склеивают сети, режут расходы или закрывают магазин. Это не «бюджет ИТ в рублях», такого никто не публикует.</t>
+          <t>У сетей на 30–200 точек плана «активно открываемся в 2026» в открытом виде нет. По 2025 кто-то чуть вырос в продажах или в прибыли с рубля, кто-то почти ноль или минус. Где тратят — чаще оснащение уже работающих точек (ценники, кассы, ремонт), не новая сетка магазинов. С расходами аккуратничают. Бюджет ИТ в рублях никто не публикует.</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
